--- a/xlsx/cards.unified.xlsx
+++ b/xlsx/cards.unified.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6900,11 +6900,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team SII。</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
           <t>SNH48,Team SII</t>
         </is>
       </c>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 曹可甜</t>
@@ -6915,11 +6918,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10337&amp;gid=10</t>
         </is>
       </c>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
+      <c r="R128" t="inlineStr"/>
+      <c r="S128" t="inlineStr"/>
+      <c r="T128" t="inlineStr"/>
+      <c r="U128" t="inlineStr"/>
+      <c r="V128" t="inlineStr"/>
+      <c r="W128" t="inlineStr"/>
+      <c r="X128" t="inlineStr"/>
+      <c r="Y128" t="inlineStr"/>
+      <c r="Z128" t="inlineStr"/>
+      <c r="AA128" t="inlineStr"/>
+      <c r="AB128" t="inlineStr"/>
+      <c r="AC128" t="inlineStr"/>
+      <c r="AD128" t="inlineStr"/>
+      <c r="AE128" t="inlineStr"/>
       <c r="AF128" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -6953,11 +6975,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team SII。</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
           <t>SNH48,Team SII</t>
         </is>
       </c>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 蒋夏羽</t>
@@ -6968,11 +6993,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10324&amp;gid=10</t>
         </is>
       </c>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr"/>
+      <c r="R129" t="inlineStr"/>
+      <c r="S129" t="inlineStr"/>
+      <c r="T129" t="inlineStr"/>
+      <c r="U129" t="inlineStr"/>
+      <c r="V129" t="inlineStr"/>
+      <c r="W129" t="inlineStr"/>
+      <c r="X129" t="inlineStr"/>
+      <c r="Y129" t="inlineStr"/>
+      <c r="Z129" t="inlineStr"/>
+      <c r="AA129" t="inlineStr"/>
+      <c r="AB129" t="inlineStr"/>
+      <c r="AC129" t="inlineStr"/>
+      <c r="AD129" t="inlineStr"/>
+      <c r="AE129" t="inlineStr"/>
       <c r="AF129" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -7006,11 +7050,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team SII。</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
           <t>SNH48,Team SII</t>
         </is>
       </c>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 刘婧阳</t>
@@ -7021,11 +7068,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10350&amp;gid=10</t>
         </is>
       </c>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
+      <c r="R130" t="inlineStr"/>
+      <c r="S130" t="inlineStr"/>
+      <c r="T130" t="inlineStr"/>
+      <c r="U130" t="inlineStr"/>
+      <c r="V130" t="inlineStr"/>
+      <c r="W130" t="inlineStr"/>
+      <c r="X130" t="inlineStr"/>
+      <c r="Y130" t="inlineStr"/>
+      <c r="Z130" t="inlineStr"/>
+      <c r="AA130" t="inlineStr"/>
+      <c r="AB130" t="inlineStr"/>
+      <c r="AC130" t="inlineStr"/>
+      <c r="AD130" t="inlineStr"/>
+      <c r="AE130" t="inlineStr"/>
       <c r="AF130" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -7059,11 +7125,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team SII。</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
           <t>SNH48,Team SII</t>
         </is>
       </c>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 刘诗彤</t>
@@ -7074,11 +7143,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10338&amp;gid=10</t>
         </is>
       </c>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr"/>
+      <c r="R131" t="inlineStr"/>
+      <c r="S131" t="inlineStr"/>
+      <c r="T131" t="inlineStr"/>
+      <c r="U131" t="inlineStr"/>
+      <c r="V131" t="inlineStr"/>
+      <c r="W131" t="inlineStr"/>
+      <c r="X131" t="inlineStr"/>
+      <c r="Y131" t="inlineStr"/>
+      <c r="Z131" t="inlineStr"/>
+      <c r="AA131" t="inlineStr"/>
+      <c r="AB131" t="inlineStr"/>
+      <c r="AC131" t="inlineStr"/>
+      <c r="AD131" t="inlineStr"/>
+      <c r="AE131" t="inlineStr"/>
       <c r="AF131" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -7112,11 +7200,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team SII。</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
           <t>SNH48,Team SII</t>
         </is>
       </c>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 李婷</t>
@@ -7127,11 +7218,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10353&amp;gid=10</t>
         </is>
       </c>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr"/>
+      <c r="R132" t="inlineStr"/>
+      <c r="S132" t="inlineStr"/>
+      <c r="T132" t="inlineStr"/>
+      <c r="U132" t="inlineStr"/>
+      <c r="V132" t="inlineStr"/>
+      <c r="W132" t="inlineStr"/>
+      <c r="X132" t="inlineStr"/>
+      <c r="Y132" t="inlineStr"/>
+      <c r="Z132" t="inlineStr"/>
+      <c r="AA132" t="inlineStr"/>
+      <c r="AB132" t="inlineStr"/>
+      <c r="AC132" t="inlineStr"/>
+      <c r="AD132" t="inlineStr"/>
+      <c r="AE132" t="inlineStr"/>
       <c r="AF132" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -7153,7 +7263,7 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -7165,11 +7275,18 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team SII。</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>https://bkimg.cdn.bcebos.com/pic/aa18972bd40735fae6cd8d304d0618b30f2443a7a2b8?x-bce-process=image/format,f_auto/quality,Q_70/resize,m_lfit,limit_1,w_536</t>
+        </is>
+      </c>
       <c r="I133" t="inlineStr">
         <is>
           <t>SNH48,Team SII</t>
         </is>
       </c>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 芦馨怡</t>
@@ -7180,11 +7297,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10267&amp;gid=10</t>
         </is>
       </c>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
+      <c r="R133" t="inlineStr"/>
+      <c r="S133" t="inlineStr"/>
+      <c r="T133" t="inlineStr"/>
+      <c r="U133" t="inlineStr"/>
+      <c r="V133" t="inlineStr"/>
+      <c r="W133" t="inlineStr"/>
+      <c r="X133" t="inlineStr"/>
+      <c r="Y133" t="inlineStr"/>
+      <c r="Z133" t="inlineStr"/>
+      <c r="AA133" t="inlineStr"/>
+      <c r="AB133" t="inlineStr"/>
+      <c r="AC133" t="inlineStr"/>
+      <c r="AD133" t="inlineStr"/>
+      <c r="AE133" t="inlineStr"/>
       <c r="AF133" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -7218,11 +7354,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team SII。</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
           <t>SNH48,Team SII</t>
         </is>
       </c>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 柳雨呈</t>
@@ -7233,11 +7372,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10339&amp;gid=10</t>
         </is>
       </c>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
+      <c r="R134" t="inlineStr"/>
+      <c r="S134" t="inlineStr"/>
+      <c r="T134" t="inlineStr"/>
+      <c r="U134" t="inlineStr"/>
+      <c r="V134" t="inlineStr"/>
+      <c r="W134" t="inlineStr"/>
+      <c r="X134" t="inlineStr"/>
+      <c r="Y134" t="inlineStr"/>
+      <c r="Z134" t="inlineStr"/>
+      <c r="AA134" t="inlineStr"/>
+      <c r="AB134" t="inlineStr"/>
+      <c r="AC134" t="inlineStr"/>
+      <c r="AD134" t="inlineStr"/>
+      <c r="AE134" t="inlineStr"/>
       <c r="AF134" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -7271,11 +7429,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team SII。</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
           <t>SNH48,Team SII</t>
         </is>
       </c>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 刘增艳</t>
@@ -7286,11 +7447,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10125&amp;gid=10</t>
         </is>
       </c>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr"/>
+      <c r="S135" t="inlineStr"/>
+      <c r="T135" t="inlineStr"/>
+      <c r="U135" t="inlineStr"/>
+      <c r="V135" t="inlineStr"/>
+      <c r="W135" t="inlineStr"/>
+      <c r="X135" t="inlineStr"/>
+      <c r="Y135" t="inlineStr"/>
+      <c r="Z135" t="inlineStr"/>
+      <c r="AA135" t="inlineStr"/>
+      <c r="AB135" t="inlineStr"/>
+      <c r="AC135" t="inlineStr"/>
+      <c r="AD135" t="inlineStr"/>
+      <c r="AE135" t="inlineStr"/>
       <c r="AF135" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -7324,11 +7504,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team SII。</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
           <t>SNH48,Team SII</t>
         </is>
       </c>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 宁轲</t>
@@ -7339,11 +7522,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10230&amp;gid=10</t>
         </is>
       </c>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr"/>
+      <c r="R136" t="inlineStr"/>
+      <c r="S136" t="inlineStr"/>
+      <c r="T136" t="inlineStr"/>
+      <c r="U136" t="inlineStr"/>
+      <c r="V136" t="inlineStr"/>
+      <c r="W136" t="inlineStr"/>
+      <c r="X136" t="inlineStr"/>
+      <c r="Y136" t="inlineStr"/>
+      <c r="Z136" t="inlineStr"/>
+      <c r="AA136" t="inlineStr"/>
+      <c r="AB136" t="inlineStr"/>
+      <c r="AC136" t="inlineStr"/>
+      <c r="AD136" t="inlineStr"/>
+      <c r="AE136" t="inlineStr"/>
       <c r="AF136" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -7377,11 +7579,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team SII。</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
           <t>SNH48,Team SII</t>
         </is>
       </c>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 盛乐</t>
@@ -7392,11 +7597,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10329&amp;gid=10</t>
         </is>
       </c>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr"/>
+      <c r="R137" t="inlineStr"/>
+      <c r="S137" t="inlineStr"/>
+      <c r="T137" t="inlineStr"/>
+      <c r="U137" t="inlineStr"/>
+      <c r="V137" t="inlineStr"/>
+      <c r="W137" t="inlineStr"/>
+      <c r="X137" t="inlineStr"/>
+      <c r="Y137" t="inlineStr"/>
+      <c r="Z137" t="inlineStr"/>
+      <c r="AA137" t="inlineStr"/>
+      <c r="AB137" t="inlineStr"/>
+      <c r="AC137" t="inlineStr"/>
+      <c r="AD137" t="inlineStr"/>
+      <c r="AE137" t="inlineStr"/>
       <c r="AF137" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -7430,11 +7654,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team SII。</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
           <t>SNH48,Team SII</t>
         </is>
       </c>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 田姝丽</t>
@@ -7445,11 +7672,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10130&amp;gid=10</t>
         </is>
       </c>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="inlineStr"/>
+      <c r="S138" t="inlineStr"/>
+      <c r="T138" t="inlineStr"/>
+      <c r="U138" t="inlineStr"/>
+      <c r="V138" t="inlineStr"/>
+      <c r="W138" t="inlineStr"/>
+      <c r="X138" t="inlineStr"/>
+      <c r="Y138" t="inlineStr"/>
+      <c r="Z138" t="inlineStr"/>
+      <c r="AA138" t="inlineStr"/>
+      <c r="AB138" t="inlineStr"/>
+      <c r="AC138" t="inlineStr"/>
+      <c r="AD138" t="inlineStr"/>
+      <c r="AE138" t="inlineStr"/>
       <c r="AF138" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -7483,11 +7729,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team SII。</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
           <t>SNH48,Team SII</t>
         </is>
       </c>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 吴志越</t>
@@ -7498,11 +7747,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10376&amp;gid=10</t>
         </is>
       </c>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr"/>
+      <c r="R139" t="inlineStr"/>
+      <c r="S139" t="inlineStr"/>
+      <c r="T139" t="inlineStr"/>
+      <c r="U139" t="inlineStr"/>
+      <c r="V139" t="inlineStr"/>
+      <c r="W139" t="inlineStr"/>
+      <c r="X139" t="inlineStr"/>
+      <c r="Y139" t="inlineStr"/>
+      <c r="Z139" t="inlineStr"/>
+      <c r="AA139" t="inlineStr"/>
+      <c r="AB139" t="inlineStr"/>
+      <c r="AC139" t="inlineStr"/>
+      <c r="AD139" t="inlineStr"/>
+      <c r="AE139" t="inlineStr"/>
       <c r="AF139" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -7536,11 +7804,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team SII。</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
           <t>SNH48,Team SII</t>
         </is>
       </c>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 由淼</t>
@@ -7551,11 +7822,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10227&amp;gid=10</t>
         </is>
       </c>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr"/>
+      <c r="R140" t="inlineStr"/>
+      <c r="S140" t="inlineStr"/>
+      <c r="T140" t="inlineStr"/>
+      <c r="U140" t="inlineStr"/>
+      <c r="V140" t="inlineStr"/>
+      <c r="W140" t="inlineStr"/>
+      <c r="X140" t="inlineStr"/>
+      <c r="Y140" t="inlineStr"/>
+      <c r="Z140" t="inlineStr"/>
+      <c r="AA140" t="inlineStr"/>
+      <c r="AB140" t="inlineStr"/>
+      <c r="AC140" t="inlineStr"/>
+      <c r="AD140" t="inlineStr"/>
+      <c r="AE140" t="inlineStr"/>
       <c r="AF140" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -7589,11 +7879,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team SII。</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
           <t>SNH48,Team SII</t>
         </is>
       </c>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 闫明筠</t>
@@ -7604,11 +7897,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10094&amp;gid=10</t>
         </is>
       </c>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr"/>
+      <c r="R141" t="inlineStr"/>
+      <c r="S141" t="inlineStr"/>
+      <c r="T141" t="inlineStr"/>
+      <c r="U141" t="inlineStr"/>
+      <c r="V141" t="inlineStr"/>
+      <c r="W141" t="inlineStr"/>
+      <c r="X141" t="inlineStr"/>
+      <c r="Y141" t="inlineStr"/>
+      <c r="Z141" t="inlineStr"/>
+      <c r="AA141" t="inlineStr"/>
+      <c r="AB141" t="inlineStr"/>
+      <c r="AC141" t="inlineStr"/>
+      <c r="AD141" t="inlineStr"/>
+      <c r="AE141" t="inlineStr"/>
       <c r="AF141" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -7642,11 +7954,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team SII。</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
           <t>SNH48,Team SII</t>
         </is>
       </c>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 杨心渝</t>
@@ -7657,11 +7972,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10289&amp;gid=10</t>
         </is>
       </c>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr"/>
+      <c r="R142" t="inlineStr"/>
+      <c r="S142" t="inlineStr"/>
+      <c r="T142" t="inlineStr"/>
+      <c r="U142" t="inlineStr"/>
+      <c r="V142" t="inlineStr"/>
+      <c r="W142" t="inlineStr"/>
+      <c r="X142" t="inlineStr"/>
+      <c r="Y142" t="inlineStr"/>
+      <c r="Z142" t="inlineStr"/>
+      <c r="AA142" t="inlineStr"/>
+      <c r="AB142" t="inlineStr"/>
+      <c r="AC142" t="inlineStr"/>
+      <c r="AD142" t="inlineStr"/>
+      <c r="AE142" t="inlineStr"/>
       <c r="AF142" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -7695,11 +8029,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team SII。</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
           <t>SNH48,Team SII</t>
         </is>
       </c>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 张雷雷</t>
@@ -7710,11 +8047,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10318&amp;gid=10</t>
         </is>
       </c>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr"/>
+      <c r="Q143" t="inlineStr"/>
+      <c r="R143" t="inlineStr"/>
+      <c r="S143" t="inlineStr"/>
+      <c r="T143" t="inlineStr"/>
+      <c r="U143" t="inlineStr"/>
+      <c r="V143" t="inlineStr"/>
+      <c r="W143" t="inlineStr"/>
+      <c r="X143" t="inlineStr"/>
+      <c r="Y143" t="inlineStr"/>
+      <c r="Z143" t="inlineStr"/>
+      <c r="AA143" t="inlineStr"/>
+      <c r="AB143" t="inlineStr"/>
+      <c r="AC143" t="inlineStr"/>
+      <c r="AD143" t="inlineStr"/>
+      <c r="AE143" t="inlineStr"/>
       <c r="AF143" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -7748,11 +8104,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team SII。</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
           <t>SNH48,Team SII</t>
         </is>
       </c>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 张倩</t>
@@ -7763,11 +8122,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10299&amp;gid=10</t>
         </is>
       </c>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr"/>
+      <c r="R144" t="inlineStr"/>
+      <c r="S144" t="inlineStr"/>
+      <c r="T144" t="inlineStr"/>
+      <c r="U144" t="inlineStr"/>
+      <c r="V144" t="inlineStr"/>
+      <c r="W144" t="inlineStr"/>
+      <c r="X144" t="inlineStr"/>
+      <c r="Y144" t="inlineStr"/>
+      <c r="Z144" t="inlineStr"/>
+      <c r="AA144" t="inlineStr"/>
+      <c r="AB144" t="inlineStr"/>
+      <c r="AC144" t="inlineStr"/>
+      <c r="AD144" t="inlineStr"/>
+      <c r="AE144" t="inlineStr"/>
       <c r="AF144" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -7801,11 +8179,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team SII。</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
           <t>SNH48,Team SII</t>
         </is>
       </c>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 周童玥</t>
@@ -7816,11 +8197,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10290&amp;gid=10</t>
         </is>
       </c>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
+      <c r="Q145" t="inlineStr"/>
+      <c r="R145" t="inlineStr"/>
+      <c r="S145" t="inlineStr"/>
+      <c r="T145" t="inlineStr"/>
+      <c r="U145" t="inlineStr"/>
+      <c r="V145" t="inlineStr"/>
+      <c r="W145" t="inlineStr"/>
+      <c r="X145" t="inlineStr"/>
+      <c r="Y145" t="inlineStr"/>
+      <c r="Z145" t="inlineStr"/>
+      <c r="AA145" t="inlineStr"/>
+      <c r="AB145" t="inlineStr"/>
+      <c r="AC145" t="inlineStr"/>
+      <c r="AD145" t="inlineStr"/>
+      <c r="AE145" t="inlineStr"/>
       <c r="AF145" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -7854,11 +8254,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team NII。</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
           <t>SNH48,Team NII</t>
         </is>
       </c>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 柏欣妤</t>
@@ -7869,11 +8272,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10234&amp;gid=10</t>
         </is>
       </c>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="inlineStr"/>
+      <c r="S146" t="inlineStr"/>
+      <c r="T146" t="inlineStr"/>
+      <c r="U146" t="inlineStr"/>
+      <c r="V146" t="inlineStr"/>
+      <c r="W146" t="inlineStr"/>
+      <c r="X146" t="inlineStr"/>
+      <c r="Y146" t="inlineStr"/>
+      <c r="Z146" t="inlineStr"/>
+      <c r="AA146" t="inlineStr"/>
+      <c r="AB146" t="inlineStr"/>
+      <c r="AC146" t="inlineStr"/>
+      <c r="AD146" t="inlineStr"/>
+      <c r="AE146" t="inlineStr"/>
       <c r="AF146" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -7907,11 +8329,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team NII。</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
           <t>SNH48,Team NII</t>
         </is>
       </c>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 葛俊言</t>
@@ -7922,11 +8347,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10371&amp;gid=10</t>
         </is>
       </c>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr"/>
+      <c r="R147" t="inlineStr"/>
+      <c r="S147" t="inlineStr"/>
+      <c r="T147" t="inlineStr"/>
+      <c r="U147" t="inlineStr"/>
+      <c r="V147" t="inlineStr"/>
+      <c r="W147" t="inlineStr"/>
+      <c r="X147" t="inlineStr"/>
+      <c r="Y147" t="inlineStr"/>
+      <c r="Z147" t="inlineStr"/>
+      <c r="AA147" t="inlineStr"/>
+      <c r="AB147" t="inlineStr"/>
+      <c r="AC147" t="inlineStr"/>
+      <c r="AD147" t="inlineStr"/>
+      <c r="AE147" t="inlineStr"/>
       <c r="AF147" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -7960,11 +8404,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team NII。</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
           <t>SNH48,Team NII</t>
         </is>
       </c>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 黄孟浠</t>
@@ -7975,11 +8422,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10372&amp;gid=10</t>
         </is>
       </c>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
+      <c r="Q148" t="inlineStr"/>
+      <c r="R148" t="inlineStr"/>
+      <c r="S148" t="inlineStr"/>
+      <c r="T148" t="inlineStr"/>
+      <c r="U148" t="inlineStr"/>
+      <c r="V148" t="inlineStr"/>
+      <c r="W148" t="inlineStr"/>
+      <c r="X148" t="inlineStr"/>
+      <c r="Y148" t="inlineStr"/>
+      <c r="Z148" t="inlineStr"/>
+      <c r="AA148" t="inlineStr"/>
+      <c r="AB148" t="inlineStr"/>
+      <c r="AC148" t="inlineStr"/>
+      <c r="AD148" t="inlineStr"/>
+      <c r="AE148" t="inlineStr"/>
       <c r="AF148" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -8013,11 +8479,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team NII。</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
           <t>SNH48,Team NII</t>
         </is>
       </c>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 胡晓慧</t>
@@ -8028,11 +8497,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10118&amp;gid=10</t>
         </is>
       </c>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
+      <c r="Q149" t="inlineStr"/>
+      <c r="R149" t="inlineStr"/>
+      <c r="S149" t="inlineStr"/>
+      <c r="T149" t="inlineStr"/>
+      <c r="U149" t="inlineStr"/>
+      <c r="V149" t="inlineStr"/>
+      <c r="W149" t="inlineStr"/>
+      <c r="X149" t="inlineStr"/>
+      <c r="Y149" t="inlineStr"/>
+      <c r="Z149" t="inlineStr"/>
+      <c r="AA149" t="inlineStr"/>
+      <c r="AB149" t="inlineStr"/>
+      <c r="AC149" t="inlineStr"/>
+      <c r="AD149" t="inlineStr"/>
+      <c r="AE149" t="inlineStr"/>
       <c r="AF149" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -8066,11 +8554,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team NII。</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
           <t>SNH48,Team NII</t>
         </is>
       </c>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 金莹玥</t>
@@ -8081,11 +8572,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10178&amp;gid=10</t>
         </is>
       </c>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr"/>
+      <c r="Q150" t="inlineStr"/>
+      <c r="R150" t="inlineStr"/>
+      <c r="S150" t="inlineStr"/>
+      <c r="T150" t="inlineStr"/>
+      <c r="U150" t="inlineStr"/>
+      <c r="V150" t="inlineStr"/>
+      <c r="W150" t="inlineStr"/>
+      <c r="X150" t="inlineStr"/>
+      <c r="Y150" t="inlineStr"/>
+      <c r="Z150" t="inlineStr"/>
+      <c r="AA150" t="inlineStr"/>
+      <c r="AB150" t="inlineStr"/>
+      <c r="AC150" t="inlineStr"/>
+      <c r="AD150" t="inlineStr"/>
+      <c r="AE150" t="inlineStr"/>
       <c r="AF150" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -8119,11 +8629,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team NII。</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
           <t>SNH48,Team NII</t>
         </is>
       </c>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 李继醇</t>
@@ -8134,11 +8647,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10349&amp;gid=10</t>
         </is>
       </c>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
+      <c r="Q151" t="inlineStr"/>
+      <c r="R151" t="inlineStr"/>
+      <c r="S151" t="inlineStr"/>
+      <c r="T151" t="inlineStr"/>
+      <c r="U151" t="inlineStr"/>
+      <c r="V151" t="inlineStr"/>
+      <c r="W151" t="inlineStr"/>
+      <c r="X151" t="inlineStr"/>
+      <c r="Y151" t="inlineStr"/>
+      <c r="Z151" t="inlineStr"/>
+      <c r="AA151" t="inlineStr"/>
+      <c r="AB151" t="inlineStr"/>
+      <c r="AC151" t="inlineStr"/>
+      <c r="AD151" t="inlineStr"/>
+      <c r="AE151" t="inlineStr"/>
       <c r="AF151" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -8172,11 +8704,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team NII。</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
           <t>SNH48,Team NII</t>
         </is>
       </c>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 潘瑛琪</t>
@@ -8187,11 +8722,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10126&amp;gid=10</t>
         </is>
       </c>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr"/>
+      <c r="Q152" t="inlineStr"/>
+      <c r="R152" t="inlineStr"/>
+      <c r="S152" t="inlineStr"/>
+      <c r="T152" t="inlineStr"/>
+      <c r="U152" t="inlineStr"/>
+      <c r="V152" t="inlineStr"/>
+      <c r="W152" t="inlineStr"/>
+      <c r="X152" t="inlineStr"/>
+      <c r="Y152" t="inlineStr"/>
+      <c r="Z152" t="inlineStr"/>
+      <c r="AA152" t="inlineStr"/>
+      <c r="AB152" t="inlineStr"/>
+      <c r="AC152" t="inlineStr"/>
+      <c r="AD152" t="inlineStr"/>
+      <c r="AE152" t="inlineStr"/>
       <c r="AF152" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -8225,11 +8779,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team NII。</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
           <t>SNH48,Team NII</t>
         </is>
       </c>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 秦箐忆</t>
@@ -8240,11 +8797,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10368&amp;gid=10</t>
         </is>
       </c>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr"/>
+      <c r="R153" t="inlineStr"/>
+      <c r="S153" t="inlineStr"/>
+      <c r="T153" t="inlineStr"/>
+      <c r="U153" t="inlineStr"/>
+      <c r="V153" t="inlineStr"/>
+      <c r="W153" t="inlineStr"/>
+      <c r="X153" t="inlineStr"/>
+      <c r="Y153" t="inlineStr"/>
+      <c r="Z153" t="inlineStr"/>
+      <c r="AA153" t="inlineStr"/>
+      <c r="AB153" t="inlineStr"/>
+      <c r="AC153" t="inlineStr"/>
+      <c r="AD153" t="inlineStr"/>
+      <c r="AE153" t="inlineStr"/>
       <c r="AF153" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -8278,11 +8854,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team NII。</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
           <t>SNH48,Team NII</t>
         </is>
       </c>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 青钰雯</t>
@@ -8293,11 +8872,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10238&amp;gid=10</t>
         </is>
       </c>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
+      <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="inlineStr"/>
+      <c r="S154" t="inlineStr"/>
+      <c r="T154" t="inlineStr"/>
+      <c r="U154" t="inlineStr"/>
+      <c r="V154" t="inlineStr"/>
+      <c r="W154" t="inlineStr"/>
+      <c r="X154" t="inlineStr"/>
+      <c r="Y154" t="inlineStr"/>
+      <c r="Z154" t="inlineStr"/>
+      <c r="AA154" t="inlineStr"/>
+      <c r="AB154" t="inlineStr"/>
+      <c r="AC154" t="inlineStr"/>
+      <c r="AD154" t="inlineStr"/>
+      <c r="AE154" t="inlineStr"/>
       <c r="AF154" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -8331,11 +8929,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team NII。</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr">
         <is>
           <t>SNH48,Team NII</t>
         </is>
       </c>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 沈馨</t>
@@ -8346,11 +8947,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10354&amp;gid=10</t>
         </is>
       </c>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr"/>
+      <c r="Q155" t="inlineStr"/>
+      <c r="R155" t="inlineStr"/>
+      <c r="S155" t="inlineStr"/>
+      <c r="T155" t="inlineStr"/>
+      <c r="U155" t="inlineStr"/>
+      <c r="V155" t="inlineStr"/>
+      <c r="W155" t="inlineStr"/>
+      <c r="X155" t="inlineStr"/>
+      <c r="Y155" t="inlineStr"/>
+      <c r="Z155" t="inlineStr"/>
+      <c r="AA155" t="inlineStr"/>
+      <c r="AB155" t="inlineStr"/>
+      <c r="AC155" t="inlineStr"/>
+      <c r="AD155" t="inlineStr"/>
+      <c r="AE155" t="inlineStr"/>
       <c r="AF155" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -8384,11 +9004,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team NII。</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
           <t>SNH48,Team NII</t>
         </is>
       </c>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 唐程成</t>
@@ -8399,11 +9022,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10295&amp;gid=10</t>
         </is>
       </c>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr"/>
+      <c r="Q156" t="inlineStr"/>
+      <c r="R156" t="inlineStr"/>
+      <c r="S156" t="inlineStr"/>
+      <c r="T156" t="inlineStr"/>
+      <c r="U156" t="inlineStr"/>
+      <c r="V156" t="inlineStr"/>
+      <c r="W156" t="inlineStr"/>
+      <c r="X156" t="inlineStr"/>
+      <c r="Y156" t="inlineStr"/>
+      <c r="Z156" t="inlineStr"/>
+      <c r="AA156" t="inlineStr"/>
+      <c r="AB156" t="inlineStr"/>
+      <c r="AC156" t="inlineStr"/>
+      <c r="AD156" t="inlineStr"/>
+      <c r="AE156" t="inlineStr"/>
       <c r="AF156" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -8437,11 +9079,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team NII。</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr">
         <is>
           <t>SNH48,Team NII</t>
         </is>
       </c>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 徐佳琳</t>
@@ -8452,11 +9097,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10355&amp;gid=10</t>
         </is>
       </c>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr"/>
+      <c r="Q157" t="inlineStr"/>
+      <c r="R157" t="inlineStr"/>
+      <c r="S157" t="inlineStr"/>
+      <c r="T157" t="inlineStr"/>
+      <c r="U157" t="inlineStr"/>
+      <c r="V157" t="inlineStr"/>
+      <c r="W157" t="inlineStr"/>
+      <c r="X157" t="inlineStr"/>
+      <c r="Y157" t="inlineStr"/>
+      <c r="Z157" t="inlineStr"/>
+      <c r="AA157" t="inlineStr"/>
+      <c r="AB157" t="inlineStr"/>
+      <c r="AC157" t="inlineStr"/>
+      <c r="AD157" t="inlineStr"/>
+      <c r="AE157" t="inlineStr"/>
       <c r="AF157" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -8490,11 +9154,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team NII。</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr">
         <is>
           <t>SNH48,Team NII</t>
         </is>
       </c>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 叶凡</t>
@@ -8505,11 +9172,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10298&amp;gid=10</t>
         </is>
       </c>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr"/>
+      <c r="Q158" t="inlineStr"/>
+      <c r="R158" t="inlineStr"/>
+      <c r="S158" t="inlineStr"/>
+      <c r="T158" t="inlineStr"/>
+      <c r="U158" t="inlineStr"/>
+      <c r="V158" t="inlineStr"/>
+      <c r="W158" t="inlineStr"/>
+      <c r="X158" t="inlineStr"/>
+      <c r="Y158" t="inlineStr"/>
+      <c r="Z158" t="inlineStr"/>
+      <c r="AA158" t="inlineStr"/>
+      <c r="AB158" t="inlineStr"/>
+      <c r="AC158" t="inlineStr"/>
+      <c r="AD158" t="inlineStr"/>
+      <c r="AE158" t="inlineStr"/>
       <c r="AF158" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -8543,11 +9229,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team NII。</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
           <t>SNH48,Team NII</t>
         </is>
       </c>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 杨宇馨</t>
@@ -8558,11 +9247,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10249&amp;gid=10</t>
         </is>
       </c>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr"/>
+      <c r="Q159" t="inlineStr"/>
+      <c r="R159" t="inlineStr"/>
+      <c r="S159" t="inlineStr"/>
+      <c r="T159" t="inlineStr"/>
+      <c r="U159" t="inlineStr"/>
+      <c r="V159" t="inlineStr"/>
+      <c r="W159" t="inlineStr"/>
+      <c r="X159" t="inlineStr"/>
+      <c r="Y159" t="inlineStr"/>
+      <c r="Z159" t="inlineStr"/>
+      <c r="AA159" t="inlineStr"/>
+      <c r="AB159" t="inlineStr"/>
+      <c r="AC159" t="inlineStr"/>
+      <c r="AD159" t="inlineStr"/>
+      <c r="AE159" t="inlineStr"/>
       <c r="AF159" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -8596,11 +9304,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team NII。</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
           <t>SNH48,Team NII</t>
         </is>
       </c>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 臧文萱</t>
@@ -8611,11 +9322,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10370&amp;gid=10</t>
         </is>
       </c>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr"/>
+      <c r="Q160" t="inlineStr"/>
+      <c r="R160" t="inlineStr"/>
+      <c r="S160" t="inlineStr"/>
+      <c r="T160" t="inlineStr"/>
+      <c r="U160" t="inlineStr"/>
+      <c r="V160" t="inlineStr"/>
+      <c r="W160" t="inlineStr"/>
+      <c r="X160" t="inlineStr"/>
+      <c r="Y160" t="inlineStr"/>
+      <c r="Z160" t="inlineStr"/>
+      <c r="AA160" t="inlineStr"/>
+      <c r="AB160" t="inlineStr"/>
+      <c r="AC160" t="inlineStr"/>
+      <c r="AD160" t="inlineStr"/>
+      <c r="AE160" t="inlineStr"/>
       <c r="AF160" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -8649,11 +9379,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team NII。</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
           <t>SNH48,Team NII</t>
         </is>
       </c>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 周湘</t>
@@ -8664,11 +9397,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10293&amp;gid=10</t>
         </is>
       </c>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr"/>
+      <c r="Q161" t="inlineStr"/>
+      <c r="R161" t="inlineStr"/>
+      <c r="S161" t="inlineStr"/>
+      <c r="T161" t="inlineStr"/>
+      <c r="U161" t="inlineStr"/>
+      <c r="V161" t="inlineStr"/>
+      <c r="W161" t="inlineStr"/>
+      <c r="X161" t="inlineStr"/>
+      <c r="Y161" t="inlineStr"/>
+      <c r="Z161" t="inlineStr"/>
+      <c r="AA161" t="inlineStr"/>
+      <c r="AB161" t="inlineStr"/>
+      <c r="AC161" t="inlineStr"/>
+      <c r="AD161" t="inlineStr"/>
+      <c r="AE161" t="inlineStr"/>
       <c r="AF161" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -8702,11 +9454,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team NII。</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
           <t>SNH48,Team NII</t>
         </is>
       </c>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 钟亚男</t>
@@ -8717,11 +9472,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10336&amp;gid=10</t>
         </is>
       </c>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr"/>
+      <c r="Q162" t="inlineStr"/>
+      <c r="R162" t="inlineStr"/>
+      <c r="S162" t="inlineStr"/>
+      <c r="T162" t="inlineStr"/>
+      <c r="U162" t="inlineStr"/>
+      <c r="V162" t="inlineStr"/>
+      <c r="W162" t="inlineStr"/>
+      <c r="X162" t="inlineStr"/>
+      <c r="Y162" t="inlineStr"/>
+      <c r="Z162" t="inlineStr"/>
+      <c r="AA162" t="inlineStr"/>
+      <c r="AB162" t="inlineStr"/>
+      <c r="AC162" t="inlineStr"/>
+      <c r="AD162" t="inlineStr"/>
+      <c r="AE162" t="inlineStr"/>
       <c r="AF162" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -8755,11 +9529,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team NII。</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
           <t>SNH48,Team NII</t>
         </is>
       </c>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 朱怡欣</t>
@@ -8770,11 +9547,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10320&amp;gid=10</t>
         </is>
       </c>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
+      <c r="P163" t="inlineStr"/>
+      <c r="Q163" t="inlineStr"/>
+      <c r="R163" t="inlineStr"/>
+      <c r="S163" t="inlineStr"/>
+      <c r="T163" t="inlineStr"/>
+      <c r="U163" t="inlineStr"/>
+      <c r="V163" t="inlineStr"/>
+      <c r="W163" t="inlineStr"/>
+      <c r="X163" t="inlineStr"/>
+      <c r="Y163" t="inlineStr"/>
+      <c r="Z163" t="inlineStr"/>
+      <c r="AA163" t="inlineStr"/>
+      <c r="AB163" t="inlineStr"/>
+      <c r="AC163" t="inlineStr"/>
+      <c r="AD163" t="inlineStr"/>
+      <c r="AE163" t="inlineStr"/>
       <c r="AF163" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -8808,11 +9604,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team HII。</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr">
         <is>
           <t>SNH48,Team HII</t>
         </is>
       </c>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 陈嘉仪</t>
@@ -8823,11 +9622,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10344&amp;gid=10</t>
         </is>
       </c>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
+      <c r="P164" t="inlineStr"/>
+      <c r="Q164" t="inlineStr"/>
+      <c r="R164" t="inlineStr"/>
+      <c r="S164" t="inlineStr"/>
+      <c r="T164" t="inlineStr"/>
+      <c r="U164" t="inlineStr"/>
+      <c r="V164" t="inlineStr"/>
+      <c r="W164" t="inlineStr"/>
+      <c r="X164" t="inlineStr"/>
+      <c r="Y164" t="inlineStr"/>
+      <c r="Z164" t="inlineStr"/>
+      <c r="AA164" t="inlineStr"/>
+      <c r="AB164" t="inlineStr"/>
+      <c r="AC164" t="inlineStr"/>
+      <c r="AD164" t="inlineStr"/>
+      <c r="AE164" t="inlineStr"/>
       <c r="AF164" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -8861,11 +9679,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team HII。</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
           <t>SNH48,Team HII</t>
         </is>
       </c>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 陈俞希</t>
@@ -8876,11 +9697,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10312&amp;gid=10</t>
         </is>
       </c>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr"/>
+      <c r="P165" t="inlineStr"/>
+      <c r="Q165" t="inlineStr"/>
+      <c r="R165" t="inlineStr"/>
+      <c r="S165" t="inlineStr"/>
+      <c r="T165" t="inlineStr"/>
+      <c r="U165" t="inlineStr"/>
+      <c r="V165" t="inlineStr"/>
+      <c r="W165" t="inlineStr"/>
+      <c r="X165" t="inlineStr"/>
+      <c r="Y165" t="inlineStr"/>
+      <c r="Z165" t="inlineStr"/>
+      <c r="AA165" t="inlineStr"/>
+      <c r="AB165" t="inlineStr"/>
+      <c r="AC165" t="inlineStr"/>
+      <c r="AD165" t="inlineStr"/>
+      <c r="AE165" t="inlineStr"/>
       <c r="AF165" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -8914,11 +9754,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team HII。</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
           <t>SNH48,Team HII</t>
         </is>
       </c>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 龚晨美</t>
@@ -8929,11 +9772,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10322&amp;gid=10</t>
         </is>
       </c>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
+      <c r="P166" t="inlineStr"/>
+      <c r="Q166" t="inlineStr"/>
+      <c r="R166" t="inlineStr"/>
+      <c r="S166" t="inlineStr"/>
+      <c r="T166" t="inlineStr"/>
+      <c r="U166" t="inlineStr"/>
+      <c r="V166" t="inlineStr"/>
+      <c r="W166" t="inlineStr"/>
+      <c r="X166" t="inlineStr"/>
+      <c r="Y166" t="inlineStr"/>
+      <c r="Z166" t="inlineStr"/>
+      <c r="AA166" t="inlineStr"/>
+      <c r="AB166" t="inlineStr"/>
+      <c r="AC166" t="inlineStr"/>
+      <c r="AD166" t="inlineStr"/>
+      <c r="AE166" t="inlineStr"/>
       <c r="AF166" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -8967,11 +9829,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team HII。</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
           <t>SNH48,Team HII</t>
         </is>
       </c>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 何馨曼</t>
@@ -8982,11 +9847,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10373&amp;gid=10</t>
         </is>
       </c>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr"/>
+      <c r="P167" t="inlineStr"/>
+      <c r="Q167" t="inlineStr"/>
+      <c r="R167" t="inlineStr"/>
+      <c r="S167" t="inlineStr"/>
+      <c r="T167" t="inlineStr"/>
+      <c r="U167" t="inlineStr"/>
+      <c r="V167" t="inlineStr"/>
+      <c r="W167" t="inlineStr"/>
+      <c r="X167" t="inlineStr"/>
+      <c r="Y167" t="inlineStr"/>
+      <c r="Z167" t="inlineStr"/>
+      <c r="AA167" t="inlineStr"/>
+      <c r="AB167" t="inlineStr"/>
+      <c r="AC167" t="inlineStr"/>
+      <c r="AD167" t="inlineStr"/>
+      <c r="AE167" t="inlineStr"/>
       <c r="AF167" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -9020,11 +9904,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team HII。</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr">
         <is>
           <t>SNH48,Team HII</t>
         </is>
       </c>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 蒋舒婷</t>
@@ -9035,11 +9922,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10120&amp;gid=10</t>
         </is>
       </c>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr"/>
+      <c r="P168" t="inlineStr"/>
+      <c r="Q168" t="inlineStr"/>
+      <c r="R168" t="inlineStr"/>
+      <c r="S168" t="inlineStr"/>
+      <c r="T168" t="inlineStr"/>
+      <c r="U168" t="inlineStr"/>
+      <c r="V168" t="inlineStr"/>
+      <c r="W168" t="inlineStr"/>
+      <c r="X168" t="inlineStr"/>
+      <c r="Y168" t="inlineStr"/>
+      <c r="Z168" t="inlineStr"/>
+      <c r="AA168" t="inlineStr"/>
+      <c r="AB168" t="inlineStr"/>
+      <c r="AC168" t="inlineStr"/>
+      <c r="AD168" t="inlineStr"/>
+      <c r="AE168" t="inlineStr"/>
       <c r="AF168" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -9073,11 +9979,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team HII。</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr">
         <is>
           <t>SNH48,Team HII</t>
         </is>
       </c>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 康楚翊</t>
@@ -9088,11 +9997,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10325&amp;gid=10</t>
         </is>
       </c>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="inlineStr"/>
+      <c r="Q169" t="inlineStr"/>
+      <c r="R169" t="inlineStr"/>
+      <c r="S169" t="inlineStr"/>
+      <c r="T169" t="inlineStr"/>
+      <c r="U169" t="inlineStr"/>
+      <c r="V169" t="inlineStr"/>
+      <c r="W169" t="inlineStr"/>
+      <c r="X169" t="inlineStr"/>
+      <c r="Y169" t="inlineStr"/>
+      <c r="Z169" t="inlineStr"/>
+      <c r="AA169" t="inlineStr"/>
+      <c r="AB169" t="inlineStr"/>
+      <c r="AC169" t="inlineStr"/>
+      <c r="AD169" t="inlineStr"/>
+      <c r="AE169" t="inlineStr"/>
       <c r="AF169" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -9126,11 +10054,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team HII。</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
           <t>SNH48,Team HII</t>
         </is>
       </c>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 李佳恩</t>
@@ -9141,11 +10072,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10151&amp;gid=10</t>
         </is>
       </c>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr"/>
+      <c r="P170" t="inlineStr"/>
+      <c r="Q170" t="inlineStr"/>
+      <c r="R170" t="inlineStr"/>
+      <c r="S170" t="inlineStr"/>
+      <c r="T170" t="inlineStr"/>
+      <c r="U170" t="inlineStr"/>
+      <c r="V170" t="inlineStr"/>
+      <c r="W170" t="inlineStr"/>
+      <c r="X170" t="inlineStr"/>
+      <c r="Y170" t="inlineStr"/>
+      <c r="Z170" t="inlineStr"/>
+      <c r="AA170" t="inlineStr"/>
+      <c r="AB170" t="inlineStr"/>
+      <c r="AC170" t="inlineStr"/>
+      <c r="AD170" t="inlineStr"/>
+      <c r="AE170" t="inlineStr"/>
       <c r="AF170" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -9179,11 +10129,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team HII。</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr">
         <is>
           <t>SNH48,Team HII</t>
         </is>
       </c>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 林舒晴</t>
@@ -9194,11 +10147,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10212&amp;gid=10</t>
         </is>
       </c>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
+      <c r="P171" t="inlineStr"/>
+      <c r="Q171" t="inlineStr"/>
+      <c r="R171" t="inlineStr"/>
+      <c r="S171" t="inlineStr"/>
+      <c r="T171" t="inlineStr"/>
+      <c r="U171" t="inlineStr"/>
+      <c r="V171" t="inlineStr"/>
+      <c r="W171" t="inlineStr"/>
+      <c r="X171" t="inlineStr"/>
+      <c r="Y171" t="inlineStr"/>
+      <c r="Z171" t="inlineStr"/>
+      <c r="AA171" t="inlineStr"/>
+      <c r="AB171" t="inlineStr"/>
+      <c r="AC171" t="inlineStr"/>
+      <c r="AD171" t="inlineStr"/>
+      <c r="AE171" t="inlineStr"/>
       <c r="AF171" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -9232,11 +10204,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team HII。</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
           <t>SNH48,Team HII</t>
         </is>
       </c>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 刘思雨</t>
@@ -9247,11 +10222,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10352&amp;gid=10</t>
         </is>
       </c>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr"/>
+      <c r="P172" t="inlineStr"/>
+      <c r="Q172" t="inlineStr"/>
+      <c r="R172" t="inlineStr"/>
+      <c r="S172" t="inlineStr"/>
+      <c r="T172" t="inlineStr"/>
+      <c r="U172" t="inlineStr"/>
+      <c r="V172" t="inlineStr"/>
+      <c r="W172" t="inlineStr"/>
+      <c r="X172" t="inlineStr"/>
+      <c r="Y172" t="inlineStr"/>
+      <c r="Z172" t="inlineStr"/>
+      <c r="AA172" t="inlineStr"/>
+      <c r="AB172" t="inlineStr"/>
+      <c r="AC172" t="inlineStr"/>
+      <c r="AD172" t="inlineStr"/>
+      <c r="AE172" t="inlineStr"/>
       <c r="AF172" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -9285,11 +10279,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team HII。</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
           <t>SNH48,Team HII</t>
         </is>
       </c>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 刘钇霏</t>
@@ -9300,11 +10297,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10367&amp;gid=10</t>
         </is>
       </c>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr"/>
+      <c r="P173" t="inlineStr"/>
+      <c r="Q173" t="inlineStr"/>
+      <c r="R173" t="inlineStr"/>
+      <c r="S173" t="inlineStr"/>
+      <c r="T173" t="inlineStr"/>
+      <c r="U173" t="inlineStr"/>
+      <c r="V173" t="inlineStr"/>
+      <c r="W173" t="inlineStr"/>
+      <c r="X173" t="inlineStr"/>
+      <c r="Y173" t="inlineStr"/>
+      <c r="Z173" t="inlineStr"/>
+      <c r="AA173" t="inlineStr"/>
+      <c r="AB173" t="inlineStr"/>
+      <c r="AC173" t="inlineStr"/>
+      <c r="AD173" t="inlineStr"/>
+      <c r="AE173" t="inlineStr"/>
       <c r="AF173" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -9338,11 +10354,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team HII。</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr">
         <is>
           <t>SNH48,Team HII</t>
         </is>
       </c>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 阙佳慧</t>
@@ -9353,11 +10372,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10328&amp;gid=10</t>
         </is>
       </c>
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr"/>
+      <c r="P174" t="inlineStr"/>
+      <c r="Q174" t="inlineStr"/>
+      <c r="R174" t="inlineStr"/>
+      <c r="S174" t="inlineStr"/>
+      <c r="T174" t="inlineStr"/>
+      <c r="U174" t="inlineStr"/>
+      <c r="V174" t="inlineStr"/>
+      <c r="W174" t="inlineStr"/>
+      <c r="X174" t="inlineStr"/>
+      <c r="Y174" t="inlineStr"/>
+      <c r="Z174" t="inlineStr"/>
+      <c r="AA174" t="inlineStr"/>
+      <c r="AB174" t="inlineStr"/>
+      <c r="AC174" t="inlineStr"/>
+      <c r="AD174" t="inlineStr"/>
+      <c r="AE174" t="inlineStr"/>
       <c r="AF174" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -9391,11 +10429,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team HII。</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr">
         <is>
           <t>SNH48,Team HII</t>
         </is>
       </c>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 覃柯蒙</t>
@@ -9406,11 +10447,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10330&amp;gid=10</t>
         </is>
       </c>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr"/>
+      <c r="P175" t="inlineStr"/>
+      <c r="Q175" t="inlineStr"/>
+      <c r="R175" t="inlineStr"/>
+      <c r="S175" t="inlineStr"/>
+      <c r="T175" t="inlineStr"/>
+      <c r="U175" t="inlineStr"/>
+      <c r="V175" t="inlineStr"/>
+      <c r="W175" t="inlineStr"/>
+      <c r="X175" t="inlineStr"/>
+      <c r="Y175" t="inlineStr"/>
+      <c r="Z175" t="inlineStr"/>
+      <c r="AA175" t="inlineStr"/>
+      <c r="AB175" t="inlineStr"/>
+      <c r="AC175" t="inlineStr"/>
+      <c r="AD175" t="inlineStr"/>
+      <c r="AE175" t="inlineStr"/>
       <c r="AF175" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -9444,11 +10504,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team HII。</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
           <t>SNH48,Team HII</t>
         </is>
       </c>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 宋昕冉</t>
@@ -9459,11 +10522,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10087&amp;gid=10</t>
         </is>
       </c>
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr"/>
+      <c r="P176" t="inlineStr"/>
+      <c r="Q176" t="inlineStr"/>
+      <c r="R176" t="inlineStr"/>
+      <c r="S176" t="inlineStr"/>
+      <c r="T176" t="inlineStr"/>
+      <c r="U176" t="inlineStr"/>
+      <c r="V176" t="inlineStr"/>
+      <c r="W176" t="inlineStr"/>
+      <c r="X176" t="inlineStr"/>
+      <c r="Y176" t="inlineStr"/>
+      <c r="Z176" t="inlineStr"/>
+      <c r="AA176" t="inlineStr"/>
+      <c r="AB176" t="inlineStr"/>
+      <c r="AC176" t="inlineStr"/>
+      <c r="AD176" t="inlineStr"/>
+      <c r="AE176" t="inlineStr"/>
       <c r="AF176" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -9497,11 +10579,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team HII。</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr">
         <is>
           <t>SNH48,Team HII</t>
         </is>
       </c>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 王佳琪</t>
@@ -9512,11 +10597,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10374&amp;gid=10</t>
         </is>
       </c>
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr"/>
+      <c r="P177" t="inlineStr"/>
+      <c r="Q177" t="inlineStr"/>
+      <c r="R177" t="inlineStr"/>
+      <c r="S177" t="inlineStr"/>
+      <c r="T177" t="inlineStr"/>
+      <c r="U177" t="inlineStr"/>
+      <c r="V177" t="inlineStr"/>
+      <c r="W177" t="inlineStr"/>
+      <c r="X177" t="inlineStr"/>
+      <c r="Y177" t="inlineStr"/>
+      <c r="Z177" t="inlineStr"/>
+      <c r="AA177" t="inlineStr"/>
+      <c r="AB177" t="inlineStr"/>
+      <c r="AC177" t="inlineStr"/>
+      <c r="AD177" t="inlineStr"/>
+      <c r="AE177" t="inlineStr"/>
       <c r="AF177" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -9550,11 +10654,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team HII。</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
           <t>SNH48,Team HII</t>
         </is>
       </c>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 温若其</t>
@@ -9565,11 +10672,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10286&amp;gid=10</t>
         </is>
       </c>
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr"/>
+      <c r="P178" t="inlineStr"/>
+      <c r="Q178" t="inlineStr"/>
+      <c r="R178" t="inlineStr"/>
+      <c r="S178" t="inlineStr"/>
+      <c r="T178" t="inlineStr"/>
+      <c r="U178" t="inlineStr"/>
+      <c r="V178" t="inlineStr"/>
+      <c r="W178" t="inlineStr"/>
+      <c r="X178" t="inlineStr"/>
+      <c r="Y178" t="inlineStr"/>
+      <c r="Z178" t="inlineStr"/>
+      <c r="AA178" t="inlineStr"/>
+      <c r="AB178" t="inlineStr"/>
+      <c r="AC178" t="inlineStr"/>
+      <c r="AD178" t="inlineStr"/>
+      <c r="AE178" t="inlineStr"/>
       <c r="AF178" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -9603,11 +10729,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team HII。</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr">
         <is>
           <t>SNH48,Team HII</t>
         </is>
       </c>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 王天娇</t>
@@ -9618,11 +10747,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10375&amp;gid=10</t>
         </is>
       </c>
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr"/>
+      <c r="P179" t="inlineStr"/>
+      <c r="Q179" t="inlineStr"/>
+      <c r="R179" t="inlineStr"/>
+      <c r="S179" t="inlineStr"/>
+      <c r="T179" t="inlineStr"/>
+      <c r="U179" t="inlineStr"/>
+      <c r="V179" t="inlineStr"/>
+      <c r="W179" t="inlineStr"/>
+      <c r="X179" t="inlineStr"/>
+      <c r="Y179" t="inlineStr"/>
+      <c r="Z179" t="inlineStr"/>
+      <c r="AA179" t="inlineStr"/>
+      <c r="AB179" t="inlineStr"/>
+      <c r="AC179" t="inlineStr"/>
+      <c r="AD179" t="inlineStr"/>
+      <c r="AE179" t="inlineStr"/>
       <c r="AF179" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -9656,11 +10804,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team HII。</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
           <t>SNH48,Team HII</t>
         </is>
       </c>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 应籽言</t>
@@ -9671,11 +10822,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10334&amp;gid=10</t>
         </is>
       </c>
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr"/>
+      <c r="P180" t="inlineStr"/>
+      <c r="Q180" t="inlineStr"/>
+      <c r="R180" t="inlineStr"/>
+      <c r="S180" t="inlineStr"/>
+      <c r="T180" t="inlineStr"/>
+      <c r="U180" t="inlineStr"/>
+      <c r="V180" t="inlineStr"/>
+      <c r="W180" t="inlineStr"/>
+      <c r="X180" t="inlineStr"/>
+      <c r="Y180" t="inlineStr"/>
+      <c r="Z180" t="inlineStr"/>
+      <c r="AA180" t="inlineStr"/>
+      <c r="AB180" t="inlineStr"/>
+      <c r="AC180" t="inlineStr"/>
+      <c r="AD180" t="inlineStr"/>
+      <c r="AE180" t="inlineStr"/>
       <c r="AF180" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -9709,11 +10879,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team HII。</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
           <t>SNH48,Team HII</t>
         </is>
       </c>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 张宸</t>
@@ -9724,11 +10897,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10377&amp;gid=10</t>
         </is>
       </c>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr"/>
+      <c r="P181" t="inlineStr"/>
+      <c r="Q181" t="inlineStr"/>
+      <c r="R181" t="inlineStr"/>
+      <c r="S181" t="inlineStr"/>
+      <c r="T181" t="inlineStr"/>
+      <c r="U181" t="inlineStr"/>
+      <c r="V181" t="inlineStr"/>
+      <c r="W181" t="inlineStr"/>
+      <c r="X181" t="inlineStr"/>
+      <c r="Y181" t="inlineStr"/>
+      <c r="Z181" t="inlineStr"/>
+      <c r="AA181" t="inlineStr"/>
+      <c r="AB181" t="inlineStr"/>
+      <c r="AC181" t="inlineStr"/>
+      <c r="AD181" t="inlineStr"/>
+      <c r="AE181" t="inlineStr"/>
       <c r="AF181" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -9762,11 +10954,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team HII。</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
           <t>SNH48,Team HII</t>
         </is>
       </c>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 郑柯炜</t>
@@ -9777,11 +10972,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10358&amp;gid=10</t>
         </is>
       </c>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr"/>
+      <c r="P182" t="inlineStr"/>
+      <c r="Q182" t="inlineStr"/>
+      <c r="R182" t="inlineStr"/>
+      <c r="S182" t="inlineStr"/>
+      <c r="T182" t="inlineStr"/>
+      <c r="U182" t="inlineStr"/>
+      <c r="V182" t="inlineStr"/>
+      <c r="W182" t="inlineStr"/>
+      <c r="X182" t="inlineStr"/>
+      <c r="Y182" t="inlineStr"/>
+      <c r="Z182" t="inlineStr"/>
+      <c r="AA182" t="inlineStr"/>
+      <c r="AB182" t="inlineStr"/>
+      <c r="AC182" t="inlineStr"/>
+      <c r="AD182" t="inlineStr"/>
+      <c r="AE182" t="inlineStr"/>
       <c r="AF182" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -9815,11 +11029,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team HII。</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr">
         <is>
           <t>SNH48,Team HII</t>
         </is>
       </c>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 张琼予</t>
@@ -9830,11 +11047,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10218&amp;gid=10</t>
         </is>
       </c>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr"/>
+      <c r="P183" t="inlineStr"/>
+      <c r="Q183" t="inlineStr"/>
+      <c r="R183" t="inlineStr"/>
+      <c r="S183" t="inlineStr"/>
+      <c r="T183" t="inlineStr"/>
+      <c r="U183" t="inlineStr"/>
+      <c r="V183" t="inlineStr"/>
+      <c r="W183" t="inlineStr"/>
+      <c r="X183" t="inlineStr"/>
+      <c r="Y183" t="inlineStr"/>
+      <c r="Z183" t="inlineStr"/>
+      <c r="AA183" t="inlineStr"/>
+      <c r="AB183" t="inlineStr"/>
+      <c r="AC183" t="inlineStr"/>
+      <c r="AD183" t="inlineStr"/>
+      <c r="AE183" t="inlineStr"/>
       <c r="AF183" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -9868,11 +11104,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team HII。</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
           <t>SNH48,Team HII</t>
         </is>
       </c>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 曾雪婷</t>
@@ -9883,11 +11122,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10359&amp;gid=10</t>
         </is>
       </c>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr"/>
+      <c r="P184" t="inlineStr"/>
+      <c r="Q184" t="inlineStr"/>
+      <c r="R184" t="inlineStr"/>
+      <c r="S184" t="inlineStr"/>
+      <c r="T184" t="inlineStr"/>
+      <c r="U184" t="inlineStr"/>
+      <c r="V184" t="inlineStr"/>
+      <c r="W184" t="inlineStr"/>
+      <c r="X184" t="inlineStr"/>
+      <c r="Y184" t="inlineStr"/>
+      <c r="Z184" t="inlineStr"/>
+      <c r="AA184" t="inlineStr"/>
+      <c r="AB184" t="inlineStr"/>
+      <c r="AC184" t="inlineStr"/>
+      <c r="AD184" t="inlineStr"/>
+      <c r="AE184" t="inlineStr"/>
       <c r="AF184" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -9921,11 +11179,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team X。</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
           <t>SNH48,Team X</t>
         </is>
       </c>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 陈琳</t>
@@ -9936,11 +11197,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10081&amp;gid=10</t>
         </is>
       </c>
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr"/>
+      <c r="P185" t="inlineStr"/>
+      <c r="Q185" t="inlineStr"/>
+      <c r="R185" t="inlineStr"/>
+      <c r="S185" t="inlineStr"/>
+      <c r="T185" t="inlineStr"/>
+      <c r="U185" t="inlineStr"/>
+      <c r="V185" t="inlineStr"/>
+      <c r="W185" t="inlineStr"/>
+      <c r="X185" t="inlineStr"/>
+      <c r="Y185" t="inlineStr"/>
+      <c r="Z185" t="inlineStr"/>
+      <c r="AA185" t="inlineStr"/>
+      <c r="AB185" t="inlineStr"/>
+      <c r="AC185" t="inlineStr"/>
+      <c r="AD185" t="inlineStr"/>
+      <c r="AE185" t="inlineStr"/>
       <c r="AF185" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -9974,11 +11254,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team X。</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
           <t>SNH48,Team X</t>
         </is>
       </c>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 金泓言</t>
@@ -9989,11 +11272,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10313&amp;gid=10</t>
         </is>
       </c>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr"/>
+      <c r="P186" t="inlineStr"/>
+      <c r="Q186" t="inlineStr"/>
+      <c r="R186" t="inlineStr"/>
+      <c r="S186" t="inlineStr"/>
+      <c r="T186" t="inlineStr"/>
+      <c r="U186" t="inlineStr"/>
+      <c r="V186" t="inlineStr"/>
+      <c r="W186" t="inlineStr"/>
+      <c r="X186" t="inlineStr"/>
+      <c r="Y186" t="inlineStr"/>
+      <c r="Z186" t="inlineStr"/>
+      <c r="AA186" t="inlineStr"/>
+      <c r="AB186" t="inlineStr"/>
+      <c r="AC186" t="inlineStr"/>
+      <c r="AD186" t="inlineStr"/>
+      <c r="AE186" t="inlineStr"/>
       <c r="AF186" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -10027,11 +11329,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team X。</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
           <t>SNH48,Team X</t>
         </is>
       </c>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 蒋欣洳</t>
@@ -10042,11 +11347,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10347&amp;gid=10</t>
         </is>
       </c>
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr"/>
+      <c r="P187" t="inlineStr"/>
+      <c r="Q187" t="inlineStr"/>
+      <c r="R187" t="inlineStr"/>
+      <c r="S187" t="inlineStr"/>
+      <c r="T187" t="inlineStr"/>
+      <c r="U187" t="inlineStr"/>
+      <c r="V187" t="inlineStr"/>
+      <c r="W187" t="inlineStr"/>
+      <c r="X187" t="inlineStr"/>
+      <c r="Y187" t="inlineStr"/>
+      <c r="Z187" t="inlineStr"/>
+      <c r="AA187" t="inlineStr"/>
+      <c r="AB187" t="inlineStr"/>
+      <c r="AC187" t="inlineStr"/>
+      <c r="AD187" t="inlineStr"/>
+      <c r="AE187" t="inlineStr"/>
       <c r="AF187" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -10080,11 +11404,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team X。</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr">
         <is>
           <t>SNH48,Team X</t>
         </is>
       </c>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 林佳怡</t>
@@ -10095,11 +11422,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10259&amp;gid=10</t>
         </is>
       </c>
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr"/>
+      <c r="P188" t="inlineStr"/>
+      <c r="Q188" t="inlineStr"/>
+      <c r="R188" t="inlineStr"/>
+      <c r="S188" t="inlineStr"/>
+      <c r="T188" t="inlineStr"/>
+      <c r="U188" t="inlineStr"/>
+      <c r="V188" t="inlineStr"/>
+      <c r="W188" t="inlineStr"/>
+      <c r="X188" t="inlineStr"/>
+      <c r="Y188" t="inlineStr"/>
+      <c r="Z188" t="inlineStr"/>
+      <c r="AA188" t="inlineStr"/>
+      <c r="AB188" t="inlineStr"/>
+      <c r="AC188" t="inlineStr"/>
+      <c r="AD188" t="inlineStr"/>
+      <c r="AE188" t="inlineStr"/>
       <c r="AF188" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -10133,11 +11479,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team X。</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
           <t>SNH48,Team X</t>
         </is>
       </c>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 刘小涵</t>
@@ -10148,11 +11497,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10274&amp;gid=10</t>
         </is>
       </c>
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr"/>
+      <c r="P189" t="inlineStr"/>
+      <c r="Q189" t="inlineStr"/>
+      <c r="R189" t="inlineStr"/>
+      <c r="S189" t="inlineStr"/>
+      <c r="T189" t="inlineStr"/>
+      <c r="U189" t="inlineStr"/>
+      <c r="V189" t="inlineStr"/>
+      <c r="W189" t="inlineStr"/>
+      <c r="X189" t="inlineStr"/>
+      <c r="Y189" t="inlineStr"/>
+      <c r="Z189" t="inlineStr"/>
+      <c r="AA189" t="inlineStr"/>
+      <c r="AB189" t="inlineStr"/>
+      <c r="AC189" t="inlineStr"/>
+      <c r="AD189" t="inlineStr"/>
+      <c r="AE189" t="inlineStr"/>
       <c r="AF189" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -10186,11 +11554,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team X。</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
           <t>SNH48,Team X</t>
         </is>
       </c>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 马欣宇</t>
@@ -10201,11 +11572,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10340&amp;gid=10</t>
         </is>
       </c>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr"/>
+      <c r="P190" t="inlineStr"/>
+      <c r="Q190" t="inlineStr"/>
+      <c r="R190" t="inlineStr"/>
+      <c r="S190" t="inlineStr"/>
+      <c r="T190" t="inlineStr"/>
+      <c r="U190" t="inlineStr"/>
+      <c r="V190" t="inlineStr"/>
+      <c r="W190" t="inlineStr"/>
+      <c r="X190" t="inlineStr"/>
+      <c r="Y190" t="inlineStr"/>
+      <c r="Z190" t="inlineStr"/>
+      <c r="AA190" t="inlineStr"/>
+      <c r="AB190" t="inlineStr"/>
+      <c r="AC190" t="inlineStr"/>
+      <c r="AD190" t="inlineStr"/>
+      <c r="AE190" t="inlineStr"/>
       <c r="AF190" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -10239,11 +11629,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team X。</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
           <t>SNH48,Team X</t>
         </is>
       </c>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 王睿琦</t>
@@ -10254,11 +11647,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10220&amp;gid=10</t>
         </is>
       </c>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr"/>
+      <c r="P191" t="inlineStr"/>
+      <c r="Q191" t="inlineStr"/>
+      <c r="R191" t="inlineStr"/>
+      <c r="S191" t="inlineStr"/>
+      <c r="T191" t="inlineStr"/>
+      <c r="U191" t="inlineStr"/>
+      <c r="V191" t="inlineStr"/>
+      <c r="W191" t="inlineStr"/>
+      <c r="X191" t="inlineStr"/>
+      <c r="Y191" t="inlineStr"/>
+      <c r="Z191" t="inlineStr"/>
+      <c r="AA191" t="inlineStr"/>
+      <c r="AB191" t="inlineStr"/>
+      <c r="AC191" t="inlineStr"/>
+      <c r="AD191" t="inlineStr"/>
+      <c r="AE191" t="inlineStr"/>
       <c r="AF191" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -10292,11 +11704,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team X。</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
           <t>SNH48,Team X</t>
         </is>
       </c>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 熊紫轶</t>
@@ -10307,11 +11722,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10269&amp;gid=10</t>
         </is>
       </c>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr"/>
+      <c r="P192" t="inlineStr"/>
+      <c r="Q192" t="inlineStr"/>
+      <c r="R192" t="inlineStr"/>
+      <c r="S192" t="inlineStr"/>
+      <c r="T192" t="inlineStr"/>
+      <c r="U192" t="inlineStr"/>
+      <c r="V192" t="inlineStr"/>
+      <c r="W192" t="inlineStr"/>
+      <c r="X192" t="inlineStr"/>
+      <c r="Y192" t="inlineStr"/>
+      <c r="Z192" t="inlineStr"/>
+      <c r="AA192" t="inlineStr"/>
+      <c r="AB192" t="inlineStr"/>
+      <c r="AC192" t="inlineStr"/>
+      <c r="AD192" t="inlineStr"/>
+      <c r="AE192" t="inlineStr"/>
       <c r="AF192" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -10345,11 +11779,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team X。</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
           <t>SNH48,Team X</t>
         </is>
       </c>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 杨冰怡</t>
@@ -10360,11 +11797,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10093&amp;gid=10</t>
         </is>
       </c>
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr"/>
+      <c r="P193" t="inlineStr"/>
+      <c r="Q193" t="inlineStr"/>
+      <c r="R193" t="inlineStr"/>
+      <c r="S193" t="inlineStr"/>
+      <c r="T193" t="inlineStr"/>
+      <c r="U193" t="inlineStr"/>
+      <c r="V193" t="inlineStr"/>
+      <c r="W193" t="inlineStr"/>
+      <c r="X193" t="inlineStr"/>
+      <c r="Y193" t="inlineStr"/>
+      <c r="Z193" t="inlineStr"/>
+      <c r="AA193" t="inlineStr"/>
+      <c r="AB193" t="inlineStr"/>
+      <c r="AC193" t="inlineStr"/>
+      <c r="AD193" t="inlineStr"/>
+      <c r="AE193" t="inlineStr"/>
       <c r="AF193" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -10398,11 +11854,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team X。</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
           <t>SNH48,Team X</t>
         </is>
       </c>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 禹佳蔚</t>
@@ -10413,11 +11872,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10261&amp;gid=10</t>
         </is>
       </c>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr"/>
+      <c r="P194" t="inlineStr"/>
+      <c r="Q194" t="inlineStr"/>
+      <c r="R194" t="inlineStr"/>
+      <c r="S194" t="inlineStr"/>
+      <c r="T194" t="inlineStr"/>
+      <c r="U194" t="inlineStr"/>
+      <c r="V194" t="inlineStr"/>
+      <c r="W194" t="inlineStr"/>
+      <c r="X194" t="inlineStr"/>
+      <c r="Y194" t="inlineStr"/>
+      <c r="Z194" t="inlineStr"/>
+      <c r="AA194" t="inlineStr"/>
+      <c r="AB194" t="inlineStr"/>
+      <c r="AC194" t="inlineStr"/>
+      <c r="AD194" t="inlineStr"/>
+      <c r="AE194" t="inlineStr"/>
       <c r="AF194" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -10451,11 +11929,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team X。</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
           <t>SNH48,Team X</t>
         </is>
       </c>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 闫娜</t>
@@ -10466,11 +11947,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10258&amp;gid=10</t>
         </is>
       </c>
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr"/>
+      <c r="P195" t="inlineStr"/>
+      <c r="Q195" t="inlineStr"/>
+      <c r="R195" t="inlineStr"/>
+      <c r="S195" t="inlineStr"/>
+      <c r="T195" t="inlineStr"/>
+      <c r="U195" t="inlineStr"/>
+      <c r="V195" t="inlineStr"/>
+      <c r="W195" t="inlineStr"/>
+      <c r="X195" t="inlineStr"/>
+      <c r="Y195" t="inlineStr"/>
+      <c r="Z195" t="inlineStr"/>
+      <c r="AA195" t="inlineStr"/>
+      <c r="AB195" t="inlineStr"/>
+      <c r="AC195" t="inlineStr"/>
+      <c r="AD195" t="inlineStr"/>
+      <c r="AE195" t="inlineStr"/>
       <c r="AF195" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -10504,11 +12004,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team X。</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
           <t>SNH48,Team X</t>
         </is>
       </c>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 杨秋野</t>
@@ -10519,11 +12022,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10316&amp;gid=10</t>
         </is>
       </c>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr"/>
+      <c r="P196" t="inlineStr"/>
+      <c r="Q196" t="inlineStr"/>
+      <c r="R196" t="inlineStr"/>
+      <c r="S196" t="inlineStr"/>
+      <c r="T196" t="inlineStr"/>
+      <c r="U196" t="inlineStr"/>
+      <c r="V196" t="inlineStr"/>
+      <c r="W196" t="inlineStr"/>
+      <c r="X196" t="inlineStr"/>
+      <c r="Y196" t="inlineStr"/>
+      <c r="Z196" t="inlineStr"/>
+      <c r="AA196" t="inlineStr"/>
+      <c r="AB196" t="inlineStr"/>
+      <c r="AC196" t="inlineStr"/>
+      <c r="AD196" t="inlineStr"/>
+      <c r="AE196" t="inlineStr"/>
       <c r="AF196" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -10557,11 +12079,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team X。</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
           <t>SNH48,Team X</t>
         </is>
       </c>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 杨晔</t>
@@ -10572,11 +12097,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10247&amp;gid=10</t>
         </is>
       </c>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr"/>
+      <c r="P197" t="inlineStr"/>
+      <c r="Q197" t="inlineStr"/>
+      <c r="R197" t="inlineStr"/>
+      <c r="S197" t="inlineStr"/>
+      <c r="T197" t="inlineStr"/>
+      <c r="U197" t="inlineStr"/>
+      <c r="V197" t="inlineStr"/>
+      <c r="W197" t="inlineStr"/>
+      <c r="X197" t="inlineStr"/>
+      <c r="Y197" t="inlineStr"/>
+      <c r="Z197" t="inlineStr"/>
+      <c r="AA197" t="inlineStr"/>
+      <c r="AB197" t="inlineStr"/>
+      <c r="AC197" t="inlineStr"/>
+      <c r="AD197" t="inlineStr"/>
+      <c r="AE197" t="inlineStr"/>
       <c r="AF197" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -10610,11 +12154,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team X。</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
           <t>SNH48,Team X</t>
         </is>
       </c>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 钟郭菲杨</t>
@@ -10625,11 +12172,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10357&amp;gid=10</t>
         </is>
       </c>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr"/>
+      <c r="P198" t="inlineStr"/>
+      <c r="Q198" t="inlineStr"/>
+      <c r="R198" t="inlineStr"/>
+      <c r="S198" t="inlineStr"/>
+      <c r="T198" t="inlineStr"/>
+      <c r="U198" t="inlineStr"/>
+      <c r="V198" t="inlineStr"/>
+      <c r="W198" t="inlineStr"/>
+      <c r="X198" t="inlineStr"/>
+      <c r="Y198" t="inlineStr"/>
+      <c r="Z198" t="inlineStr"/>
+      <c r="AA198" t="inlineStr"/>
+      <c r="AB198" t="inlineStr"/>
+      <c r="AC198" t="inlineStr"/>
+      <c r="AD198" t="inlineStr"/>
+      <c r="AE198" t="inlineStr"/>
       <c r="AF198" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -10663,11 +12229,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team X。</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
           <t>SNH48,Team X</t>
         </is>
       </c>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 朱虹蓉</t>
@@ -10678,11 +12247,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10342&amp;gid=10</t>
         </is>
       </c>
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr"/>
+      <c r="P199" t="inlineStr"/>
+      <c r="Q199" t="inlineStr"/>
+      <c r="R199" t="inlineStr"/>
+      <c r="S199" t="inlineStr"/>
+      <c r="T199" t="inlineStr"/>
+      <c r="U199" t="inlineStr"/>
+      <c r="V199" t="inlineStr"/>
+      <c r="W199" t="inlineStr"/>
+      <c r="X199" t="inlineStr"/>
+      <c r="Y199" t="inlineStr"/>
+      <c r="Z199" t="inlineStr"/>
+      <c r="AA199" t="inlineStr"/>
+      <c r="AB199" t="inlineStr"/>
+      <c r="AC199" t="inlineStr"/>
+      <c r="AD199" t="inlineStr"/>
+      <c r="AE199" t="inlineStr"/>
       <c r="AF199" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -10716,11 +12304,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team X。</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
           <t>SNH48,Team X</t>
         </is>
       </c>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 朱瑞缘</t>
@@ -10731,11 +12322,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10343&amp;gid=10</t>
         </is>
       </c>
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr"/>
+      <c r="P200" t="inlineStr"/>
+      <c r="Q200" t="inlineStr"/>
+      <c r="R200" t="inlineStr"/>
+      <c r="S200" t="inlineStr"/>
+      <c r="T200" t="inlineStr"/>
+      <c r="U200" t="inlineStr"/>
+      <c r="V200" t="inlineStr"/>
+      <c r="W200" t="inlineStr"/>
+      <c r="X200" t="inlineStr"/>
+      <c r="Y200" t="inlineStr"/>
+      <c r="Z200" t="inlineStr"/>
+      <c r="AA200" t="inlineStr"/>
+      <c r="AB200" t="inlineStr"/>
+      <c r="AC200" t="inlineStr"/>
+      <c r="AD200" t="inlineStr"/>
+      <c r="AE200" t="inlineStr"/>
       <c r="AF200" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -10769,11 +12379,14 @@
           <t>SNH48（上海）女子偶像组合成员，所属 Team X。</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
           <t>SNH48,Team X</t>
         </is>
       </c>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 曾昕妍</t>
@@ -10784,11 +12397,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10360&amp;gid=10</t>
         </is>
       </c>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr"/>
+      <c r="P201" t="inlineStr"/>
+      <c r="Q201" t="inlineStr"/>
+      <c r="R201" t="inlineStr"/>
+      <c r="S201" t="inlineStr"/>
+      <c r="T201" t="inlineStr"/>
+      <c r="U201" t="inlineStr"/>
+      <c r="V201" t="inlineStr"/>
+      <c r="W201" t="inlineStr"/>
+      <c r="X201" t="inlineStr"/>
+      <c r="Y201" t="inlineStr"/>
+      <c r="Z201" t="inlineStr"/>
+      <c r="AA201" t="inlineStr"/>
+      <c r="AB201" t="inlineStr"/>
+      <c r="AC201" t="inlineStr"/>
+      <c r="AD201" t="inlineStr"/>
+      <c r="AE201" t="inlineStr"/>
       <c r="AF201" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -10822,11 +12454,14 @@
           <t>SNH48（上海）女子偶像组合预备生（练习生）。</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr">
         <is>
           <t>SNH48,预备生</t>
         </is>
       </c>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 丁小凡</t>
@@ -10837,11 +12472,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10362&amp;gid=10</t>
         </is>
       </c>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr"/>
+      <c r="P202" t="inlineStr"/>
+      <c r="Q202" t="inlineStr"/>
+      <c r="R202" t="inlineStr"/>
+      <c r="S202" t="inlineStr"/>
+      <c r="T202" t="inlineStr"/>
+      <c r="U202" t="inlineStr"/>
+      <c r="V202" t="inlineStr"/>
+      <c r="W202" t="inlineStr"/>
+      <c r="X202" t="inlineStr"/>
+      <c r="Y202" t="inlineStr"/>
+      <c r="Z202" t="inlineStr"/>
+      <c r="AA202" t="inlineStr"/>
+      <c r="AB202" t="inlineStr"/>
+      <c r="AC202" t="inlineStr"/>
+      <c r="AD202" t="inlineStr"/>
+      <c r="AE202" t="inlineStr"/>
       <c r="AF202" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -10875,11 +12529,14 @@
           <t>SNH48（上海）女子偶像组合预备生（练习生）。</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr">
         <is>
           <t>SNH48,预备生</t>
         </is>
       </c>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 何蔡娴</t>
@@ -10890,11 +12547,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10378&amp;gid=10</t>
         </is>
       </c>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr"/>
+      <c r="P203" t="inlineStr"/>
+      <c r="Q203" t="inlineStr"/>
+      <c r="R203" t="inlineStr"/>
+      <c r="S203" t="inlineStr"/>
+      <c r="T203" t="inlineStr"/>
+      <c r="U203" t="inlineStr"/>
+      <c r="V203" t="inlineStr"/>
+      <c r="W203" t="inlineStr"/>
+      <c r="X203" t="inlineStr"/>
+      <c r="Y203" t="inlineStr"/>
+      <c r="Z203" t="inlineStr"/>
+      <c r="AA203" t="inlineStr"/>
+      <c r="AB203" t="inlineStr"/>
+      <c r="AC203" t="inlineStr"/>
+      <c r="AD203" t="inlineStr"/>
+      <c r="AE203" t="inlineStr"/>
       <c r="AF203" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -10928,11 +12604,14 @@
           <t>SNH48（上海）女子偶像组合预备生（练习生）。</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr">
         <is>
           <t>SNH48,预备生</t>
         </is>
       </c>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 何绮多</t>
@@ -10943,11 +12622,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10363&amp;gid=10</t>
         </is>
       </c>
+      <c r="N204" t="inlineStr"/>
+      <c r="O204" t="inlineStr"/>
+      <c r="P204" t="inlineStr"/>
+      <c r="Q204" t="inlineStr"/>
+      <c r="R204" t="inlineStr"/>
+      <c r="S204" t="inlineStr"/>
+      <c r="T204" t="inlineStr"/>
+      <c r="U204" t="inlineStr"/>
+      <c r="V204" t="inlineStr"/>
+      <c r="W204" t="inlineStr"/>
+      <c r="X204" t="inlineStr"/>
+      <c r="Y204" t="inlineStr"/>
+      <c r="Z204" t="inlineStr"/>
+      <c r="AA204" t="inlineStr"/>
+      <c r="AB204" t="inlineStr"/>
+      <c r="AC204" t="inlineStr"/>
+      <c r="AD204" t="inlineStr"/>
+      <c r="AE204" t="inlineStr"/>
       <c r="AF204" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -10981,11 +12679,14 @@
           <t>SNH48（上海）女子偶像组合预备生（练习生）。</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr">
         <is>
           <t>SNH48,预备生</t>
         </is>
       </c>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 韩云伊</t>
@@ -10996,11 +12697,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10361&amp;gid=10</t>
         </is>
       </c>
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr"/>
+      <c r="P205" t="inlineStr"/>
+      <c r="Q205" t="inlineStr"/>
+      <c r="R205" t="inlineStr"/>
+      <c r="S205" t="inlineStr"/>
+      <c r="T205" t="inlineStr"/>
+      <c r="U205" t="inlineStr"/>
+      <c r="V205" t="inlineStr"/>
+      <c r="W205" t="inlineStr"/>
+      <c r="X205" t="inlineStr"/>
+      <c r="Y205" t="inlineStr"/>
+      <c r="Z205" t="inlineStr"/>
+      <c r="AA205" t="inlineStr"/>
+      <c r="AB205" t="inlineStr"/>
+      <c r="AC205" t="inlineStr"/>
+      <c r="AD205" t="inlineStr"/>
+      <c r="AE205" t="inlineStr"/>
       <c r="AF205" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -11034,11 +12754,14 @@
           <t>SNH48（上海）女子偶像组合预备生（练习生）。</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr">
         <is>
           <t>SNH48,预备生</t>
         </is>
       </c>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 黄子珊</t>
@@ -11049,11 +12772,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10364&amp;gid=10</t>
         </is>
       </c>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr"/>
+      <c r="P206" t="inlineStr"/>
+      <c r="Q206" t="inlineStr"/>
+      <c r="R206" t="inlineStr"/>
+      <c r="S206" t="inlineStr"/>
+      <c r="T206" t="inlineStr"/>
+      <c r="U206" t="inlineStr"/>
+      <c r="V206" t="inlineStr"/>
+      <c r="W206" t="inlineStr"/>
+      <c r="X206" t="inlineStr"/>
+      <c r="Y206" t="inlineStr"/>
+      <c r="Z206" t="inlineStr"/>
+      <c r="AA206" t="inlineStr"/>
+      <c r="AB206" t="inlineStr"/>
+      <c r="AC206" t="inlineStr"/>
+      <c r="AD206" t="inlineStr"/>
+      <c r="AE206" t="inlineStr"/>
       <c r="AF206" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -11087,11 +12829,14 @@
           <t>SNH48（上海）女子偶像组合预备生（练习生）。</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr">
         <is>
           <t>SNH48,预备生</t>
         </is>
       </c>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 黄子欣</t>
@@ -11102,11 +12847,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10346&amp;gid=10</t>
         </is>
       </c>
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr"/>
+      <c r="P207" t="inlineStr"/>
+      <c r="Q207" t="inlineStr"/>
+      <c r="R207" t="inlineStr"/>
+      <c r="S207" t="inlineStr"/>
+      <c r="T207" t="inlineStr"/>
+      <c r="U207" t="inlineStr"/>
+      <c r="V207" t="inlineStr"/>
+      <c r="W207" t="inlineStr"/>
+      <c r="X207" t="inlineStr"/>
+      <c r="Y207" t="inlineStr"/>
+      <c r="Z207" t="inlineStr"/>
+      <c r="AA207" t="inlineStr"/>
+      <c r="AB207" t="inlineStr"/>
+      <c r="AC207" t="inlineStr"/>
+      <c r="AD207" t="inlineStr"/>
+      <c r="AE207" t="inlineStr"/>
       <c r="AF207" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -11140,11 +12904,14 @@
           <t>SNH48（上海）女子偶像组合预备生（练习生）。</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr">
         <is>
           <t>SNH48,预备生</t>
         </is>
       </c>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 黄紫怡</t>
@@ -11155,11 +12922,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10323&amp;gid=10</t>
         </is>
       </c>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr"/>
+      <c r="P208" t="inlineStr"/>
+      <c r="Q208" t="inlineStr"/>
+      <c r="R208" t="inlineStr"/>
+      <c r="S208" t="inlineStr"/>
+      <c r="T208" t="inlineStr"/>
+      <c r="U208" t="inlineStr"/>
+      <c r="V208" t="inlineStr"/>
+      <c r="W208" t="inlineStr"/>
+      <c r="X208" t="inlineStr"/>
+      <c r="Y208" t="inlineStr"/>
+      <c r="Z208" t="inlineStr"/>
+      <c r="AA208" t="inlineStr"/>
+      <c r="AB208" t="inlineStr"/>
+      <c r="AC208" t="inlineStr"/>
+      <c r="AD208" t="inlineStr"/>
+      <c r="AE208" t="inlineStr"/>
       <c r="AF208" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -11193,11 +12979,14 @@
           <t>SNH48（上海）女子偶像组合预备生（练习生）。</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr">
         <is>
           <t>SNH48,预备生</t>
         </is>
       </c>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 吉雅楠</t>
@@ -11208,11 +12997,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10365&amp;gid=10</t>
         </is>
       </c>
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr"/>
+      <c r="P209" t="inlineStr"/>
+      <c r="Q209" t="inlineStr"/>
+      <c r="R209" t="inlineStr"/>
+      <c r="S209" t="inlineStr"/>
+      <c r="T209" t="inlineStr"/>
+      <c r="U209" t="inlineStr"/>
+      <c r="V209" t="inlineStr"/>
+      <c r="W209" t="inlineStr"/>
+      <c r="X209" t="inlineStr"/>
+      <c r="Y209" t="inlineStr"/>
+      <c r="Z209" t="inlineStr"/>
+      <c r="AA209" t="inlineStr"/>
+      <c r="AB209" t="inlineStr"/>
+      <c r="AC209" t="inlineStr"/>
+      <c r="AD209" t="inlineStr"/>
+      <c r="AE209" t="inlineStr"/>
       <c r="AF209" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -11246,11 +13054,14 @@
           <t>SNH48（上海）女子偶像组合预备生（练习生）。</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr">
         <is>
           <t>SNH48,预备生</t>
         </is>
       </c>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 李沁洁</t>
@@ -11261,11 +13072,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10366&amp;gid=10</t>
         </is>
       </c>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr"/>
+      <c r="P210" t="inlineStr"/>
+      <c r="Q210" t="inlineStr"/>
+      <c r="R210" t="inlineStr"/>
+      <c r="S210" t="inlineStr"/>
+      <c r="T210" t="inlineStr"/>
+      <c r="U210" t="inlineStr"/>
+      <c r="V210" t="inlineStr"/>
+      <c r="W210" t="inlineStr"/>
+      <c r="X210" t="inlineStr"/>
+      <c r="Y210" t="inlineStr"/>
+      <c r="Z210" t="inlineStr"/>
+      <c r="AA210" t="inlineStr"/>
+      <c r="AB210" t="inlineStr"/>
+      <c r="AC210" t="inlineStr"/>
+      <c r="AD210" t="inlineStr"/>
+      <c r="AE210" t="inlineStr"/>
       <c r="AF210" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -11299,11 +13129,14 @@
           <t>SNH48（上海）女子偶像组合预备生（练习生）。</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr">
         <is>
           <t>SNH48,预备生</t>
         </is>
       </c>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 李子忻</t>
@@ -11314,11 +13147,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10315&amp;gid=10</t>
         </is>
       </c>
+      <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr"/>
+      <c r="P211" t="inlineStr"/>
+      <c r="Q211" t="inlineStr"/>
+      <c r="R211" t="inlineStr"/>
+      <c r="S211" t="inlineStr"/>
+      <c r="T211" t="inlineStr"/>
+      <c r="U211" t="inlineStr"/>
+      <c r="V211" t="inlineStr"/>
+      <c r="W211" t="inlineStr"/>
+      <c r="X211" t="inlineStr"/>
+      <c r="Y211" t="inlineStr"/>
+      <c r="Z211" t="inlineStr"/>
+      <c r="AA211" t="inlineStr"/>
+      <c r="AB211" t="inlineStr"/>
+      <c r="AC211" t="inlineStr"/>
+      <c r="AD211" t="inlineStr"/>
+      <c r="AE211" t="inlineStr"/>
       <c r="AF211" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -11352,11 +13204,14 @@
           <t>SNH48（上海）女子偶像组合预备生（练习生）。</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr">
         <is>
           <t>SNH48,预备生</t>
         </is>
       </c>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 谭思慧</t>
@@ -11367,11 +13222,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10341&amp;gid=10</t>
         </is>
       </c>
+      <c r="N212" t="inlineStr"/>
+      <c r="O212" t="inlineStr"/>
+      <c r="P212" t="inlineStr"/>
+      <c r="Q212" t="inlineStr"/>
+      <c r="R212" t="inlineStr"/>
+      <c r="S212" t="inlineStr"/>
+      <c r="T212" t="inlineStr"/>
+      <c r="U212" t="inlineStr"/>
+      <c r="V212" t="inlineStr"/>
+      <c r="W212" t="inlineStr"/>
+      <c r="X212" t="inlineStr"/>
+      <c r="Y212" t="inlineStr"/>
+      <c r="Z212" t="inlineStr"/>
+      <c r="AA212" t="inlineStr"/>
+      <c r="AB212" t="inlineStr"/>
+      <c r="AC212" t="inlineStr"/>
+      <c r="AD212" t="inlineStr"/>
+      <c r="AE212" t="inlineStr"/>
       <c r="AF212" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -11405,11 +13279,14 @@
           <t>SNH48（上海）女子偶像组合预备生（练习生）。</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr">
         <is>
           <t>SNH48,预备生</t>
         </is>
       </c>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 武博涵</t>
@@ -11420,11 +13297,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10260&amp;gid=10</t>
         </is>
       </c>
+      <c r="N213" t="inlineStr"/>
+      <c r="O213" t="inlineStr"/>
+      <c r="P213" t="inlineStr"/>
+      <c r="Q213" t="inlineStr"/>
+      <c r="R213" t="inlineStr"/>
+      <c r="S213" t="inlineStr"/>
+      <c r="T213" t="inlineStr"/>
+      <c r="U213" t="inlineStr"/>
+      <c r="V213" t="inlineStr"/>
+      <c r="W213" t="inlineStr"/>
+      <c r="X213" t="inlineStr"/>
+      <c r="Y213" t="inlineStr"/>
+      <c r="Z213" t="inlineStr"/>
+      <c r="AA213" t="inlineStr"/>
+      <c r="AB213" t="inlineStr"/>
+      <c r="AC213" t="inlineStr"/>
+      <c r="AD213" t="inlineStr"/>
+      <c r="AE213" t="inlineStr"/>
       <c r="AF213" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -11458,11 +13354,14 @@
           <t>SNH48（上海）女子偶像组合预备生（练习生）。</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr"/>
       <c r="I214" t="inlineStr">
         <is>
           <t>SNH48,预备生</t>
         </is>
       </c>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 徐诗琪</t>
@@ -11473,11 +13372,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10167&amp;gid=10</t>
         </is>
       </c>
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr"/>
+      <c r="P214" t="inlineStr"/>
+      <c r="Q214" t="inlineStr"/>
+      <c r="R214" t="inlineStr"/>
+      <c r="S214" t="inlineStr"/>
+      <c r="T214" t="inlineStr"/>
+      <c r="U214" t="inlineStr"/>
+      <c r="V214" t="inlineStr"/>
+      <c r="W214" t="inlineStr"/>
+      <c r="X214" t="inlineStr"/>
+      <c r="Y214" t="inlineStr"/>
+      <c r="Z214" t="inlineStr"/>
+      <c r="AA214" t="inlineStr"/>
+      <c r="AB214" t="inlineStr"/>
+      <c r="AC214" t="inlineStr"/>
+      <c r="AD214" t="inlineStr"/>
+      <c r="AE214" t="inlineStr"/>
       <c r="AF214" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -11511,11 +13429,14 @@
           <t>SNH48（上海）女子偶像组合预备生（练习生）。</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr">
         <is>
           <t>SNH48,预备生</t>
         </is>
       </c>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 杨宝君</t>
@@ -11526,11 +13447,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10369&amp;gid=10</t>
         </is>
       </c>
+      <c r="N215" t="inlineStr"/>
+      <c r="O215" t="inlineStr"/>
+      <c r="P215" t="inlineStr"/>
+      <c r="Q215" t="inlineStr"/>
+      <c r="R215" t="inlineStr"/>
+      <c r="S215" t="inlineStr"/>
+      <c r="T215" t="inlineStr"/>
+      <c r="U215" t="inlineStr"/>
+      <c r="V215" t="inlineStr"/>
+      <c r="W215" t="inlineStr"/>
+      <c r="X215" t="inlineStr"/>
+      <c r="Y215" t="inlineStr"/>
+      <c r="Z215" t="inlineStr"/>
+      <c r="AA215" t="inlineStr"/>
+      <c r="AB215" t="inlineStr"/>
+      <c r="AC215" t="inlineStr"/>
+      <c r="AD215" t="inlineStr"/>
+      <c r="AE215" t="inlineStr"/>
       <c r="AF215" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -11564,11 +13504,14 @@
           <t>SNH48（上海）女子偶像组合预备生（练习生）。</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr">
         <is>
           <t>SNH48,预备生</t>
         </is>
       </c>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr">
         <is>
           <t>SNH48 官方主页 - 左婧媛</t>
@@ -11579,11 +13522,30 @@
           <t>https://www.snh48.com/mobile/member-detail.html?sid=10273&amp;gid=10</t>
         </is>
       </c>
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr"/>
+      <c r="P216" t="inlineStr"/>
+      <c r="Q216" t="inlineStr"/>
+      <c r="R216" t="inlineStr"/>
+      <c r="S216" t="inlineStr"/>
+      <c r="T216" t="inlineStr"/>
+      <c r="U216" t="inlineStr"/>
+      <c r="V216" t="inlineStr"/>
+      <c r="W216" t="inlineStr"/>
+      <c r="X216" t="inlineStr"/>
+      <c r="Y216" t="inlineStr"/>
+      <c r="Z216" t="inlineStr"/>
+      <c r="AA216" t="inlineStr"/>
+      <c r="AB216" t="inlineStr"/>
+      <c r="AC216" t="inlineStr"/>
+      <c r="AD216" t="inlineStr"/>
+      <c r="AE216" t="inlineStr"/>
       <c r="AF216" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="AG216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">

--- a/xlsx/cards.unified.xlsx
+++ b/xlsx/cards.unified.xlsx
@@ -7277,7 +7277,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://bkimg.cdn.bcebos.com/pic/aa18972bd40735fae6cd8d304d0618b30f2443a7a2b8?x-bce-process=image/format,f_auto/quality,Q_70/resize,m_lfit,limit_1,w_536</t>
+          <t>./assets/images/芦馨怡.webp</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">

--- a/xlsx/cards.unified.xlsx
+++ b/xlsx/cards.unified.xlsx
@@ -7277,7 +7277,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>./assets/images/芦馨怡.webp</t>
+          <t>https://zhengxie.info/topics/snh48/assets/images/芦馨怡.webp</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">

--- a/xlsx/cards.unified.xlsx
+++ b/xlsx/cards.unified.xlsx
@@ -13560,7 +13560,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>全国政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E217" t="n">
@@ -14175,7 +14175,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E227" t="n">
@@ -14235,7 +14235,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E228" t="n">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E229" t="n">
@@ -14355,7 +14355,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E230" t="n">
@@ -14415,7 +14415,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E231" t="n">
@@ -14480,7 +14480,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E232" t="n">
@@ -14540,7 +14540,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E233" t="n">
@@ -14600,7 +14600,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E234" t="n">
@@ -14660,7 +14660,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E235" t="n">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E236" t="n">
@@ -14780,7 +14780,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E237" t="n">
@@ -14840,7 +14840,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E238" t="n">
@@ -14900,7 +14900,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E239" t="n">
@@ -14960,7 +14960,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E240" t="n">
@@ -15020,7 +15020,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E241" t="n">
@@ -15080,7 +15080,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E242" t="n">
@@ -15145,7 +15145,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E243" t="n">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E244" t="n">
@@ -15270,7 +15270,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E245" t="n">
@@ -15330,7 +15330,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E246" t="n">
@@ -15390,7 +15390,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E247" t="n">
@@ -15450,7 +15450,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E248" t="n">
@@ -15510,7 +15510,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E249" t="n">
@@ -15570,7 +15570,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E250" t="n">
@@ -15630,7 +15630,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E251" t="n">
@@ -15690,7 +15690,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E252" t="n">
@@ -15750,7 +15750,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E253" t="n">
@@ -15810,7 +15810,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E254" t="n">
@@ -15870,7 +15870,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E255" t="n">
@@ -15930,7 +15930,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E256" t="n">
@@ -15990,7 +15990,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>省级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E257" t="n">
@@ -16086,10 +16086,8 @@
           <t>https://www.gzzx.gov.cn</t>
         </is>
       </c>
-      <c r="AF258" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF258" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="259">
@@ -16136,10 +16134,8 @@
           <t>https://www.szzx.gov.cn/</t>
         </is>
       </c>
-      <c r="AF259" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF259" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="260">
@@ -16186,10 +16182,8 @@
           <t>https://www.zhzx.gov.cn/</t>
         </is>
       </c>
-      <c r="AF260" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF260" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="261">
@@ -16236,10 +16230,8 @@
           <t>https://stzx.shantou.gov.cn/</t>
         </is>
       </c>
-      <c r="AF261" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF261" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="262">
@@ -16291,10 +16283,8 @@
           <t>https://www.jpzx.gov.cn/welcome</t>
         </is>
       </c>
-      <c r="AF262" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF262" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="263">
@@ -16341,10 +16331,8 @@
           <t>https://www.fszx.gov.cn/</t>
         </is>
       </c>
-      <c r="AF263" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF263" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="264">
@@ -16391,10 +16379,8 @@
           <t>https://www.sgzxb.gov.cn/</t>
         </is>
       </c>
-      <c r="AF264" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF264" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="265">
@@ -16441,10 +16427,8 @@
           <t>https://www.gdhyzx.gov.cn/hyzx/index.html</t>
         </is>
       </c>
-      <c r="AF265" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF265" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="266">
@@ -16491,10 +16475,8 @@
           <t>https://www.mzzx.gov.cn/</t>
         </is>
       </c>
-      <c r="AF266" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF266" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="267">
@@ -16541,10 +16523,8 @@
           <t>https://zx.huizhou.gov.cn/</t>
         </is>
       </c>
-      <c r="AF267" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF267" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="268">
@@ -16591,10 +16571,8 @@
           <t>https://www.swzx.gov.cn/</t>
         </is>
       </c>
-      <c r="AF268" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF268" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="269">
@@ -16641,10 +16619,8 @@
           <t>https://dgzx.dg.gov.cn/</t>
         </is>
       </c>
-      <c r="AF269" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF269" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="270">
@@ -16691,10 +16667,8 @@
           <t>https://zszx.zsnews.cn/</t>
         </is>
       </c>
-      <c r="AF270" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF270" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="271">
@@ -16741,10 +16715,8 @@
           <t>https://zx.jiangmen.cn/</t>
         </is>
       </c>
-      <c r="AF271" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF271" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="272">
@@ -16791,10 +16763,8 @@
           <t>https://www.yjszx.gov.cn/default.html</t>
         </is>
       </c>
-      <c r="AF272" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF272" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="273">
@@ -16846,10 +16816,8 @@
           <t>https://www.gdzjzx.gov.cn/</t>
         </is>
       </c>
-      <c r="AF273" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF273" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="274">
@@ -16896,10 +16864,8 @@
           <t>https://zx.maoming.gov.cn/website/main/jsp/index.jsp</t>
         </is>
       </c>
-      <c r="AF274" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF274" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -16946,10 +16912,8 @@
           <t>https://zqzx.gov.cn/index.html</t>
         </is>
       </c>
-      <c r="AF275" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF275" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="276">
@@ -16996,10 +16960,8 @@
           <t>https://czzx.gov.cn/</t>
         </is>
       </c>
-      <c r="AF276" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF276" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="277">
@@ -17046,10 +17008,8 @@
           <t xml:space="preserve">https://www.jieyangzhengxie.gov.cn/ </t>
         </is>
       </c>
-      <c r="AF277" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF277" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="278">
@@ -17096,10 +17056,8 @@
           <t>https://zx.yunfu.gov.cn/</t>
         </is>
       </c>
-      <c r="AF278" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF278" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="279">
@@ -17146,10 +17104,8 @@
           <t>https://www.hrbzx.gov.cn/</t>
         </is>
       </c>
-      <c r="AF279" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF279" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="280">
@@ -17196,10 +17152,8 @@
           <t xml:space="preserve">https://www.whzx.org.cn/  </t>
         </is>
       </c>
-      <c r="AF280" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF280" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="281">
@@ -17261,10 +17215,8 @@
           <t>https://www.12377.cn/jgjj.html?tab=5</t>
         </is>
       </c>
-      <c r="AF281" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF281" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="282">
@@ -17326,10 +17278,8 @@
           <t>https://www.12321.cn/single?tpl=institution</t>
         </is>
       </c>
-      <c r="AF282" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF282" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="283">
@@ -17361,10 +17311,8 @@
           <t>副省级政协,沈阳市,市政协,辽宁省,省会城市</t>
         </is>
       </c>
-      <c r="AF283" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF283" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="284">
@@ -17396,10 +17344,8 @@
           <t>副省级政协,成都市,市政协,四川省,省会城市</t>
         </is>
       </c>
-      <c r="AF284" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF284" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="285">
@@ -17431,10 +17377,8 @@
           <t>副省级政协,南京市,市政协,江苏省,省会城市</t>
         </is>
       </c>
-      <c r="AF285" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF285" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="286">
@@ -17466,10 +17410,8 @@
           <t>副省级政协,西安市,市政协,陕西省,省会城市</t>
         </is>
       </c>
-      <c r="AF286" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF286" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="287">
@@ -17501,10 +17443,8 @@
           <t>副省级政协,长春市,市政协,吉林省,省会城市</t>
         </is>
       </c>
-      <c r="AF287" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF287" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="288">
@@ -17536,10 +17476,8 @@
           <t>副省级政协,济南市,市政协,山东省,省会城市</t>
         </is>
       </c>
-      <c r="AF288" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF288" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="289">
@@ -17571,10 +17509,8 @@
           <t>副省级政协,杭州市,市政协,浙江省,省会城市</t>
         </is>
       </c>
-      <c r="AF289" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF289" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="290">
@@ -17606,10 +17542,8 @@
           <t>副省级政协,大连市,市政协,辽宁省,计划单列市</t>
         </is>
       </c>
-      <c r="AF290" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF290" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="291">
@@ -17641,10 +17575,8 @@
           <t>副省级政协,青岛市,市政协,山东省,计划单列市</t>
         </is>
       </c>
-      <c r="AF291" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF291" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="292">
@@ -17676,10 +17608,8 @@
           <t>副省级政协,厦门市,市政协,福建省,计划单列市</t>
         </is>
       </c>
-      <c r="AF292" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF292" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="293">
@@ -17711,10 +17641,8 @@
           <t>副省级政协,宁波市,市政协,浙江省,计划单列市</t>
         </is>
       </c>
-      <c r="AF293" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF293" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="294">
@@ -17746,10 +17674,8 @@
           <t>地级政协,清远市,市政协,广东省</t>
         </is>
       </c>
-      <c r="AF294" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF294" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="295">
@@ -17781,10 +17707,8 @@
           <t>地级政协,石家庄市,市政协,河北省</t>
         </is>
       </c>
-      <c r="AF295" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF295" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="296">
@@ -17816,10 +17740,8 @@
           <t>地级政协,唐山市,市政协,河北省</t>
         </is>
       </c>
-      <c r="AF296" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF296" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="297">
@@ -17851,10 +17773,8 @@
           <t>地级政协,秦皇岛市,市政协,河北省</t>
         </is>
       </c>
-      <c r="AF297" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF297" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="298">
@@ -17886,10 +17806,8 @@
           <t>地级政协,邯郸市,市政协,河北省</t>
         </is>
       </c>
-      <c r="AF298" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF298" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="299">
@@ -17921,10 +17839,8 @@
           <t>地级政协,邢台市,市政协,河北省</t>
         </is>
       </c>
-      <c r="AF299" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF299" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="300">
@@ -17956,10 +17872,8 @@
           <t>地级政协,保定市,市政协,河北省</t>
         </is>
       </c>
-      <c r="AF300" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF300" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="301">
@@ -17991,10 +17905,8 @@
           <t>地级政协,张家口市,市政协,河北省</t>
         </is>
       </c>
-      <c r="AF301" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF301" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="302">
@@ -18026,10 +17938,8 @@
           <t>地级政协,承德市,市政协,河北省</t>
         </is>
       </c>
-      <c r="AF302" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF302" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="303">
@@ -18061,10 +17971,8 @@
           <t>地级政协,沧州市,市政协,河北省</t>
         </is>
       </c>
-      <c r="AF303" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF303" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="304">
@@ -18096,10 +18004,8 @@
           <t>地级政协,廊坊市,市政协,河北省</t>
         </is>
       </c>
-      <c r="AF304" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF304" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="305">
@@ -18131,10 +18037,8 @@
           <t>地级政协,衡水市,市政协,河北省</t>
         </is>
       </c>
-      <c r="AF305" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF305" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="306">
@@ -18166,10 +18070,8 @@
           <t>地级政协,太原市,市政协,山西省</t>
         </is>
       </c>
-      <c r="AF306" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF306" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="307">
@@ -18201,10 +18103,8 @@
           <t>地级政协,大同市,市政协,山西省</t>
         </is>
       </c>
-      <c r="AF307" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF307" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="308">
@@ -18236,10 +18136,8 @@
           <t>地级政协,阳泉市,市政协,山西省</t>
         </is>
       </c>
-      <c r="AF308" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF308" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="309">
@@ -18271,10 +18169,8 @@
           <t>地级政协,长治市,市政协,山西省</t>
         </is>
       </c>
-      <c r="AF309" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF309" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="310">
@@ -18306,10 +18202,8 @@
           <t>地级政协,晋城市,市政协,山西省</t>
         </is>
       </c>
-      <c r="AF310" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF310" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="311">
@@ -18341,10 +18235,8 @@
           <t>地级政协,朔州市,市政协,山西省</t>
         </is>
       </c>
-      <c r="AF311" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF311" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="312">
@@ -18376,10 +18268,8 @@
           <t>地级政协,晋中市,市政协,山西省</t>
         </is>
       </c>
-      <c r="AF312" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF312" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="313">
@@ -18411,10 +18301,8 @@
           <t>地级政协,运城市,市政协,山西省</t>
         </is>
       </c>
-      <c r="AF313" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF313" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="314">
@@ -18446,10 +18334,8 @@
           <t>地级政协,忻州市,市政协,山西省</t>
         </is>
       </c>
-      <c r="AF314" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF314" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="315">
@@ -18481,10 +18367,8 @@
           <t>地级政协,临汾市,市政协,山西省</t>
         </is>
       </c>
-      <c r="AF315" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF315" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="316">
@@ -18516,10 +18400,8 @@
           <t>地级政协,吕梁市,市政协,山西省</t>
         </is>
       </c>
-      <c r="AF316" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF316" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="317">
@@ -18551,10 +18433,8 @@
           <t>地级政协,呼和浩特市,市政协,内蒙古自治区</t>
         </is>
       </c>
-      <c r="AF317" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF317" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="318">
@@ -18586,10 +18466,8 @@
           <t>地级政协,包头市,市政协,内蒙古自治区</t>
         </is>
       </c>
-      <c r="AF318" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF318" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="319">
@@ -18621,10 +18499,8 @@
           <t>地级政协,乌海市,市政协,内蒙古自治区</t>
         </is>
       </c>
-      <c r="AF319" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF319" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="320">
@@ -18656,10 +18532,8 @@
           <t>地级政协,赤峰市,市政协,内蒙古自治区</t>
         </is>
       </c>
-      <c r="AF320" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF320" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="321">
@@ -18691,10 +18565,8 @@
           <t>地级政协,通辽市,市政协,内蒙古自治区</t>
         </is>
       </c>
-      <c r="AF321" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF321" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="322">
@@ -18726,10 +18598,8 @@
           <t>地级政协,鄂尔多斯市,市政协,内蒙古自治区</t>
         </is>
       </c>
-      <c r="AF322" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF322" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="323">
@@ -18761,10 +18631,8 @@
           <t>地级政协,呼伦贝尔市,市政协,内蒙古自治区</t>
         </is>
       </c>
-      <c r="AF323" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF323" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="324">
@@ -18796,10 +18664,8 @@
           <t>地级政协,巴彦淖尔市,市政协,内蒙古自治区</t>
         </is>
       </c>
-      <c r="AF324" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF324" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="325">
@@ -18831,10 +18697,8 @@
           <t>地级政协,乌兰察布市,市政协,内蒙古自治区</t>
         </is>
       </c>
-      <c r="AF325" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF325" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="326">
@@ -18866,10 +18730,8 @@
           <t>地级政协,鞍山市,市政协,辽宁省</t>
         </is>
       </c>
-      <c r="AF326" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF326" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="327">
@@ -18901,10 +18763,8 @@
           <t>地级政协,抚顺市,市政协,辽宁省</t>
         </is>
       </c>
-      <c r="AF327" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF327" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="328">
@@ -18936,10 +18796,8 @@
           <t>地级政协,本溪市,市政协,辽宁省</t>
         </is>
       </c>
-      <c r="AF328" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF328" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="329">
@@ -18971,10 +18829,8 @@
           <t>地级政协,丹东市,市政协,辽宁省</t>
         </is>
       </c>
-      <c r="AF329" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF329" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="330">
@@ -19006,10 +18862,8 @@
           <t>地级政协,锦州市,市政协,辽宁省</t>
         </is>
       </c>
-      <c r="AF330" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF330" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="331">
@@ -19041,10 +18895,8 @@
           <t>地级政协,营口市,市政协,辽宁省</t>
         </is>
       </c>
-      <c r="AF331" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF331" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="332">
@@ -19076,10 +18928,8 @@
           <t>地级政协,阜新市,市政协,辽宁省</t>
         </is>
       </c>
-      <c r="AF332" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF332" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="333">
@@ -19111,10 +18961,8 @@
           <t>地级政协,辽阳市,市政协,辽宁省</t>
         </is>
       </c>
-      <c r="AF333" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF333" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="334">
@@ -19146,10 +18994,8 @@
           <t>地级政协,盘锦市,市政协,辽宁省</t>
         </is>
       </c>
-      <c r="AF334" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF334" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="335">
@@ -19181,10 +19027,8 @@
           <t>地级政协,铁岭市,市政协,辽宁省</t>
         </is>
       </c>
-      <c r="AF335" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF335" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="336">
@@ -19216,10 +19060,8 @@
           <t>地级政协,朝阳市,市政协,辽宁省</t>
         </is>
       </c>
-      <c r="AF336" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF336" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="337">
@@ -19251,10 +19093,8 @@
           <t>地级政协,葫芦岛市,市政协,辽宁省</t>
         </is>
       </c>
-      <c r="AF337" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF337" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="338">
@@ -19286,10 +19126,8 @@
           <t>地级政协,吉林市,市政协,吉林省</t>
         </is>
       </c>
-      <c r="AF338" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF338" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="339">
@@ -19321,10 +19159,8 @@
           <t>地级政协,四平市,市政协,吉林省</t>
         </is>
       </c>
-      <c r="AF339" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF339" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="340">
@@ -19356,10 +19192,8 @@
           <t>地级政协,辽源市,市政协,吉林省</t>
         </is>
       </c>
-      <c r="AF340" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF340" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="341">
@@ -19391,10 +19225,8 @@
           <t>地级政协,通化市,市政协,吉林省</t>
         </is>
       </c>
-      <c r="AF341" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF341" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="342">
@@ -19426,10 +19258,8 @@
           <t>地级政协,白山市,市政协,吉林省</t>
         </is>
       </c>
-      <c r="AF342" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF342" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="343">
@@ -19461,10 +19291,8 @@
           <t>地级政协,松原市,市政协,吉林省</t>
         </is>
       </c>
-      <c r="AF343" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF343" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="344">
@@ -19496,10 +19324,8 @@
           <t>地级政协,白城市,市政协,吉林省</t>
         </is>
       </c>
-      <c r="AF344" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF344" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="345">
@@ -19531,10 +19357,8 @@
           <t>地级政协,齐齐哈尔市,市政协,黑龙江省</t>
         </is>
       </c>
-      <c r="AF345" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF345" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="346">
@@ -19566,10 +19390,8 @@
           <t>地级政协,鸡西市,市政协,黑龙江省</t>
         </is>
       </c>
-      <c r="AF346" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF346" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="347">
@@ -19601,10 +19423,8 @@
           <t>地级政协,鹤岗市,市政协,黑龙江省</t>
         </is>
       </c>
-      <c r="AF347" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF347" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="348">
@@ -19636,10 +19456,8 @@
           <t>地级政协,双鸭山市,市政协,黑龙江省</t>
         </is>
       </c>
-      <c r="AF348" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF348" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="349">
@@ -19671,10 +19489,8 @@
           <t>地级政协,大庆市,市政协,黑龙江省</t>
         </is>
       </c>
-      <c r="AF349" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF349" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="350">
@@ -19706,10 +19522,8 @@
           <t>地级政协,伊春市,市政协,黑龙江省</t>
         </is>
       </c>
-      <c r="AF350" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF350" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="351">
@@ -19741,10 +19555,8 @@
           <t>地级政协,佳木斯市,市政协,黑龙江省</t>
         </is>
       </c>
-      <c r="AF351" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF351" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="352">
@@ -19776,10 +19588,8 @@
           <t>地级政协,七台河市,市政协,黑龙江省</t>
         </is>
       </c>
-      <c r="AF352" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF352" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="353">
@@ -19811,10 +19621,8 @@
           <t>地级政协,牡丹江市,市政协,黑龙江省</t>
         </is>
       </c>
-      <c r="AF353" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF353" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="354">
@@ -19846,10 +19654,8 @@
           <t>地级政协,黑河市,市政协,黑龙江省</t>
         </is>
       </c>
-      <c r="AF354" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF354" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="355">
@@ -19881,10 +19687,8 @@
           <t>地级政协,绥化市,市政协,黑龙江省</t>
         </is>
       </c>
-      <c r="AF355" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF355" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="356">
@@ -19916,10 +19720,8 @@
           <t>地级政协,无锡市,市政协,江苏省</t>
         </is>
       </c>
-      <c r="AF356" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF356" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="357">
@@ -19951,10 +19753,8 @@
           <t>地级政协,徐州市,市政协,江苏省</t>
         </is>
       </c>
-      <c r="AF357" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF357" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="358">
@@ -19986,10 +19786,8 @@
           <t>地级政协,常州市,市政协,江苏省</t>
         </is>
       </c>
-      <c r="AF358" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF358" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="359">
@@ -20021,10 +19819,8 @@
           <t>地级政协,苏州市,市政协,江苏省</t>
         </is>
       </c>
-      <c r="AF359" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF359" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="360">
@@ -20056,10 +19852,8 @@
           <t>地级政协,南通市,市政协,江苏省</t>
         </is>
       </c>
-      <c r="AF360" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF360" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="361">
@@ -20091,10 +19885,8 @@
           <t>地级政协,连云港市,市政协,江苏省</t>
         </is>
       </c>
-      <c r="AF361" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF361" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="362">
@@ -20126,10 +19918,8 @@
           <t>地级政协,淮安市,市政协,江苏省</t>
         </is>
       </c>
-      <c r="AF362" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF362" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="363">
@@ -20161,10 +19951,8 @@
           <t>地级政协,盐城市,市政协,江苏省</t>
         </is>
       </c>
-      <c r="AF363" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF363" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="364">
@@ -20196,10 +19984,8 @@
           <t>地级政协,扬州市,市政协,江苏省</t>
         </is>
       </c>
-      <c r="AF364" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF364" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="365">
@@ -20231,10 +20017,8 @@
           <t>地级政协,镇江市,市政协,江苏省</t>
         </is>
       </c>
-      <c r="AF365" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF365" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="366">
@@ -20266,10 +20050,8 @@
           <t>地级政协,泰州市,市政协,江苏省</t>
         </is>
       </c>
-      <c r="AF366" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF366" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="367">
@@ -20301,10 +20083,8 @@
           <t>地级政协,宿迁市,市政协,江苏省</t>
         </is>
       </c>
-      <c r="AF367" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF367" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="368">
@@ -20336,10 +20116,8 @@
           <t>地级政协,温州市,市政协,浙江省</t>
         </is>
       </c>
-      <c r="AF368" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF368" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="369">
@@ -20371,10 +20149,8 @@
           <t>地级政协,嘉兴市,市政协,浙江省</t>
         </is>
       </c>
-      <c r="AF369" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF369" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="370">
@@ -20406,10 +20182,8 @@
           <t>地级政协,湖州市,市政协,浙江省</t>
         </is>
       </c>
-      <c r="AF370" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF370" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="371">
@@ -20441,10 +20215,8 @@
           <t>地级政协,绍兴市,市政协,浙江省</t>
         </is>
       </c>
-      <c r="AF371" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF371" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="372">
@@ -20476,10 +20248,8 @@
           <t>地级政协,金华市,市政协,浙江省</t>
         </is>
       </c>
-      <c r="AF372" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF372" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="373">
@@ -20511,10 +20281,8 @@
           <t>地级政协,衢州市,市政协,浙江省</t>
         </is>
       </c>
-      <c r="AF373" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF373" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="374">
@@ -20546,10 +20314,8 @@
           <t>地级政协,舟山市,市政协,浙江省</t>
         </is>
       </c>
-      <c r="AF374" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF374" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="375">
@@ -20581,10 +20347,8 @@
           <t>地级政协,台州市,市政协,浙江省</t>
         </is>
       </c>
-      <c r="AF375" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF375" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="376">
@@ -20616,10 +20380,8 @@
           <t>地级政协,丽水市,市政协,浙江省</t>
         </is>
       </c>
-      <c r="AF376" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF376" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="377">
@@ -20651,10 +20413,8 @@
           <t>地级政协,合肥市,市政协,安徽省</t>
         </is>
       </c>
-      <c r="AF377" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF377" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="378">
@@ -20686,10 +20446,8 @@
           <t>地级政协,芜湖市,市政协,安徽省</t>
         </is>
       </c>
-      <c r="AF378" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF378" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="379">
@@ -20721,10 +20479,8 @@
           <t>地级政协,蚌埠市,市政协,安徽省</t>
         </is>
       </c>
-      <c r="AF379" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF379" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="380">
@@ -20756,10 +20512,8 @@
           <t>地级政协,淮南市,市政协,安徽省</t>
         </is>
       </c>
-      <c r="AF380" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF380" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="381">
@@ -20791,10 +20545,8 @@
           <t>地级政协,马鞍山市,市政协,安徽省</t>
         </is>
       </c>
-      <c r="AF381" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF381" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="382">
@@ -20826,10 +20578,8 @@
           <t>地级政协,淮北市,市政协,安徽省</t>
         </is>
       </c>
-      <c r="AF382" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF382" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="383">
@@ -20861,10 +20611,8 @@
           <t>地级政协,铜陵市,市政协,安徽省</t>
         </is>
       </c>
-      <c r="AF383" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF383" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="384">
@@ -20896,10 +20644,8 @@
           <t>地级政协,安庆市,市政协,安徽省</t>
         </is>
       </c>
-      <c r="AF384" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF384" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="385">
@@ -20931,10 +20677,8 @@
           <t>地级政协,黄山市,市政协,安徽省</t>
         </is>
       </c>
-      <c r="AF385" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF385" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="386">
@@ -20966,10 +20710,8 @@
           <t>地级政协,滁州市,市政协,安徽省</t>
         </is>
       </c>
-      <c r="AF386" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF386" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="387">
@@ -21001,10 +20743,8 @@
           <t>地级政协,阜阳市,市政协,安徽省</t>
         </is>
       </c>
-      <c r="AF387" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF387" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="388">
@@ -21036,10 +20776,8 @@
           <t>地级政协,宿州市,市政协,安徽省</t>
         </is>
       </c>
-      <c r="AF388" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF388" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="389">
@@ -21071,10 +20809,8 @@
           <t>地级政协,六安市,市政协,安徽省</t>
         </is>
       </c>
-      <c r="AF389" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF389" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="390">
@@ -21106,10 +20842,8 @@
           <t>地级政协,亳州市,市政协,安徽省</t>
         </is>
       </c>
-      <c r="AF390" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF390" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="391">
@@ -21141,10 +20875,8 @@
           <t>地级政协,池州市,市政协,安徽省</t>
         </is>
       </c>
-      <c r="AF391" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF391" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="392">
@@ -21176,10 +20908,8 @@
           <t>地级政协,宣城市,市政协,安徽省</t>
         </is>
       </c>
-      <c r="AF392" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF392" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="393">
@@ -21211,10 +20941,8 @@
           <t>地级政协,福州市,市政协,福建省</t>
         </is>
       </c>
-      <c r="AF393" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF393" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="394">
@@ -21246,10 +20974,8 @@
           <t>地级政协,莆田市,市政协,福建省</t>
         </is>
       </c>
-      <c r="AF394" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF394" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="395">
@@ -21281,10 +21007,8 @@
           <t>地级政协,三明市,市政协,福建省</t>
         </is>
       </c>
-      <c r="AF395" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF395" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="396">
@@ -21316,10 +21040,8 @@
           <t>地级政协,泉州市,市政协,福建省</t>
         </is>
       </c>
-      <c r="AF396" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF396" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="397">
@@ -21351,10 +21073,8 @@
           <t>地级政协,漳州市,市政协,福建省</t>
         </is>
       </c>
-      <c r="AF397" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF397" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="398">
@@ -21386,10 +21106,8 @@
           <t>地级政协,南平市,市政协,福建省</t>
         </is>
       </c>
-      <c r="AF398" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF398" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="399">
@@ -21421,10 +21139,8 @@
           <t>地级政协,龙岩市,市政协,福建省</t>
         </is>
       </c>
-      <c r="AF399" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF399" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="400">
@@ -21456,10 +21172,8 @@
           <t>地级政协,宁德市,市政协,福建省</t>
         </is>
       </c>
-      <c r="AF400" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF400" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="401">
@@ -21491,10 +21205,8 @@
           <t>地级政协,南昌市,市政协,江西省</t>
         </is>
       </c>
-      <c r="AF401" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF401" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="402">
@@ -21526,10 +21238,8 @@
           <t>地级政协,景德镇市,市政协,江西省</t>
         </is>
       </c>
-      <c r="AF402" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF402" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="403">
@@ -21561,10 +21271,8 @@
           <t>地级政协,萍乡市,市政协,江西省</t>
         </is>
       </c>
-      <c r="AF403" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF403" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="404">
@@ -21596,10 +21304,8 @@
           <t>地级政协,九江市,市政协,江西省</t>
         </is>
       </c>
-      <c r="AF404" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF404" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="405">
@@ -21631,10 +21337,8 @@
           <t>地级政协,新余市,市政协,江西省</t>
         </is>
       </c>
-      <c r="AF405" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF405" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="406">
@@ -21666,10 +21370,8 @@
           <t>地级政协,鹰潭市,市政协,江西省</t>
         </is>
       </c>
-      <c r="AF406" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF406" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="407">
@@ -21701,10 +21403,8 @@
           <t>地级政协,赣州市,市政协,江西省</t>
         </is>
       </c>
-      <c r="AF407" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF407" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="408">
@@ -21736,10 +21436,8 @@
           <t>地级政协,吉安市,市政协,江西省</t>
         </is>
       </c>
-      <c r="AF408" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF408" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="409">
@@ -21771,10 +21469,8 @@
           <t>地级政协,宜春市,市政协,江西省</t>
         </is>
       </c>
-      <c r="AF409" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF409" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="410">
@@ -21806,10 +21502,8 @@
           <t>地级政协,抚州市,市政协,江西省</t>
         </is>
       </c>
-      <c r="AF410" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF410" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="411">
@@ -21841,10 +21535,8 @@
           <t>地级政协,上饶市,市政协,江西省</t>
         </is>
       </c>
-      <c r="AF411" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF411" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="412">
@@ -21876,10 +21568,8 @@
           <t>地级政协,淄博市,市政协,山东省</t>
         </is>
       </c>
-      <c r="AF412" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF412" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="413">
@@ -21911,10 +21601,8 @@
           <t>地级政协,枣庄市,市政协,山东省</t>
         </is>
       </c>
-      <c r="AF413" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF413" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="414">
@@ -21946,10 +21634,8 @@
           <t>地级政协,东营市,市政协,山东省</t>
         </is>
       </c>
-      <c r="AF414" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF414" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="415">
@@ -21981,10 +21667,8 @@
           <t>地级政协,烟台市,市政协,山东省</t>
         </is>
       </c>
-      <c r="AF415" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF415" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="416">
@@ -22016,10 +21700,8 @@
           <t>地级政协,潍坊市,市政协,山东省</t>
         </is>
       </c>
-      <c r="AF416" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF416" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="417">
@@ -22051,10 +21733,8 @@
           <t>地级政协,济宁市,市政协,山东省</t>
         </is>
       </c>
-      <c r="AF417" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF417" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="418">
@@ -22086,10 +21766,8 @@
           <t>地级政协,泰安市,市政协,山东省</t>
         </is>
       </c>
-      <c r="AF418" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF418" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="419">
@@ -22121,10 +21799,8 @@
           <t>地级政协,威海市,市政协,山东省</t>
         </is>
       </c>
-      <c r="AF419" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF419" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="420">
@@ -22156,10 +21832,8 @@
           <t>地级政协,日照市,市政协,山东省</t>
         </is>
       </c>
-      <c r="AF420" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF420" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="421">
@@ -22191,10 +21865,8 @@
           <t>地级政协,临沂市,市政协,山东省</t>
         </is>
       </c>
-      <c r="AF421" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF421" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="422">
@@ -22226,10 +21898,8 @@
           <t>地级政协,德州市,市政协,山东省</t>
         </is>
       </c>
-      <c r="AF422" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF422" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="423">
@@ -22261,10 +21931,8 @@
           <t>地级政协,聊城市,市政协,山东省</t>
         </is>
       </c>
-      <c r="AF423" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF423" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="424">
@@ -22296,10 +21964,8 @@
           <t>地级政协,滨州市,市政协,山东省</t>
         </is>
       </c>
-      <c r="AF424" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF424" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="425">
@@ -22331,10 +21997,8 @@
           <t>地级政协,菏泽市,市政协,山东省</t>
         </is>
       </c>
-      <c r="AF425" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF425" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="426">
@@ -22366,10 +22030,8 @@
           <t>地级政协,郑州市,市政协,河南省</t>
         </is>
       </c>
-      <c r="AF426" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF426" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="427">
@@ -22401,10 +22063,8 @@
           <t>地级政协,开封市,市政协,河南省</t>
         </is>
       </c>
-      <c r="AF427" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF427" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="428">
@@ -22436,10 +22096,8 @@
           <t>地级政协,洛阳市,市政协,河南省</t>
         </is>
       </c>
-      <c r="AF428" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF428" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="429">
@@ -22471,10 +22129,8 @@
           <t>地级政协,平顶山市,市政协,河南省</t>
         </is>
       </c>
-      <c r="AF429" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF429" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="430">
@@ -22506,10 +22162,8 @@
           <t>地级政协,安阳市,市政协,河南省</t>
         </is>
       </c>
-      <c r="AF430" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF430" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="431">
@@ -22541,10 +22195,8 @@
           <t>地级政协,鹤壁市,市政协,河南省</t>
         </is>
       </c>
-      <c r="AF431" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF431" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="432">
@@ -22576,10 +22228,8 @@
           <t>地级政协,新乡市,市政协,河南省</t>
         </is>
       </c>
-      <c r="AF432" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF432" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="433">
@@ -22611,10 +22261,8 @@
           <t>地级政协,焦作市,市政协,河南省</t>
         </is>
       </c>
-      <c r="AF433" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF433" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="434">
@@ -22646,10 +22294,8 @@
           <t>地级政协,濮阳市,市政协,河南省</t>
         </is>
       </c>
-      <c r="AF434" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF434" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="435">
@@ -22681,10 +22327,8 @@
           <t>地级政协,许昌市,市政协,河南省</t>
         </is>
       </c>
-      <c r="AF435" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF435" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="436">
@@ -22716,10 +22360,8 @@
           <t>地级政协,漯河市,市政协,河南省</t>
         </is>
       </c>
-      <c r="AF436" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF436" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="437">
@@ -22751,10 +22393,8 @@
           <t>地级政协,三门峡市,市政协,河南省</t>
         </is>
       </c>
-      <c r="AF437" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF437" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="438">
@@ -22786,10 +22426,8 @@
           <t>地级政协,南阳市,市政协,河南省</t>
         </is>
       </c>
-      <c r="AF438" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF438" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="439">
@@ -22821,10 +22459,8 @@
           <t>地级政协,商丘市,市政协,河南省</t>
         </is>
       </c>
-      <c r="AF439" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF439" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="440">
@@ -22856,10 +22492,8 @@
           <t>地级政协,信阳市,市政协,河南省</t>
         </is>
       </c>
-      <c r="AF440" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF440" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="441">
@@ -22891,10 +22525,8 @@
           <t>地级政协,周口市,市政协,河南省</t>
         </is>
       </c>
-      <c r="AF441" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF441" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="442">
@@ -22926,10 +22558,8 @@
           <t>地级政协,驻马店市,市政协,河南省</t>
         </is>
       </c>
-      <c r="AF442" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF442" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="443">
@@ -22961,10 +22591,8 @@
           <t>地级政协,黄石市,市政协,湖北省</t>
         </is>
       </c>
-      <c r="AF443" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF443" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="444">
@@ -22996,10 +22624,8 @@
           <t>地级政协,十堰市,市政协,湖北省</t>
         </is>
       </c>
-      <c r="AF444" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF444" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="445">
@@ -23031,10 +22657,8 @@
           <t>地级政协,宜昌市,市政协,湖北省</t>
         </is>
       </c>
-      <c r="AF445" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF445" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="446">
@@ -23066,10 +22690,8 @@
           <t>地级政协,襄阳市,市政协,湖北省</t>
         </is>
       </c>
-      <c r="AF446" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF446" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="447">
@@ -23101,10 +22723,8 @@
           <t>地级政协,鄂州市,市政协,湖北省</t>
         </is>
       </c>
-      <c r="AF447" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF447" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="448">
@@ -23136,10 +22756,8 @@
           <t>地级政协,荆门市,市政协,湖北省</t>
         </is>
       </c>
-      <c r="AF448" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF448" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="449">
@@ -23171,10 +22789,8 @@
           <t>地级政协,孝感市,市政协,湖北省</t>
         </is>
       </c>
-      <c r="AF449" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF449" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="450">
@@ -23206,10 +22822,8 @@
           <t>地级政协,荆州市,市政协,湖北省</t>
         </is>
       </c>
-      <c r="AF450" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF450" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="451">
@@ -23241,10 +22855,8 @@
           <t>地级政协,黄冈市,市政协,湖北省</t>
         </is>
       </c>
-      <c r="AF451" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF451" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="452">
@@ -23276,10 +22888,8 @@
           <t>地级政协,咸宁市,市政协,湖北省</t>
         </is>
       </c>
-      <c r="AF452" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF452" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="453">
@@ -23311,10 +22921,8 @@
           <t>地级政协,随州市,市政协,湖北省</t>
         </is>
       </c>
-      <c r="AF453" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF453" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="454">
@@ -23346,10 +22954,8 @@
           <t>地级政协,长沙市,市政协,湖南省</t>
         </is>
       </c>
-      <c r="AF454" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF454" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="455">
@@ -23381,10 +22987,8 @@
           <t>地级政协,株洲市,市政协,湖南省</t>
         </is>
       </c>
-      <c r="AF455" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF455" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="456">
@@ -23416,10 +23020,8 @@
           <t>地级政协,湘潭市,市政协,湖南省</t>
         </is>
       </c>
-      <c r="AF456" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF456" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="457">
@@ -23451,10 +23053,8 @@
           <t>地级政协,衡阳市,市政协,湖南省</t>
         </is>
       </c>
-      <c r="AF457" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF457" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="458">
@@ -23486,10 +23086,8 @@
           <t>地级政协,邵阳市,市政协,湖南省</t>
         </is>
       </c>
-      <c r="AF458" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF458" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="459">
@@ -23521,10 +23119,8 @@
           <t>地级政协,岳阳市,市政协,湖南省</t>
         </is>
       </c>
-      <c r="AF459" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF459" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="460">
@@ -23556,10 +23152,8 @@
           <t>地级政协,常德市,市政协,湖南省</t>
         </is>
       </c>
-      <c r="AF460" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF460" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="461">
@@ -23591,10 +23185,8 @@
           <t>地级政协,张家界市,市政协,湖南省</t>
         </is>
       </c>
-      <c r="AF461" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF461" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="462">
@@ -23626,10 +23218,8 @@
           <t>地级政协,益阳市,市政协,湖南省</t>
         </is>
       </c>
-      <c r="AF462" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF462" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="463">
@@ -23661,10 +23251,8 @@
           <t>地级政协,郴州市,市政协,湖南省</t>
         </is>
       </c>
-      <c r="AF463" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF463" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="464">
@@ -23696,10 +23284,8 @@
           <t>地级政协,永州市,市政协,湖南省</t>
         </is>
       </c>
-      <c r="AF464" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF464" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="465">
@@ -23731,10 +23317,8 @@
           <t>地级政协,怀化市,市政协,湖南省</t>
         </is>
       </c>
-      <c r="AF465" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF465" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="466">
@@ -23766,10 +23350,8 @@
           <t>地级政协,娄底市,市政协,湖南省</t>
         </is>
       </c>
-      <c r="AF466" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF466" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="467">
@@ -23801,10 +23383,8 @@
           <t>地级政协,南宁市,市政协,广西壮族自治区</t>
         </is>
       </c>
-      <c r="AF467" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF467" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="468">
@@ -23836,10 +23416,8 @@
           <t>地级政协,柳州市,市政协,广西壮族自治区</t>
         </is>
       </c>
-      <c r="AF468" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF468" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="469">
@@ -23871,10 +23449,8 @@
           <t>地级政协,桂林市,市政协,广西壮族自治区</t>
         </is>
       </c>
-      <c r="AF469" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF469" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="470">
@@ -23906,10 +23482,8 @@
           <t>地级政协,梧州市,市政协,广西壮族自治区</t>
         </is>
       </c>
-      <c r="AF470" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF470" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="471">
@@ -23941,10 +23515,8 @@
           <t>地级政协,北海市,市政协,广西壮族自治区</t>
         </is>
       </c>
-      <c r="AF471" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF471" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="472">
@@ -23976,10 +23548,8 @@
           <t>地级政协,防城港市,市政协,广西壮族自治区</t>
         </is>
       </c>
-      <c r="AF472" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF472" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="473">
@@ -24011,10 +23581,8 @@
           <t>地级政协,钦州市,市政协,广西壮族自治区</t>
         </is>
       </c>
-      <c r="AF473" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF473" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="474">
@@ -24046,10 +23614,8 @@
           <t>地级政协,贵港市,市政协,广西壮族自治区</t>
         </is>
       </c>
-      <c r="AF474" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF474" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="475">
@@ -24081,10 +23647,8 @@
           <t>地级政协,玉林市,市政协,广西壮族自治区</t>
         </is>
       </c>
-      <c r="AF475" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF475" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="476">
@@ -24116,10 +23680,8 @@
           <t>地级政协,百色市,市政协,广西壮族自治区</t>
         </is>
       </c>
-      <c r="AF476" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF476" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="477">
@@ -24151,10 +23713,8 @@
           <t>地级政协,贺州市,市政协,广西壮族自治区</t>
         </is>
       </c>
-      <c r="AF477" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF477" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="478">
@@ -24186,10 +23746,8 @@
           <t>地级政协,河池市,市政协,广西壮族自治区</t>
         </is>
       </c>
-      <c r="AF478" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF478" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="479">
@@ -24221,10 +23779,8 @@
           <t>地级政协,来宾市,市政协,广西壮族自治区</t>
         </is>
       </c>
-      <c r="AF479" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF479" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="480">
@@ -24256,10 +23812,8 @@
           <t>地级政协,崇左市,市政协,广西壮族自治区</t>
         </is>
       </c>
-      <c r="AF480" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF480" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="481">
@@ -24291,10 +23845,8 @@
           <t>地级政协,海口市,市政协,海南省</t>
         </is>
       </c>
-      <c r="AF481" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF481" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="482">
@@ -24326,10 +23878,8 @@
           <t>地级政协,三亚市,市政协,海南省</t>
         </is>
       </c>
-      <c r="AF482" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF482" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="483">
@@ -24361,10 +23911,8 @@
           <t>地级政协,三沙市,市政协,海南省</t>
         </is>
       </c>
-      <c r="AF483" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF483" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="484">
@@ -24396,10 +23944,8 @@
           <t>地级政协,儋州市,市政协,海南省</t>
         </is>
       </c>
-      <c r="AF484" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF484" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="485">
@@ -24431,10 +23977,8 @@
           <t>地级政协,自贡市,市政协,四川省</t>
         </is>
       </c>
-      <c r="AF485" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF485" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="486">
@@ -24466,10 +24010,8 @@
           <t>地级政协,攀枝花市,市政协,四川省</t>
         </is>
       </c>
-      <c r="AF486" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF486" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="487">
@@ -24501,10 +24043,8 @@
           <t>地级政协,泸州市,市政协,四川省</t>
         </is>
       </c>
-      <c r="AF487" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF487" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="488">
@@ -24536,10 +24076,8 @@
           <t>地级政协,德阳市,市政协,四川省</t>
         </is>
       </c>
-      <c r="AF488" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF488" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="489">
@@ -24571,10 +24109,8 @@
           <t>地级政协,绵阳市,市政协,四川省</t>
         </is>
       </c>
-      <c r="AF489" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF489" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="490">
@@ -24606,10 +24142,8 @@
           <t>地级政协,广元市,市政协,四川省</t>
         </is>
       </c>
-      <c r="AF490" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF490" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="491">
@@ -24641,10 +24175,8 @@
           <t>地级政协,遂宁市,市政协,四川省</t>
         </is>
       </c>
-      <c r="AF491" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF491" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="492">
@@ -24676,10 +24208,8 @@
           <t>地级政协,内江市,市政协,四川省</t>
         </is>
       </c>
-      <c r="AF492" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF492" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="493">
@@ -24711,10 +24241,8 @@
           <t>地级政协,乐山市,市政协,四川省</t>
         </is>
       </c>
-      <c r="AF493" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF493" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="494">
@@ -24746,10 +24274,8 @@
           <t>地级政协,南充市,市政协,四川省</t>
         </is>
       </c>
-      <c r="AF494" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF494" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="495">
@@ -24781,10 +24307,8 @@
           <t>地级政协,眉山市,市政协,四川省</t>
         </is>
       </c>
-      <c r="AF495" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF495" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="496">
@@ -24816,10 +24340,8 @@
           <t>地级政协,宜宾市,市政协,四川省</t>
         </is>
       </c>
-      <c r="AF496" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF496" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="497">
@@ -24851,10 +24373,8 @@
           <t>地级政协,广安市,市政协,四川省</t>
         </is>
       </c>
-      <c r="AF497" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF497" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="498">
@@ -24886,10 +24406,8 @@
           <t>地级政协,达州市,市政协,四川省</t>
         </is>
       </c>
-      <c r="AF498" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF498" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="499">
@@ -24921,10 +24439,8 @@
           <t>地级政协,雅安市,市政协,四川省</t>
         </is>
       </c>
-      <c r="AF499" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF499" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="500">
@@ -24956,10 +24472,8 @@
           <t>地级政协,巴中市,市政协,四川省</t>
         </is>
       </c>
-      <c r="AF500" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF500" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="501">
@@ -24991,10 +24505,8 @@
           <t>地级政协,资阳市,市政协,四川省</t>
         </is>
       </c>
-      <c r="AF501" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF501" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="502">
@@ -25026,10 +24538,8 @@
           <t>地级政协,贵阳市,市政协,贵州省</t>
         </is>
       </c>
-      <c r="AF502" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF502" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="503">
@@ -25061,10 +24571,8 @@
           <t>地级政协,六盘水市,市政协,贵州省</t>
         </is>
       </c>
-      <c r="AF503" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF503" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="504">
@@ -25096,10 +24604,8 @@
           <t>地级政协,遵义市,市政协,贵州省</t>
         </is>
       </c>
-      <c r="AF504" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF504" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="505">
@@ -25131,10 +24637,8 @@
           <t>地级政协,安顺市,市政协,贵州省</t>
         </is>
       </c>
-      <c r="AF505" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF505" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="506">
@@ -25166,10 +24670,8 @@
           <t>地级政协,毕节市,市政协,贵州省</t>
         </is>
       </c>
-      <c r="AF506" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF506" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="507">
@@ -25201,10 +24703,8 @@
           <t>地级政协,铜仁市,市政协,贵州省</t>
         </is>
       </c>
-      <c r="AF507" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF507" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="508">
@@ -25236,10 +24736,8 @@
           <t>地级政协,昆明市,市政协,贵州省</t>
         </is>
       </c>
-      <c r="AF508" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF508" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="509">
@@ -25271,10 +24769,8 @@
           <t>地级政协,曲靖市,市政协,贵州省</t>
         </is>
       </c>
-      <c r="AF509" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF509" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="510">
@@ -25306,10 +24802,8 @@
           <t>地级政协,玉溪市,市政协,贵州省</t>
         </is>
       </c>
-      <c r="AF510" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF510" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="511">
@@ -25341,10 +24835,8 @@
           <t>地级政协,保山市,市政协,贵州省</t>
         </is>
       </c>
-      <c r="AF511" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF511" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="512">
@@ -25376,10 +24868,8 @@
           <t>地级政协,昭通市,市政协,贵州省</t>
         </is>
       </c>
-      <c r="AF512" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF512" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="513">
@@ -25411,10 +24901,8 @@
           <t>地级政协,丽江市,市政协,贵州省</t>
         </is>
       </c>
-      <c r="AF513" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF513" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="514">
@@ -25446,10 +24934,8 @@
           <t>地级政协,普洱市,市政协,贵州省</t>
         </is>
       </c>
-      <c r="AF514" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF514" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="515">
@@ -25481,10 +24967,8 @@
           <t>地级政协,临沧市,市政协,贵州省</t>
         </is>
       </c>
-      <c r="AF515" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF515" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="516">
@@ -25516,10 +25000,8 @@
           <t>地级政协,拉萨市,市政协,贵州省</t>
         </is>
       </c>
-      <c r="AF516" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF516" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="517">
@@ -25551,10 +25033,8 @@
           <t>地级政协,日喀则市,市政协,贵州省</t>
         </is>
       </c>
-      <c r="AF517" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF517" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="518">
@@ -25586,10 +25066,8 @@
           <t>地级政协,昌都市,市政协,贵州省</t>
         </is>
       </c>
-      <c r="AF518" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF518" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="519">
@@ -25621,10 +25099,8 @@
           <t>地级政协,林芝市,市政协,贵州省</t>
         </is>
       </c>
-      <c r="AF519" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF519" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="520">
@@ -25656,10 +25132,8 @@
           <t>地级政协,山南市,市政协,贵州省</t>
         </is>
       </c>
-      <c r="AF520" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF520" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="521">
@@ -25691,10 +25165,8 @@
           <t>地级政协,那曲市,市政协,贵州省</t>
         </is>
       </c>
-      <c r="AF521" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF521" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="522">
@@ -25726,10 +25198,8 @@
           <t>地级政协,铜川市,市政协,陕西省</t>
         </is>
       </c>
-      <c r="AF522" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF522" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="523">
@@ -25761,10 +25231,8 @@
           <t>地级政协,宝鸡市,市政协,陕西省</t>
         </is>
       </c>
-      <c r="AF523" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF523" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="524">
@@ -25796,10 +25264,8 @@
           <t>地级政协,咸阳市,市政协,陕西省</t>
         </is>
       </c>
-      <c r="AF524" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF524" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="525">
@@ -25831,10 +25297,8 @@
           <t>地级政协,渭南市,市政协,陕西省</t>
         </is>
       </c>
-      <c r="AF525" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF525" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="526">
@@ -25866,10 +25330,8 @@
           <t>地级政协,延安市,市政协,陕西省</t>
         </is>
       </c>
-      <c r="AF526" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF526" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="527">
@@ -25901,10 +25363,8 @@
           <t>地级政协,汉中市,市政协,陕西省</t>
         </is>
       </c>
-      <c r="AF527" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF527" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="528">
@@ -25936,10 +25396,8 @@
           <t>地级政协,榆林市,市政协,陕西省</t>
         </is>
       </c>
-      <c r="AF528" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF528" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="529">
@@ -25971,10 +25429,8 @@
           <t>地级政协,安康市,市政协,陕西省</t>
         </is>
       </c>
-      <c r="AF529" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF529" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="530">
@@ -26006,10 +25462,8 @@
           <t>地级政协,商洛市,市政协,陕西省</t>
         </is>
       </c>
-      <c r="AF530" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF530" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="531">
@@ -26041,10 +25495,8 @@
           <t>地级政协,兰州市,市政协,甘肃省</t>
         </is>
       </c>
-      <c r="AF531" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF531" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="532">
@@ -26076,10 +25528,8 @@
           <t>地级政协,嘉峪关市,市政协,甘肃省</t>
         </is>
       </c>
-      <c r="AF532" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF532" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="533">
@@ -26111,10 +25561,8 @@
           <t>地级政协,金昌市,市政协,甘肃省</t>
         </is>
       </c>
-      <c r="AF533" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF533" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="534">
@@ -26146,10 +25594,8 @@
           <t>地级政协,白银市,市政协,甘肃省</t>
         </is>
       </c>
-      <c r="AF534" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF534" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="535">
@@ -26181,10 +25627,8 @@
           <t>地级政协,天水市,市政协,甘肃省</t>
         </is>
       </c>
-      <c r="AF535" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF535" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="536">
@@ -26216,10 +25660,8 @@
           <t>地级政协,武威市,市政协,甘肃省</t>
         </is>
       </c>
-      <c r="AF536" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF536" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="537">
@@ -26251,10 +25693,8 @@
           <t>地级政协,张掖市,市政协,甘肃省</t>
         </is>
       </c>
-      <c r="AF537" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF537" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="538">
@@ -26286,10 +25726,8 @@
           <t>地级政协,平凉市,市政协,甘肃省</t>
         </is>
       </c>
-      <c r="AF538" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF538" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="539">
@@ -26321,10 +25759,8 @@
           <t>地级政协,酒泉市,市政协,甘肃省</t>
         </is>
       </c>
-      <c r="AF539" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF539" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="540">
@@ -26356,10 +25792,8 @@
           <t>地级政协,庆阳市,市政协,甘肃省</t>
         </is>
       </c>
-      <c r="AF540" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF540" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="541">
@@ -26391,10 +25825,8 @@
           <t>地级政协,定西市,市政协,甘肃省</t>
         </is>
       </c>
-      <c r="AF541" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF541" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="542">
@@ -26426,10 +25858,8 @@
           <t>地级政协,陇南市,市政协,甘肃省</t>
         </is>
       </c>
-      <c r="AF542" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF542" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="543">
@@ -26461,10 +25891,8 @@
           <t>地级政协,西宁市,市政协,青海省</t>
         </is>
       </c>
-      <c r="AF543" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF543" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="544">
@@ -26496,10 +25924,8 @@
           <t>地级政协,海东市,市政协,青海省</t>
         </is>
       </c>
-      <c r="AF544" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF544" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="545">
@@ -26531,10 +25957,8 @@
           <t>地级政协,银川市,市政协,宁夏回族自治区</t>
         </is>
       </c>
-      <c r="AF545" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF545" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="546">
@@ -26566,10 +25990,8 @@
           <t>地级政协,石嘴山市,市政协,宁夏回族自治区</t>
         </is>
       </c>
-      <c r="AF546" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF546" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="547">
@@ -26601,10 +26023,8 @@
           <t>地级政协,吴忠市,市政协,宁夏回族自治区</t>
         </is>
       </c>
-      <c r="AF547" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF547" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="548">
@@ -26636,10 +26056,8 @@
           <t>地级政协,固原市,市政协,宁夏回族自治区</t>
         </is>
       </c>
-      <c r="AF548" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF548" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="549">
@@ -26671,10 +26089,8 @@
           <t>地级政协,中卫市,市政协,宁夏回族自治区</t>
         </is>
       </c>
-      <c r="AF549" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF549" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="550">
@@ -26706,10 +26122,8 @@
           <t>地级政协,乌鲁木齐市,市政协,新疆维吾尔自治区</t>
         </is>
       </c>
-      <c r="AF550" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF550" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="551">
@@ -26741,10 +26155,8 @@
           <t>地级政协,克拉玛依市,市政协,新疆维吾尔自治区</t>
         </is>
       </c>
-      <c r="AF551" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF551" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="552">
@@ -26776,10 +26188,8 @@
           <t>地级政协,吐鲁番市,市政协,新疆维吾尔自治区</t>
         </is>
       </c>
-      <c r="AF552" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF552" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="553">
@@ -26811,10 +26221,8 @@
           <t>地级政协,哈密市,市政协,新疆维吾尔自治区</t>
         </is>
       </c>
-      <c r="AF553" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="AF553" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/cards.unified.xlsx
+++ b/xlsx/cards.unified.xlsx
@@ -14193,7 +14193,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>正省级政协,北京市,直辖市政协</t>
+          <t>直辖市政协,北京市</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -14253,7 +14253,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>正省级政协,天津市,直辖市政协</t>
+          <t>直辖市政协,天津市</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>正省级政协,河北省,省政协</t>
+          <t>省政协,河北省</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>正省级政协,山西省,省政协</t>
+          <t>省政协,山西省</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -14438,7 +14438,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>正省级政协,内蒙古自治区,自治区政协</t>
+          <t>自治区政协,内蒙古自治区</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -14498,7 +14498,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>正省级政协,辽宁省,省政协</t>
+          <t>省政协,辽宁省</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -14558,7 +14558,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>正省级政协,吉林省,省政协</t>
+          <t>省政协,吉林省</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -14618,7 +14618,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>正省级政协,黑龙江省,省政协</t>
+          <t>省政协,黑龙江省</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -14678,7 +14678,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>正省级政协,上海市,直辖市政协</t>
+          <t>直辖市政协,上海市</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -14738,7 +14738,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>正省级政协,江苏省,省政协</t>
+          <t>省政协,江苏省</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -14798,7 +14798,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>正省级政协,浙江省,省政协</t>
+          <t>省政协,浙江省</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -14858,7 +14858,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>正省级政协,安徽省,省政协</t>
+          <t>省政协,安徽省</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -14918,7 +14918,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>正省级政协,福建省,省政协</t>
+          <t>省政协,福建省</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -14978,7 +14978,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>正省级政协,江西省,省政协</t>
+          <t>省政协,江西省</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -15038,7 +15038,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>正省级政协,山东省,省政协</t>
+          <t>省政协,山东省</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -15103,7 +15103,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>正省级政协,河南省,省政协</t>
+          <t>省政协,河南省</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -15168,7 +15168,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>正省级政协,湖北省,省政协</t>
+          <t>省政协,湖北省</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>正省级政协,湖南省,省政协</t>
+          <t>省政协,湖南省</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -15288,7 +15288,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>正省级政协,广东省,省政协</t>
+          <t>省政协,广东省</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -15348,7 +15348,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>正省级政协,广西壮族自治区,自治区政协</t>
+          <t>自治区政协,广西壮族自治区</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -15408,7 +15408,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>正省级政协,海南省,省政协</t>
+          <t>省政协,海南省</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>正省级政协,重庆市,直辖市政协</t>
+          <t>直辖市政协,重庆市</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>正省级政协,四川省,省政协</t>
+          <t>省政协,四川省</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -15588,7 +15588,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>正省级政协,贵州省,省政协</t>
+          <t>省政协,贵州省</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -15648,7 +15648,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>正省级政协,云南省,省政协</t>
+          <t>省政协,云南省</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -15708,7 +15708,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>正省级政协,西藏自治区,自治区政协</t>
+          <t>自治区政协,西藏自治区</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -15768,7 +15768,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>正省级政协,陕西省,省政协</t>
+          <t>省政协,陕西省</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -15828,7 +15828,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>正省级政协,甘肃省,省政协</t>
+          <t>省政协,甘肃省</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -15888,7 +15888,7 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>正省级政协,青海省,省政协</t>
+          <t>省政协,青海省</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -15948,7 +15948,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>正省级政协,宁夏回族自治区,自治区政协</t>
+          <t>自治区政协,宁夏回族自治区</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -16008,7 +16008,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>正省级政协,新疆维吾尔自治区,自治区政协</t>
+          <t>自治区政协,新疆维吾尔自治区</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -16050,7 +16050,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>副省级城市政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E258" t="n">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>副省级政协,广州市,市政协,广东省,省会城市</t>
+          <t>广州市,副省级城市政协,省会城市,广东省</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -16087,7 +16087,7 @@
         </is>
       </c>
       <c r="AF258" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259">
@@ -16103,7 +16103,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>副省级城市政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E259" t="n">
@@ -16121,7 +16121,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>副省级政协,深圳市,市政协,广东省,计划单市</t>
+          <t>深圳市,副省级城市政协,计划单市,广东省</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -16135,7 +16135,7 @@
         </is>
       </c>
       <c r="AF259" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260">
@@ -17073,7 +17073,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>副省级城市政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E279" t="n">
@@ -17091,7 +17091,7 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>副省级政协,哈尔滨市,市政协,黑龙江省,省会城市</t>
+          <t>哈尔滨市,副省级城市政协,省会城市,黑龙江省</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -17105,7 +17105,7 @@
         </is>
       </c>
       <c r="AF279" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280">
@@ -17121,7 +17121,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>副省级城市政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E280" t="n">
@@ -17139,7 +17139,7 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>副省级政协,武汉市,市政协,湖北省,省会城市</t>
+          <t>武汉市,副省级城市政协,省会城市,湖北省</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -17153,7 +17153,7 @@
         </is>
       </c>
       <c r="AF280" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="281">
@@ -17216,7 +17216,7 @@
         </is>
       </c>
       <c r="AF281" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282">
@@ -17279,7 +17279,7 @@
         </is>
       </c>
       <c r="AF282" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="283">
@@ -17295,7 +17295,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>副省级城市政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E283" t="n">
@@ -17308,11 +17308,11 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>副省级政协,沈阳市,市政协,辽宁省,省会城市</t>
+          <t>沈阳市,副省级城市政协,省会城市,辽宁省</t>
         </is>
       </c>
       <c r="AF283" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="284">
@@ -17328,7 +17328,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>副省级城市政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E284" t="n">
@@ -17341,11 +17341,11 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>副省级政协,成都市,市政协,四川省,省会城市</t>
+          <t>成都市,副省级城市政协,省会城市,四川省</t>
         </is>
       </c>
       <c r="AF284" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="285">
@@ -17361,7 +17361,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>副省级城市政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E285" t="n">
@@ -17374,11 +17374,11 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>副省级政协,南京市,市政协,江苏省,省会城市</t>
+          <t>南京市,副省级城市政协,省会城市,江苏省</t>
         </is>
       </c>
       <c r="AF285" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="286">
@@ -17394,7 +17394,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>副省级城市政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E286" t="n">
@@ -17407,11 +17407,11 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>副省级政协,西安市,市政协,陕西省,省会城市</t>
+          <t>西安市,副省级城市政协,省会城市,陕西省</t>
         </is>
       </c>
       <c r="AF286" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="287">
@@ -17427,7 +17427,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>副省级城市政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E287" t="n">
@@ -17440,11 +17440,11 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>副省级政协,长春市,市政协,吉林省,省会城市</t>
+          <t>长春市,副省级城市政协,省会城市,吉林省</t>
         </is>
       </c>
       <c r="AF287" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288">
@@ -17460,7 +17460,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>副省级城市政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E288" t="n">
@@ -17473,11 +17473,11 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>副省级政协,济南市,市政协,山东省,省会城市</t>
+          <t>济南市,副省级城市政协,省会城市,山东省</t>
         </is>
       </c>
       <c r="AF288" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289">
@@ -17493,7 +17493,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>副省级城市政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E289" t="n">
@@ -17506,11 +17506,11 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>副省级政协,杭州市,市政协,浙江省,省会城市</t>
+          <t>杭州市,副省级城市政协,省会城市,浙江省</t>
         </is>
       </c>
       <c r="AF289" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="290">
@@ -17526,7 +17526,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>副省级城市政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E290" t="n">
@@ -17539,11 +17539,11 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>副省级政协,大连市,市政协,辽宁省,计划单列市</t>
+          <t>大连市,副省级城市政协,计划单列市,辽宁省</t>
         </is>
       </c>
       <c r="AF290" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="291">
@@ -17559,7 +17559,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>副省级城市政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E291" t="n">
@@ -17572,11 +17572,11 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>副省级政协,青岛市,市政协,山东省,计划单列市</t>
+          <t>青岛市,副省级城市政协,计划单列市,山东省</t>
         </is>
       </c>
       <c r="AF291" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>副省级城市政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E292" t="n">
@@ -17605,11 +17605,11 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>副省级政协,厦门市,市政协,福建省,计划单列市</t>
+          <t>厦门市,副省级城市政协,计划单列市,福建省</t>
         </is>
       </c>
       <c r="AF292" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="293">
@@ -17625,7 +17625,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>副省级城市政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E293" t="n">
@@ -17638,11 +17638,11 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>副省级政协,宁波市,市政协,浙江省,计划单列市</t>
+          <t>宁波市,副省级城市政协,计划单列市,浙江省</t>
         </is>
       </c>
       <c r="AF293" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="294">

--- a/xlsx/cards.unified.xlsx
+++ b/xlsx/cards.unified.xlsx
@@ -16111,27 +16111,27 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>深圳市政协</t>
+          <t>武汉市政协</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议深圳市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议武汉市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>深圳市,副省级城市政协,计划单市,广东省</t>
+          <t>武汉市,副省级城市政协,省会城市,湖北省</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>访问官网 - www.szzx.gov.cn</t>
+          <t>访问官网 - www.whzx.org.cn</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>https://www.szzx.gov.cn/</t>
+          <t xml:space="preserve">https://www.whzx.org.cn/  </t>
         </is>
       </c>
       <c r="AF259" t="b">
@@ -16151,7 +16151,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E260" t="n">
@@ -16159,31 +16159,31 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>珠海市政协</t>
+          <t>哈尔滨市政协</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议珠海市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议哈尔滨市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>地级政协,珠海市,市政协,广东省</t>
+          <t>哈尔滨市,副省级城市政协,省会城市,黑龙江省</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>访问官网 - www.zhzx.gov.cn</t>
+          <t>访问官网 - www.hrbzx.gov.cn</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>https://www.zhzx.gov.cn/</t>
+          <t>https://www.hrbzx.gov.cn/</t>
         </is>
       </c>
       <c r="AF260" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261">
@@ -16199,7 +16199,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E261" t="n">
@@ -16207,31 +16207,16 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>汕头市政协</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>中国人民政治协商会议汕头市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>沈阳市政协</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>地级政协,汕头市,市政协,广东省</t>
-        </is>
-      </c>
-      <c r="L261" t="inlineStr">
-        <is>
-          <t>访问官网 - stzx.shantou.gov.cn</t>
-        </is>
-      </c>
-      <c r="M261" t="inlineStr">
-        <is>
-          <t>https://stzx.shantou.gov.cn/</t>
+          <t>沈阳市,副省级城市政协,省会城市,辽宁省</t>
         </is>
       </c>
       <c r="AF261" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="262">
@@ -16247,7 +16232,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>县级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E262" t="n">
@@ -16255,36 +16240,16 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>汕头市金平区政协</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>中国人民政治协商会议汕头市金平区委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
-        </is>
-      </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>http://www.jpzx.gov.cn/favicon.ico</t>
+          <t>成都市政协</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>县级政协,汕头市金平区,市辖区政协,广东省</t>
-        </is>
-      </c>
-      <c r="L262" t="inlineStr">
-        <is>
-          <t>访问官网 - www.jpzx.gov.cn</t>
-        </is>
-      </c>
-      <c r="M262" t="inlineStr">
-        <is>
-          <t>https://www.jpzx.gov.cn/welcome</t>
+          <t>成都市,副省级城市政协,省会城市,四川省</t>
         </is>
       </c>
       <c r="AF262" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263">
@@ -16300,7 +16265,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E263" t="n">
@@ -16308,31 +16273,16 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>佛山市政协</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>中国人民政治协商会议佛山市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>南京市政协</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>地级政协,佛山市,市政协,广东省</t>
-        </is>
-      </c>
-      <c r="L263" t="inlineStr">
-        <is>
-          <t>访问官网 - www.fszx.gov.cn</t>
-        </is>
-      </c>
-      <c r="M263" t="inlineStr">
-        <is>
-          <t>https://www.fszx.gov.cn/</t>
+          <t>南京市,副省级城市政协,省会城市,江苏省</t>
         </is>
       </c>
       <c r="AF263" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264">
@@ -16348,7 +16298,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E264" t="n">
@@ -16356,31 +16306,16 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>韶关市政协</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>中国人民政治协商会议韶关市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>西安市政协</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>地级政协,韶关市,市政协,广东省</t>
-        </is>
-      </c>
-      <c r="L264" t="inlineStr">
-        <is>
-          <t>访问官网 - www.sgzxb.gov.cn</t>
-        </is>
-      </c>
-      <c r="M264" t="inlineStr">
-        <is>
-          <t>https://www.sgzxb.gov.cn/</t>
+          <t>西安市,副省级城市政协,省会城市,陕西省</t>
         </is>
       </c>
       <c r="AF264" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="265">
@@ -16396,7 +16331,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E265" t="n">
@@ -16404,31 +16339,16 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>河源市政协</t>
-        </is>
-      </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>中国人民政治协商会议河源市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>长春市政协</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>地级政协,河源市,市政协,广东省</t>
-        </is>
-      </c>
-      <c r="L265" t="inlineStr">
-        <is>
-          <t>访问官网 - www.gdhyzx.gov.cn</t>
-        </is>
-      </c>
-      <c r="M265" t="inlineStr">
-        <is>
-          <t>https://www.gdhyzx.gov.cn/hyzx/index.html</t>
+          <t>长春市,副省级城市政协,省会城市,吉林省</t>
         </is>
       </c>
       <c r="AF265" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="266">
@@ -16444,7 +16364,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E266" t="n">
@@ -16452,31 +16372,16 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>梅州市政协</t>
-        </is>
-      </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>中国人民政治协商会议梅州市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>济南市政协</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>地级政协,梅州市,市政协,广东省</t>
-        </is>
-      </c>
-      <c r="L266" t="inlineStr">
-        <is>
-          <t>访问官网 - www.mzzx.gov.cn</t>
-        </is>
-      </c>
-      <c r="M266" t="inlineStr">
-        <is>
-          <t>https://www.mzzx.gov.cn/</t>
+          <t>济南市,副省级城市政协,省会城市,山东省</t>
         </is>
       </c>
       <c r="AF266" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267">
@@ -16492,7 +16397,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E267" t="n">
@@ -16500,31 +16405,16 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>惠州市政协</t>
-        </is>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>中国人民政治协商会议惠州市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>杭州市政协</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>地级政协,惠州市,市政协,广东省</t>
-        </is>
-      </c>
-      <c r="L267" t="inlineStr">
-        <is>
-          <t>访问官网 - zx.huizhou.gov.cn</t>
-        </is>
-      </c>
-      <c r="M267" t="inlineStr">
-        <is>
-          <t>https://zx.huizhou.gov.cn/</t>
+          <t>杭州市,副省级城市政协,省会城市,浙江省</t>
         </is>
       </c>
       <c r="AF267" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268">
@@ -16540,7 +16430,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E268" t="n">
@@ -16548,31 +16438,16 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>汕尾市政协</t>
-        </is>
-      </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>中国人民政治协商会议汕尾市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>大连市政协</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>地级政协,汕尾市,市政协,广东省</t>
-        </is>
-      </c>
-      <c r="L268" t="inlineStr">
-        <is>
-          <t>访问官网 - www.swzx.gov.cn</t>
-        </is>
-      </c>
-      <c r="M268" t="inlineStr">
-        <is>
-          <t>https://www.swzx.gov.cn/</t>
+          <t>大连市,副省级城市政协,计划单列市,辽宁省</t>
         </is>
       </c>
       <c r="AF268" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="269">
@@ -16588,7 +16463,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E269" t="n">
@@ -16596,31 +16471,16 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>东莞市政协</t>
-        </is>
-      </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>中国人民政治协商会议东莞市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>青岛市政协</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>地级政协,东莞市,市政协,广东省</t>
-        </is>
-      </c>
-      <c r="L269" t="inlineStr">
-        <is>
-          <t>访问官网 - dgzx.dg.gov.cn</t>
-        </is>
-      </c>
-      <c r="M269" t="inlineStr">
-        <is>
-          <t>https://dgzx.dg.gov.cn/</t>
+          <t>青岛市,副省级城市政协,计划单列市,山东省</t>
         </is>
       </c>
       <c r="AF269" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270">
@@ -16636,7 +16496,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E270" t="n">
@@ -16644,31 +16504,31 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>中山市政协</t>
+          <t>深圳市政协</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议中山市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议深圳市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>地级政协,中山市,市政协,广东省</t>
+          <t>深圳市,副省级城市政协,计划单列市,广东省</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>访问官网 - zszx.zsnews.cn</t>
+          <t>访问官网 - www.szzx.gov.cn</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>https://zszx.zsnews.cn/</t>
+          <t>https://www.szzx.gov.cn/</t>
         </is>
       </c>
       <c r="AF270" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
@@ -16684,7 +16544,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E271" t="n">
@@ -16692,31 +16552,16 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>江门市政协</t>
-        </is>
-      </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>中国人民政治协商会议江门市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>厦门市政协</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>地级政协,江门市,市政协,广东省</t>
-        </is>
-      </c>
-      <c r="L271" t="inlineStr">
-        <is>
-          <t>访问官网 - zx.jiangmen.cn</t>
-        </is>
-      </c>
-      <c r="M271" t="inlineStr">
-        <is>
-          <t>https://zx.jiangmen.cn/</t>
+          <t>厦门市,副省级城市政协,计划单列市,福建省</t>
         </is>
       </c>
       <c r="AF271" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272">
@@ -16732,7 +16577,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E272" t="n">
@@ -16740,31 +16585,16 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>阳江市政协</t>
-        </is>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>中国人民政治协商会议阳江市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>宁波市政协</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>地级政协,阳江市,市政协,广东省</t>
-        </is>
-      </c>
-      <c r="L272" t="inlineStr">
-        <is>
-          <t>访问官网 - www.yjszx.gov.cn</t>
-        </is>
-      </c>
-      <c r="M272" t="inlineStr">
-        <is>
-          <t>https://www.yjszx.gov.cn/default.html</t>
+          <t>宁波市,副省级城市政协,计划单列市,浙江省</t>
         </is>
       </c>
       <c r="AF272" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
@@ -16788,32 +16618,27 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>湛江市政协</t>
+          <t>珠海市政协</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议湛江市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
-        </is>
-      </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>https://www.google.com/s2/favicons?domain=http://www.gdzjzx.gov.cn/</t>
+          <t>中国人民政治协商会议珠海市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>地级政协,湛江市,市政协,广东省</t>
+          <t>地级政协,珠海市,市政协,广东省</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>访问官网 - www.gdzjzx.gov.cn</t>
+          <t>访问官网 - www.zhzx.gov.cn</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>https://www.gdzjzx.gov.cn/</t>
+          <t>https://www.zhzx.gov.cn/</t>
         </is>
       </c>
       <c r="AF273" t="b">
@@ -16841,27 +16666,27 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>茂名市政协</t>
+          <t>汕头市政协</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议茂名市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议汕头市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>地级政协,茂名市,市政协,广东省</t>
+          <t>地级政协,汕头市,市政协,广东省</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>访问官网 - zx.maoming.gov.cn</t>
+          <t>访问官网 - stzx.shantou.gov.cn</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>https://zx.maoming.gov.cn/website/main/jsp/index.jsp</t>
+          <t>https://stzx.shantou.gov.cn/</t>
         </is>
       </c>
       <c r="AF274" t="b">
@@ -16881,7 +16706,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>县级政协</t>
         </is>
       </c>
       <c r="E275" t="n">
@@ -16889,27 +16714,32 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>肇庆市政协</t>
+          <t>汕头市金平区政协</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议肇庆市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议汕头市金平区委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>http://www.jpzx.gov.cn/favicon.ico</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>地级政协,肇庆市,市政协,广东省</t>
+          <t>县级政协,汕头市金平区,市辖区政协,广东省</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>访问官网 - zqzx.gov.cn</t>
+          <t>访问官网 - www.jpzx.gov.cn</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>https://zqzx.gov.cn/index.html</t>
+          <t>https://www.jpzx.gov.cn/welcome</t>
         </is>
       </c>
       <c r="AF275" t="b">
@@ -16937,27 +16767,27 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>潮州市政协</t>
+          <t>佛山市政协</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议潮州市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议佛山市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>地级政协,潮州市,市政协,广东省</t>
+          <t>地级政协,佛山市,市政协,广东省</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>访问官网 - czzx.gov.cn</t>
+          <t>访问官网 - www.fszx.gov.cn</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>https://czzx.gov.cn/</t>
+          <t>https://www.fszx.gov.cn/</t>
         </is>
       </c>
       <c r="AF276" t="b">
@@ -16985,27 +16815,27 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>揭阳市政协</t>
+          <t>韶关市政协</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议揭阳市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议韶关市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>地级政协,揭阳市,市政协,广东省</t>
+          <t>地级政协,韶关市,市政协,广东省</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>访问官网 - www.jieyangzhengxie.gov.cn/</t>
+          <t>访问官网 - www.sgzxb.gov.cn</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.jieyangzhengxie.gov.cn/ </t>
+          <t>https://www.sgzxb.gov.cn/</t>
         </is>
       </c>
       <c r="AF277" t="b">
@@ -17033,27 +16863,27 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>云浮市政协</t>
+          <t>河源市政协</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议云浮市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议河源市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>地级政协,云浮市,市政协,广东省</t>
+          <t>地级政协,河源市,市政协,广东省</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>访问官网 - zx.yunfu.gov.cn</t>
+          <t>访问官网 - www.gdhyzx.gov.cn</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>https://zx.yunfu.gov.cn/</t>
+          <t>https://www.gdhyzx.gov.cn/hyzx/index.html</t>
         </is>
       </c>
       <c r="AF278" t="b">
@@ -17073,7 +16903,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E279" t="n">
@@ -17081,31 +16911,31 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>哈尔滨市政协</t>
+          <t>梅州市政协</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议哈尔滨市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议梅州市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>哈尔滨市,副省级城市政协,省会城市,黑龙江省</t>
+          <t>地级政协,梅州市,市政协,广东省</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>访问官网 - www.hrbzx.gov.cn</t>
+          <t>访问官网 - www.mzzx.gov.cn</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>https://www.hrbzx.gov.cn/</t>
+          <t>https://www.mzzx.gov.cn/</t>
         </is>
       </c>
       <c r="AF279" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="280">
@@ -17121,7 +16951,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E280" t="n">
@@ -17129,31 +16959,31 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>武汉市政协</t>
+          <t>惠州市政协</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议武汉市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+          <t>中国人民政治协商会议惠州市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>武汉市,副省级城市政协,省会城市,湖北省</t>
+          <t>地级政协,惠州市,市政协,广东省</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>访问官网 - www.whzx.org.cn</t>
+          <t>访问官网 - zx.huizhou.gov.cn</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.whzx.org.cn/  </t>
+          <t>https://zx.huizhou.gov.cn/</t>
         </is>
       </c>
       <c r="AF280" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="281">
@@ -17169,54 +16999,39 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>相关机构</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>中央网信办（国家互联网信息办公室）违法和不良信息举报中心</t>
+          <t>汕尾市政协</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>统筹协调全国互联网违法和不良信息举报工作；指导、监督各地各网站规范开展互联网违法和不良信息举报工作；受理、协助处置网民对互联网违法和不良信息的举报；宣传动员广大网民积极参与互联网违法和不良信息举报监督；主办中国互联网联合辟谣平台，统筹做好网络辟谣工作；开展国际交流合作，加强与境外国际组织、相关机构、互联网企业的联系，协调处理相关有害信息。</t>
-        </is>
-      </c>
-      <c r="H281" t="inlineStr">
-        <is>
-          <t>https://zhengxie.com.cn/assets/images/12377-3-04.webp</t>
+          <t>中国人民政治协商会议汕尾市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>举报中心</t>
+          <t>地级政协,汕尾市,市政协,广东省</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>访问官网</t>
+          <t>访问官网 - www.swzx.gov.cn</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>https://www.12377.cn</t>
-        </is>
-      </c>
-      <c r="N281" t="inlineStr">
-        <is>
-          <t>机构简介</t>
-        </is>
-      </c>
-      <c r="O281" t="inlineStr">
-        <is>
-          <t>https://www.12377.cn/jgjj.html?tab=5</t>
+          <t>https://www.swzx.gov.cn/</t>
         </is>
       </c>
       <c r="AF281" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="282">
@@ -17232,7 +17047,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>相关机构</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E282" t="n">
@@ -17240,46 +17055,31 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>12321网络不良与垃圾信息举报受理中心</t>
+          <t>东莞市政协</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>中国互联网协会受工业和信息化部委托设立的投诉受理机构。负责协助工业和信息化部承担关于互联网、移动电话网、固定电话网等各种形式信息通信网络及电信业务中不良与垃圾信息的投诉受理、线索转办及信息统计等工作。</t>
-        </is>
-      </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t>https://www.12321.cn/Public/home/image/favicon.ico,#FFFFFF</t>
+          <t>中国人民政治协商会议东莞市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>举报中心</t>
+          <t>地级政协,东莞市,市政协,广东省</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>访问官网</t>
+          <t>访问官网 - dgzx.dg.gov.cn</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>https://www.12321.cn</t>
-        </is>
-      </c>
-      <c r="N282" t="inlineStr">
-        <is>
-          <t>机构介绍</t>
-        </is>
-      </c>
-      <c r="O282" t="inlineStr">
-        <is>
-          <t>https://www.12321.cn/single?tpl=institution</t>
+          <t>https://dgzx.dg.gov.cn/</t>
         </is>
       </c>
       <c r="AF282" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="283">
@@ -17295,7 +17095,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E283" t="n">
@@ -17303,16 +17103,31 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>沈阳市政协</t>
+          <t>中山市政协</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>中国人民政治协商会议中山市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>沈阳市,副省级城市政协,省会城市,辽宁省</t>
+          <t>地级政协,中山市,市政协,广东省</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>访问官网 - zszx.zsnews.cn</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>https://zszx.zsnews.cn/</t>
         </is>
       </c>
       <c r="AF283" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="284">
@@ -17328,7 +17143,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E284" t="n">
@@ -17336,16 +17151,31 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>成都市政协</t>
+          <t>江门市政协</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>中国人民政治协商会议江门市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>成都市,副省级城市政协,省会城市,四川省</t>
+          <t>地级政协,江门市,市政协,广东省</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>访问官网 - zx.jiangmen.cn</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>https://zx.jiangmen.cn/</t>
         </is>
       </c>
       <c r="AF284" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285">
@@ -17361,7 +17191,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E285" t="n">
@@ -17369,16 +17199,31 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>南京市政协</t>
+          <t>阳江市政协</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>中国人民政治协商会议阳江市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>南京市,副省级城市政协,省会城市,江苏省</t>
+          <t>地级政协,阳江市,市政协,广东省</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>访问官网 - www.yjszx.gov.cn</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>https://www.yjszx.gov.cn/default.html</t>
         </is>
       </c>
       <c r="AF285" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="286">
@@ -17394,7 +17239,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E286" t="n">
@@ -17402,16 +17247,36 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>西安市政协</t>
+          <t>湛江市政协</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>中国人民政治协商会议湛江市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>https://www.google.com/s2/favicons?domain=http://www.gdzjzx.gov.cn/</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>西安市,副省级城市政协,省会城市,陕西省</t>
+          <t>地级政协,湛江市,市政协,广东省</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>访问官网 - www.gdzjzx.gov.cn</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>https://www.gdzjzx.gov.cn/</t>
         </is>
       </c>
       <c r="AF286" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287">
@@ -17427,7 +17292,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E287" t="n">
@@ -17435,16 +17300,31 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>长春市政协</t>
+          <t>茂名市政协</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>中国人民政治协商会议茂名市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>长春市,副省级城市政协,省会城市,吉林省</t>
+          <t>地级政协,茂名市,市政协,广东省</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>访问官网 - zx.maoming.gov.cn</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>https://zx.maoming.gov.cn/website/main/jsp/index.jsp</t>
         </is>
       </c>
       <c r="AF287" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288">
@@ -17460,7 +17340,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E288" t="n">
@@ -17468,16 +17348,31 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>济南市政协</t>
+          <t>肇庆市政协</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>中国人民政治协商会议肇庆市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>济南市,副省级城市政协,省会城市,山东省</t>
+          <t>地级政协,肇庆市,市政协,广东省</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>访问官网 - zqzx.gov.cn</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>https://zqzx.gov.cn/index.html</t>
         </is>
       </c>
       <c r="AF288" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289">
@@ -17493,7 +17388,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E289" t="n">
@@ -17501,16 +17396,31 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>杭州市政协</t>
+          <t>潮州市政协</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>中国人民政治协商会议潮州市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>杭州市,副省级城市政协,省会城市,浙江省</t>
+          <t>地级政协,潮州市,市政协,广东省</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>访问官网 - czzx.gov.cn</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>https://czzx.gov.cn/</t>
         </is>
       </c>
       <c r="AF289" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290">
@@ -17526,7 +17436,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E290" t="n">
@@ -17534,16 +17444,31 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>大连市政协</t>
+          <t>揭阳市政协</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>中国人民政治协商会议揭阳市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>大连市,副省级城市政协,计划单列市,辽宁省</t>
+          <t>地级政协,揭阳市,市政协,广东省</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>访问官网 - www.jieyangzhengxie.gov.cn/</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jieyangzhengxie.gov.cn/ </t>
         </is>
       </c>
       <c r="AF290" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291">
@@ -17559,7 +17484,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E291" t="n">
@@ -17567,16 +17492,31 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>青岛市政协</t>
+          <t>云浮市政协</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>中国人民政治协商会议云浮市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>青岛市,副省级城市政协,计划单列市,山东省</t>
+          <t>地级政协,云浮市,市政协,广东省</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>访问官网 - zx.yunfu.gov.cn</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>https://zx.yunfu.gov.cn/</t>
         </is>
       </c>
       <c r="AF291" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292">
@@ -17592,7 +17532,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E292" t="n">
@@ -17600,16 +17540,16 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>厦门市政协</t>
+          <t>清远市政协</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>厦门市,副省级城市政协,计划单列市,福建省</t>
+          <t>地级政协,清远市,市政协,广东省</t>
         </is>
       </c>
       <c r="AF292" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293">
@@ -17625,7 +17565,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>政协</t>
+          <t>地级政协</t>
         </is>
       </c>
       <c r="E293" t="n">
@@ -17633,16 +17573,16 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>宁波市政协</t>
+          <t>石家庄市政协</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>宁波市,副省级城市政协,计划单列市,浙江省</t>
+          <t>地级政协,石家庄市,市政协,河北省</t>
         </is>
       </c>
       <c r="AF293" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="294">
@@ -17666,12 +17606,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>清远市政协</t>
+          <t>唐山市政协</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>地级政协,清远市,市政协,广东省</t>
+          <t>地级政协,唐山市,市政协,河北省</t>
         </is>
       </c>
       <c r="AF294" t="b">
@@ -17699,12 +17639,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>石家庄市政协</t>
+          <t>秦皇岛市政协</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>地级政协,石家庄市,市政协,河北省</t>
+          <t>地级政协,秦皇岛市,市政协,河北省</t>
         </is>
       </c>
       <c r="AF295" t="b">
@@ -17732,12 +17672,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>唐山市政协</t>
+          <t>邯郸市政协</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>地级政协,唐山市,市政协,河北省</t>
+          <t>地级政协,邯郸市,市政协,河北省</t>
         </is>
       </c>
       <c r="AF296" t="b">
@@ -17765,12 +17705,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>秦皇岛市政协</t>
+          <t>邢台市政协</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>地级政协,秦皇岛市,市政协,河北省</t>
+          <t>地级政协,邢台市,市政协,河北省</t>
         </is>
       </c>
       <c r="AF297" t="b">
@@ -17798,12 +17738,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>邯郸市政协</t>
+          <t>保定市政协</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>地级政协,邯郸市,市政协,河北省</t>
+          <t>地级政协,保定市,市政协,河北省</t>
         </is>
       </c>
       <c r="AF298" t="b">
@@ -17831,12 +17771,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>邢台市政协</t>
+          <t>张家口市政协</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>地级政协,邢台市,市政协,河北省</t>
+          <t>地级政协,张家口市,市政协,河北省</t>
         </is>
       </c>
       <c r="AF299" t="b">
@@ -17864,12 +17804,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>保定市政协</t>
+          <t>承德市政协</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>地级政协,保定市,市政协,河北省</t>
+          <t>地级政协,承德市,市政协,河北省</t>
         </is>
       </c>
       <c r="AF300" t="b">
@@ -17897,12 +17837,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>张家口市政协</t>
+          <t>沧州市政协</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>地级政协,张家口市,市政协,河北省</t>
+          <t>地级政协,沧州市,市政协,河北省</t>
         </is>
       </c>
       <c r="AF301" t="b">
@@ -17930,12 +17870,12 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>承德市政协</t>
+          <t>廊坊市政协</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>地级政协,承德市,市政协,河北省</t>
+          <t>地级政协,廊坊市,市政协,河北省</t>
         </is>
       </c>
       <c r="AF302" t="b">
@@ -17963,12 +17903,12 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>沧州市政协</t>
+          <t>衡水市政协</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>地级政协,沧州市,市政协,河北省</t>
+          <t>地级政协,衡水市,市政协,河北省</t>
         </is>
       </c>
       <c r="AF303" t="b">
@@ -17996,12 +17936,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>廊坊市政协</t>
+          <t>太原市政协</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>地级政协,廊坊市,市政协,河北省</t>
+          <t>地级政协,太原市,市政协,山西省</t>
         </is>
       </c>
       <c r="AF304" t="b">
@@ -18029,12 +17969,12 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>衡水市政协</t>
+          <t>大同市政协</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>地级政协,衡水市,市政协,河北省</t>
+          <t>地级政协,大同市,市政协,山西省</t>
         </is>
       </c>
       <c r="AF305" t="b">
@@ -18062,12 +18002,12 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>太原市政协</t>
+          <t>阳泉市政协</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>地级政协,太原市,市政协,山西省</t>
+          <t>地级政协,阳泉市,市政协,山西省</t>
         </is>
       </c>
       <c r="AF306" t="b">
@@ -18095,12 +18035,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>大同市政协</t>
+          <t>长治市政协</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>地级政协,大同市,市政协,山西省</t>
+          <t>地级政协,长治市,市政协,山西省</t>
         </is>
       </c>
       <c r="AF307" t="b">
@@ -18128,12 +18068,12 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>阳泉市政协</t>
+          <t>晋城市政协</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>地级政协,阳泉市,市政协,山西省</t>
+          <t>地级政协,晋城市,市政协,山西省</t>
         </is>
       </c>
       <c r="AF308" t="b">
@@ -18161,12 +18101,12 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>长治市政协</t>
+          <t>朔州市政协</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>地级政协,长治市,市政协,山西省</t>
+          <t>地级政协,朔州市,市政协,山西省</t>
         </is>
       </c>
       <c r="AF309" t="b">
@@ -18194,12 +18134,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>晋城市政协</t>
+          <t>晋中市政协</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>地级政协,晋城市,市政协,山西省</t>
+          <t>地级政协,晋中市,市政协,山西省</t>
         </is>
       </c>
       <c r="AF310" t="b">
@@ -18227,12 +18167,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>朔州市政协</t>
+          <t>运城市政协</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>地级政协,朔州市,市政协,山西省</t>
+          <t>地级政协,运城市,市政协,山西省</t>
         </is>
       </c>
       <c r="AF311" t="b">
@@ -18260,12 +18200,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>晋中市政协</t>
+          <t>忻州市政协</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>地级政协,晋中市,市政协,山西省</t>
+          <t>地级政协,忻州市,市政协,山西省</t>
         </is>
       </c>
       <c r="AF312" t="b">
@@ -18293,12 +18233,12 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>运城市政协</t>
+          <t>临汾市政协</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>地级政协,运城市,市政协,山西省</t>
+          <t>地级政协,临汾市,市政协,山西省</t>
         </is>
       </c>
       <c r="AF313" t="b">
@@ -18326,12 +18266,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>忻州市政协</t>
+          <t>吕梁市政协</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>地级政协,忻州市,市政协,山西省</t>
+          <t>地级政协,吕梁市,市政协,山西省</t>
         </is>
       </c>
       <c r="AF314" t="b">
@@ -18359,12 +18299,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>临汾市政协</t>
+          <t>呼和浩特市政协</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>地级政协,临汾市,市政协,山西省</t>
+          <t>地级政协,呼和浩特市,市政协,内蒙古自治区</t>
         </is>
       </c>
       <c r="AF315" t="b">
@@ -18392,12 +18332,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>吕梁市政协</t>
+          <t>包头市政协</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>地级政协,吕梁市,市政协,山西省</t>
+          <t>地级政协,包头市,市政协,内蒙古自治区</t>
         </is>
       </c>
       <c r="AF316" t="b">
@@ -18425,12 +18365,12 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>呼和浩特市政协</t>
+          <t>乌海市政协</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>地级政协,呼和浩特市,市政协,内蒙古自治区</t>
+          <t>地级政协,乌海市,市政协,内蒙古自治区</t>
         </is>
       </c>
       <c r="AF317" t="b">
@@ -18458,12 +18398,12 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>包头市政协</t>
+          <t>赤峰市政协</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>地级政协,包头市,市政协,内蒙古自治区</t>
+          <t>地级政协,赤峰市,市政协,内蒙古自治区</t>
         </is>
       </c>
       <c r="AF318" t="b">
@@ -18491,12 +18431,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>乌海市政协</t>
+          <t>通辽市政协</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>地级政协,乌海市,市政协,内蒙古自治区</t>
+          <t>地级政协,通辽市,市政协,内蒙古自治区</t>
         </is>
       </c>
       <c r="AF319" t="b">
@@ -18524,12 +18464,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>赤峰市政协</t>
+          <t>鄂尔多斯市政协</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>地级政协,赤峰市,市政协,内蒙古自治区</t>
+          <t>地级政协,鄂尔多斯市,市政协,内蒙古自治区</t>
         </is>
       </c>
       <c r="AF320" t="b">
@@ -18557,12 +18497,12 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>通辽市政协</t>
+          <t>呼伦贝尔市政协</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>地级政协,通辽市,市政协,内蒙古自治区</t>
+          <t>地级政协,呼伦贝尔市,市政协,内蒙古自治区</t>
         </is>
       </c>
       <c r="AF321" t="b">
@@ -18590,12 +18530,12 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>鄂尔多斯市政协</t>
+          <t>巴彦淖尔市政协</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>地级政协,鄂尔多斯市,市政协,内蒙古自治区</t>
+          <t>地级政协,巴彦淖尔市,市政协,内蒙古自治区</t>
         </is>
       </c>
       <c r="AF322" t="b">
@@ -18623,12 +18563,12 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>呼伦贝尔市政协</t>
+          <t>乌兰察布市政协</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>地级政协,呼伦贝尔市,市政协,内蒙古自治区</t>
+          <t>地级政协,乌兰察布市,市政协,内蒙古自治区</t>
         </is>
       </c>
       <c r="AF323" t="b">
@@ -18656,12 +18596,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>巴彦淖尔市政协</t>
+          <t>鞍山市政协</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>地级政协,巴彦淖尔市,市政协,内蒙古自治区</t>
+          <t>地级政协,鞍山市,市政协,辽宁省</t>
         </is>
       </c>
       <c r="AF324" t="b">
@@ -18689,12 +18629,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>乌兰察布市政协</t>
+          <t>抚顺市政协</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>地级政协,乌兰察布市,市政协,内蒙古自治区</t>
+          <t>地级政协,抚顺市,市政协,辽宁省</t>
         </is>
       </c>
       <c r="AF325" t="b">
@@ -18722,12 +18662,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>鞍山市政协</t>
+          <t>本溪市政协</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>地级政协,鞍山市,市政协,辽宁省</t>
+          <t>地级政协,本溪市,市政协,辽宁省</t>
         </is>
       </c>
       <c r="AF326" t="b">
@@ -18755,12 +18695,12 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>抚顺市政协</t>
+          <t>丹东市政协</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>地级政协,抚顺市,市政协,辽宁省</t>
+          <t>地级政协,丹东市,市政协,辽宁省</t>
         </is>
       </c>
       <c r="AF327" t="b">
@@ -18788,12 +18728,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>本溪市政协</t>
+          <t>锦州市政协</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>地级政协,本溪市,市政协,辽宁省</t>
+          <t>地级政协,锦州市,市政协,辽宁省</t>
         </is>
       </c>
       <c r="AF328" t="b">
@@ -18821,12 +18761,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>丹东市政协</t>
+          <t>营口市政协</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>地级政协,丹东市,市政协,辽宁省</t>
+          <t>地级政协,营口市,市政协,辽宁省</t>
         </is>
       </c>
       <c r="AF329" t="b">
@@ -18854,12 +18794,12 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>锦州市政协</t>
+          <t>阜新市政协</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>地级政协,锦州市,市政协,辽宁省</t>
+          <t>地级政协,阜新市,市政协,辽宁省</t>
         </is>
       </c>
       <c r="AF330" t="b">
@@ -18887,12 +18827,12 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>营口市政协</t>
+          <t>辽阳市政协</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>地级政协,营口市,市政协,辽宁省</t>
+          <t>地级政协,辽阳市,市政协,辽宁省</t>
         </is>
       </c>
       <c r="AF331" t="b">
@@ -18920,12 +18860,12 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>阜新市政协</t>
+          <t>盘锦市政协</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>地级政协,阜新市,市政协,辽宁省</t>
+          <t>地级政协,盘锦市,市政协,辽宁省</t>
         </is>
       </c>
       <c r="AF332" t="b">
@@ -18953,12 +18893,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>辽阳市政协</t>
+          <t>铁岭市政协</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>地级政协,辽阳市,市政协,辽宁省</t>
+          <t>地级政协,铁岭市,市政协,辽宁省</t>
         </is>
       </c>
       <c r="AF333" t="b">
@@ -18986,12 +18926,12 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>盘锦市政协</t>
+          <t>朝阳市政协</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>地级政协,盘锦市,市政协,辽宁省</t>
+          <t>地级政协,朝阳市,市政协,辽宁省</t>
         </is>
       </c>
       <c r="AF334" t="b">
@@ -19019,12 +18959,12 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>铁岭市政协</t>
+          <t>葫芦岛市政协</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>地级政协,铁岭市,市政协,辽宁省</t>
+          <t>地级政协,葫芦岛市,市政协,辽宁省</t>
         </is>
       </c>
       <c r="AF335" t="b">
@@ -19052,12 +18992,12 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>朝阳市政协</t>
+          <t>吉林市政协</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>地级政协,朝阳市,市政协,辽宁省</t>
+          <t>地级政协,吉林市,市政协,吉林省</t>
         </is>
       </c>
       <c r="AF336" t="b">
@@ -19085,12 +19025,12 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>葫芦岛市政协</t>
+          <t>四平市政协</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>地级政协,葫芦岛市,市政协,辽宁省</t>
+          <t>地级政协,四平市,市政协,吉林省</t>
         </is>
       </c>
       <c r="AF337" t="b">
@@ -19118,12 +19058,12 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>吉林市政协</t>
+          <t>辽源市政协</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>地级政协,吉林市,市政协,吉林省</t>
+          <t>地级政协,辽源市,市政协,吉林省</t>
         </is>
       </c>
       <c r="AF338" t="b">
@@ -19151,12 +19091,12 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>四平市政协</t>
+          <t>通化市政协</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>地级政协,四平市,市政协,吉林省</t>
+          <t>地级政协,通化市,市政协,吉林省</t>
         </is>
       </c>
       <c r="AF339" t="b">
@@ -19184,12 +19124,12 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>辽源市政协</t>
+          <t>白山市政协</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>地级政协,辽源市,市政协,吉林省</t>
+          <t>地级政协,白山市,市政协,吉林省</t>
         </is>
       </c>
       <c r="AF340" t="b">
@@ -19217,12 +19157,12 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>通化市政协</t>
+          <t>松原市政协</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>地级政协,通化市,市政协,吉林省</t>
+          <t>地级政协,松原市,市政协,吉林省</t>
         </is>
       </c>
       <c r="AF341" t="b">
@@ -19250,12 +19190,12 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>白山市政协</t>
+          <t>白城市政协</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>地级政协,白山市,市政协,吉林省</t>
+          <t>地级政协,白城市,市政协,吉林省</t>
         </is>
       </c>
       <c r="AF342" t="b">
@@ -19283,12 +19223,12 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>松原市政协</t>
+          <t>齐齐哈尔市政协</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>地级政协,松原市,市政协,吉林省</t>
+          <t>地级政协,齐齐哈尔市,市政协,黑龙江省</t>
         </is>
       </c>
       <c r="AF343" t="b">
@@ -19316,12 +19256,12 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>白城市政协</t>
+          <t>鸡西市政协</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>地级政协,白城市,市政协,吉林省</t>
+          <t>地级政协,鸡西市,市政协,黑龙江省</t>
         </is>
       </c>
       <c r="AF344" t="b">
@@ -19349,12 +19289,12 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>齐齐哈尔市政协</t>
+          <t>鹤岗市政协</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>地级政协,齐齐哈尔市,市政协,黑龙江省</t>
+          <t>地级政协,鹤岗市,市政协,黑龙江省</t>
         </is>
       </c>
       <c r="AF345" t="b">
@@ -19382,12 +19322,12 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>鸡西市政协</t>
+          <t>双鸭山市政协</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>地级政协,鸡西市,市政协,黑龙江省</t>
+          <t>地级政协,双鸭山市,市政协,黑龙江省</t>
         </is>
       </c>
       <c r="AF346" t="b">
@@ -19415,12 +19355,12 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>鹤岗市政协</t>
+          <t>大庆市政协</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>地级政协,鹤岗市,市政协,黑龙江省</t>
+          <t>地级政协,大庆市,市政协,黑龙江省</t>
         </is>
       </c>
       <c r="AF347" t="b">
@@ -19448,12 +19388,12 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>双鸭山市政协</t>
+          <t>伊春市政协</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>地级政协,双鸭山市,市政协,黑龙江省</t>
+          <t>地级政协,伊春市,市政协,黑龙江省</t>
         </is>
       </c>
       <c r="AF348" t="b">
@@ -19481,12 +19421,12 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>大庆市政协</t>
+          <t>佳木斯市政协</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>地级政协,大庆市,市政协,黑龙江省</t>
+          <t>地级政协,佳木斯市,市政协,黑龙江省</t>
         </is>
       </c>
       <c r="AF349" t="b">
@@ -19514,12 +19454,12 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>伊春市政协</t>
+          <t>七台河市政协</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>地级政协,伊春市,市政协,黑龙江省</t>
+          <t>地级政协,七台河市,市政协,黑龙江省</t>
         </is>
       </c>
       <c r="AF350" t="b">
@@ -19547,12 +19487,12 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>佳木斯市政协</t>
+          <t>牡丹江市政协</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>地级政协,佳木斯市,市政协,黑龙江省</t>
+          <t>地级政协,牡丹江市,市政协,黑龙江省</t>
         </is>
       </c>
       <c r="AF351" t="b">
@@ -19580,12 +19520,12 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>七台河市政协</t>
+          <t>黑河市政协</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>地级政协,七台河市,市政协,黑龙江省</t>
+          <t>地级政协,黑河市,市政协,黑龙江省</t>
         </is>
       </c>
       <c r="AF352" t="b">
@@ -19613,12 +19553,12 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>牡丹江市政协</t>
+          <t>绥化市政协</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>地级政协,牡丹江市,市政协,黑龙江省</t>
+          <t>地级政协,绥化市,市政协,黑龙江省</t>
         </is>
       </c>
       <c r="AF353" t="b">
@@ -19646,12 +19586,12 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>黑河市政协</t>
+          <t>无锡市政协</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>地级政协,黑河市,市政协,黑龙江省</t>
+          <t>地级政协,无锡市,市政协,江苏省</t>
         </is>
       </c>
       <c r="AF354" t="b">
@@ -19679,12 +19619,12 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>绥化市政协</t>
+          <t>徐州市政协</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>地级政协,绥化市,市政协,黑龙江省</t>
+          <t>地级政协,徐州市,市政协,江苏省</t>
         </is>
       </c>
       <c r="AF355" t="b">
@@ -19712,12 +19652,12 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>无锡市政协</t>
+          <t>常州市政协</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>地级政协,无锡市,市政协,江苏省</t>
+          <t>地级政协,常州市,市政协,江苏省</t>
         </is>
       </c>
       <c r="AF356" t="b">
@@ -19745,12 +19685,12 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>徐州市政协</t>
+          <t>苏州市政协</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>地级政协,徐州市,市政协,江苏省</t>
+          <t>地级政协,苏州市,市政协,江苏省</t>
         </is>
       </c>
       <c r="AF357" t="b">
@@ -19778,12 +19718,12 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>常州市政协</t>
+          <t>南通市政协</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>地级政协,常州市,市政协,江苏省</t>
+          <t>地级政协,南通市,市政协,江苏省</t>
         </is>
       </c>
       <c r="AF358" t="b">
@@ -19811,12 +19751,12 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>苏州市政协</t>
+          <t>连云港市政协</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>地级政协,苏州市,市政协,江苏省</t>
+          <t>地级政协,连云港市,市政协,江苏省</t>
         </is>
       </c>
       <c r="AF359" t="b">
@@ -19844,12 +19784,12 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>南通市政协</t>
+          <t>淮安市政协</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>地级政协,南通市,市政协,江苏省</t>
+          <t>地级政协,淮安市,市政协,江苏省</t>
         </is>
       </c>
       <c r="AF360" t="b">
@@ -19877,12 +19817,12 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>连云港市政协</t>
+          <t>盐城市政协</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>地级政协,连云港市,市政协,江苏省</t>
+          <t>地级政协,盐城市,市政协,江苏省</t>
         </is>
       </c>
       <c r="AF361" t="b">
@@ -19910,12 +19850,12 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>淮安市政协</t>
+          <t>扬州市政协</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>地级政协,淮安市,市政协,江苏省</t>
+          <t>地级政协,扬州市,市政协,江苏省</t>
         </is>
       </c>
       <c r="AF362" t="b">
@@ -19943,12 +19883,12 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>盐城市政协</t>
+          <t>镇江市政协</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>地级政协,盐城市,市政协,江苏省</t>
+          <t>地级政协,镇江市,市政协,江苏省</t>
         </is>
       </c>
       <c r="AF363" t="b">
@@ -19976,12 +19916,12 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>扬州市政协</t>
+          <t>泰州市政协</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>地级政协,扬州市,市政协,江苏省</t>
+          <t>地级政协,泰州市,市政协,江苏省</t>
         </is>
       </c>
       <c r="AF364" t="b">
@@ -20009,12 +19949,12 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>镇江市政协</t>
+          <t>宿迁市政协</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>地级政协,镇江市,市政协,江苏省</t>
+          <t>地级政协,宿迁市,市政协,江苏省</t>
         </is>
       </c>
       <c r="AF365" t="b">
@@ -20042,12 +19982,12 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>泰州市政协</t>
+          <t>温州市政协</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>地级政协,泰州市,市政协,江苏省</t>
+          <t>地级政协,温州市,市政协,浙江省</t>
         </is>
       </c>
       <c r="AF366" t="b">
@@ -20075,12 +20015,12 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>宿迁市政协</t>
+          <t>嘉兴市政协</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>地级政协,宿迁市,市政协,江苏省</t>
+          <t>地级政协,嘉兴市,市政协,浙江省</t>
         </is>
       </c>
       <c r="AF367" t="b">
@@ -20108,12 +20048,12 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>温州市政协</t>
+          <t>湖州市政协</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>地级政协,温州市,市政协,浙江省</t>
+          <t>地级政协,湖州市,市政协,浙江省</t>
         </is>
       </c>
       <c r="AF368" t="b">
@@ -20141,12 +20081,12 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>嘉兴市政协</t>
+          <t>绍兴市政协</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>地级政协,嘉兴市,市政协,浙江省</t>
+          <t>地级政协,绍兴市,市政协,浙江省</t>
         </is>
       </c>
       <c r="AF369" t="b">
@@ -20174,12 +20114,12 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>湖州市政协</t>
+          <t>金华市政协</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>地级政协,湖州市,市政协,浙江省</t>
+          <t>地级政协,金华市,市政协,浙江省</t>
         </is>
       </c>
       <c r="AF370" t="b">
@@ -20207,12 +20147,12 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>绍兴市政协</t>
+          <t>衢州市政协</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>地级政协,绍兴市,市政协,浙江省</t>
+          <t>地级政协,衢州市,市政协,浙江省</t>
         </is>
       </c>
       <c r="AF371" t="b">
@@ -20240,12 +20180,12 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>金华市政协</t>
+          <t>舟山市政协</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>地级政协,金华市,市政协,浙江省</t>
+          <t>地级政协,舟山市,市政协,浙江省</t>
         </is>
       </c>
       <c r="AF372" t="b">
@@ -20273,12 +20213,12 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>衢州市政协</t>
+          <t>台州市政协</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>地级政协,衢州市,市政协,浙江省</t>
+          <t>地级政协,台州市,市政协,浙江省</t>
         </is>
       </c>
       <c r="AF373" t="b">
@@ -20306,12 +20246,12 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>舟山市政协</t>
+          <t>丽水市政协</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>地级政协,舟山市,市政协,浙江省</t>
+          <t>地级政协,丽水市,市政协,浙江省</t>
         </is>
       </c>
       <c r="AF374" t="b">
@@ -20339,12 +20279,12 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>台州市政协</t>
+          <t>合肥市政协</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>地级政协,台州市,市政协,浙江省</t>
+          <t>地级政协,合肥市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF375" t="b">
@@ -20372,12 +20312,12 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>丽水市政协</t>
+          <t>芜湖市政协</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>地级政协,丽水市,市政协,浙江省</t>
+          <t>地级政协,芜湖市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF376" t="b">
@@ -20405,12 +20345,12 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>合肥市政协</t>
+          <t>蚌埠市政协</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>地级政协,合肥市,市政协,安徽省</t>
+          <t>地级政协,蚌埠市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF377" t="b">
@@ -20438,12 +20378,12 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>芜湖市政协</t>
+          <t>淮南市政协</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>地级政协,芜湖市,市政协,安徽省</t>
+          <t>地级政协,淮南市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF378" t="b">
@@ -20471,12 +20411,12 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>蚌埠市政协</t>
+          <t>马鞍山市政协</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>地级政协,蚌埠市,市政协,安徽省</t>
+          <t>地级政协,马鞍山市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF379" t="b">
@@ -20504,12 +20444,12 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>淮南市政协</t>
+          <t>淮北市政协</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>地级政协,淮南市,市政协,安徽省</t>
+          <t>地级政协,淮北市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF380" t="b">
@@ -20537,12 +20477,12 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>马鞍山市政协</t>
+          <t>铜陵市政协</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>地级政协,马鞍山市,市政协,安徽省</t>
+          <t>地级政协,铜陵市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF381" t="b">
@@ -20570,12 +20510,12 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>淮北市政协</t>
+          <t>安庆市政协</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>地级政协,淮北市,市政协,安徽省</t>
+          <t>地级政协,安庆市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF382" t="b">
@@ -20603,12 +20543,12 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>铜陵市政协</t>
+          <t>黄山市政协</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>地级政协,铜陵市,市政协,安徽省</t>
+          <t>地级政协,黄山市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF383" t="b">
@@ -20636,12 +20576,12 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>安庆市政协</t>
+          <t>滁州市政协</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>地级政协,安庆市,市政协,安徽省</t>
+          <t>地级政协,滁州市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF384" t="b">
@@ -20669,12 +20609,12 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>黄山市政协</t>
+          <t>阜阳市政协</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>地级政协,黄山市,市政协,安徽省</t>
+          <t>地级政协,阜阳市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF385" t="b">
@@ -20702,12 +20642,12 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>滁州市政协</t>
+          <t>宿州市政协</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>地级政协,滁州市,市政协,安徽省</t>
+          <t>地级政协,宿州市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF386" t="b">
@@ -20735,12 +20675,12 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>阜阳市政协</t>
+          <t>六安市政协</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>地级政协,阜阳市,市政协,安徽省</t>
+          <t>地级政协,六安市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF387" t="b">
@@ -20768,12 +20708,12 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>宿州市政协</t>
+          <t>亳州市政协</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>地级政协,宿州市,市政协,安徽省</t>
+          <t>地级政协,亳州市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF388" t="b">
@@ -20801,12 +20741,12 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>六安市政协</t>
+          <t>池州市政协</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>地级政协,六安市,市政协,安徽省</t>
+          <t>地级政协,池州市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF389" t="b">
@@ -20834,12 +20774,12 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>亳州市政协</t>
+          <t>宣城市政协</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>地级政协,亳州市,市政协,安徽省</t>
+          <t>地级政协,宣城市,市政协,安徽省</t>
         </is>
       </c>
       <c r="AF390" t="b">
@@ -20867,12 +20807,12 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>池州市政协</t>
+          <t>福州市政协</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>地级政协,池州市,市政协,安徽省</t>
+          <t>地级政协,福州市,市政协,福建省</t>
         </is>
       </c>
       <c r="AF391" t="b">
@@ -20900,12 +20840,12 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>宣城市政协</t>
+          <t>莆田市政协</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>地级政协,宣城市,市政协,安徽省</t>
+          <t>地级政协,莆田市,市政协,福建省</t>
         </is>
       </c>
       <c r="AF392" t="b">
@@ -20933,12 +20873,12 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>福州市政协</t>
+          <t>三明市政协</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>地级政协,福州市,市政协,福建省</t>
+          <t>地级政协,三明市,市政协,福建省</t>
         </is>
       </c>
       <c r="AF393" t="b">
@@ -20966,12 +20906,12 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>莆田市政协</t>
+          <t>泉州市政协</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>地级政协,莆田市,市政协,福建省</t>
+          <t>地级政协,泉州市,市政协,福建省</t>
         </is>
       </c>
       <c r="AF394" t="b">
@@ -20999,12 +20939,12 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>三明市政协</t>
+          <t>漳州市政协</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>地级政协,三明市,市政协,福建省</t>
+          <t>地级政协,漳州市,市政协,福建省</t>
         </is>
       </c>
       <c r="AF395" t="b">
@@ -21032,12 +20972,12 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>泉州市政协</t>
+          <t>南平市政协</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>地级政协,泉州市,市政协,福建省</t>
+          <t>地级政协,南平市,市政协,福建省</t>
         </is>
       </c>
       <c r="AF396" t="b">
@@ -21065,12 +21005,12 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>漳州市政协</t>
+          <t>龙岩市政协</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>地级政协,漳州市,市政协,福建省</t>
+          <t>地级政协,龙岩市,市政协,福建省</t>
         </is>
       </c>
       <c r="AF397" t="b">
@@ -21098,12 +21038,12 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>南平市政协</t>
+          <t>宁德市政协</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>地级政协,南平市,市政协,福建省</t>
+          <t>地级政协,宁德市,市政协,福建省</t>
         </is>
       </c>
       <c r="AF398" t="b">
@@ -21131,12 +21071,12 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>龙岩市政协</t>
+          <t>南昌市政协</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>地级政协,龙岩市,市政协,福建省</t>
+          <t>地级政协,南昌市,市政协,江西省</t>
         </is>
       </c>
       <c r="AF399" t="b">
@@ -21164,12 +21104,12 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>宁德市政协</t>
+          <t>景德镇市政协</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>地级政协,宁德市,市政协,福建省</t>
+          <t>地级政协,景德镇市,市政协,江西省</t>
         </is>
       </c>
       <c r="AF400" t="b">
@@ -21197,12 +21137,12 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>南昌市政协</t>
+          <t>萍乡市政协</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>地级政协,南昌市,市政协,江西省</t>
+          <t>地级政协,萍乡市,市政协,江西省</t>
         </is>
       </c>
       <c r="AF401" t="b">
@@ -21230,12 +21170,12 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>景德镇市政协</t>
+          <t>九江市政协</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>地级政协,景德镇市,市政协,江西省</t>
+          <t>地级政协,九江市,市政协,江西省</t>
         </is>
       </c>
       <c r="AF402" t="b">
@@ -21263,12 +21203,12 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>萍乡市政协</t>
+          <t>新余市政协</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>地级政协,萍乡市,市政协,江西省</t>
+          <t>地级政协,新余市,市政协,江西省</t>
         </is>
       </c>
       <c r="AF403" t="b">
@@ -21296,12 +21236,12 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>九江市政协</t>
+          <t>鹰潭市政协</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>地级政协,九江市,市政协,江西省</t>
+          <t>地级政协,鹰潭市,市政协,江西省</t>
         </is>
       </c>
       <c r="AF404" t="b">
@@ -21329,12 +21269,12 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>新余市政协</t>
+          <t>赣州市政协</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>地级政协,新余市,市政协,江西省</t>
+          <t>地级政协,赣州市,市政协,江西省</t>
         </is>
       </c>
       <c r="AF405" t="b">
@@ -21362,12 +21302,12 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>鹰潭市政协</t>
+          <t>吉安市政协</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>地级政协,鹰潭市,市政协,江西省</t>
+          <t>地级政协,吉安市,市政协,江西省</t>
         </is>
       </c>
       <c r="AF406" t="b">
@@ -21395,12 +21335,12 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>赣州市政协</t>
+          <t>宜春市政协</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>地级政协,赣州市,市政协,江西省</t>
+          <t>地级政协,宜春市,市政协,江西省</t>
         </is>
       </c>
       <c r="AF407" t="b">
@@ -21428,12 +21368,12 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>吉安市政协</t>
+          <t>抚州市政协</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>地级政协,吉安市,市政协,江西省</t>
+          <t>地级政协,抚州市,市政协,江西省</t>
         </is>
       </c>
       <c r="AF408" t="b">
@@ -21461,12 +21401,12 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>宜春市政协</t>
+          <t>上饶市政协</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>地级政协,宜春市,市政协,江西省</t>
+          <t>地级政协,上饶市,市政协,江西省</t>
         </is>
       </c>
       <c r="AF409" t="b">
@@ -21494,12 +21434,12 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>抚州市政协</t>
+          <t>淄博市政协</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>地级政协,抚州市,市政协,江西省</t>
+          <t>地级政协,淄博市,市政协,山东省</t>
         </is>
       </c>
       <c r="AF410" t="b">
@@ -21527,12 +21467,12 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>上饶市政协</t>
+          <t>枣庄市政协</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>地级政协,上饶市,市政协,江西省</t>
+          <t>地级政协,枣庄市,市政协,山东省</t>
         </is>
       </c>
       <c r="AF411" t="b">
@@ -21560,12 +21500,12 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>淄博市政协</t>
+          <t>东营市政协</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>地级政协,淄博市,市政协,山东省</t>
+          <t>地级政协,东营市,市政协,山东省</t>
         </is>
       </c>
       <c r="AF412" t="b">
@@ -21593,12 +21533,12 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>枣庄市政协</t>
+          <t>烟台市政协</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>地级政协,枣庄市,市政协,山东省</t>
+          <t>地级政协,烟台市,市政协,山东省</t>
         </is>
       </c>
       <c r="AF413" t="b">
@@ -21626,12 +21566,12 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>东营市政协</t>
+          <t>潍坊市政协</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>地级政协,东营市,市政协,山东省</t>
+          <t>地级政协,潍坊市,市政协,山东省</t>
         </is>
       </c>
       <c r="AF414" t="b">
@@ -21659,12 +21599,12 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>烟台市政协</t>
+          <t>济宁市政协</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>地级政协,烟台市,市政协,山东省</t>
+          <t>地级政协,济宁市,市政协,山东省</t>
         </is>
       </c>
       <c r="AF415" t="b">
@@ -21692,12 +21632,12 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>潍坊市政协</t>
+          <t>泰安市政协</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>地级政协,潍坊市,市政协,山东省</t>
+          <t>地级政协,泰安市,市政协,山东省</t>
         </is>
       </c>
       <c r="AF416" t="b">
@@ -21725,12 +21665,12 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>济宁市政协</t>
+          <t>威海市政协</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>地级政协,济宁市,市政协,山东省</t>
+          <t>地级政协,威海市,市政协,山东省</t>
         </is>
       </c>
       <c r="AF417" t="b">
@@ -21758,12 +21698,12 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>泰安市政协</t>
+          <t>日照市政协</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>地级政协,泰安市,市政协,山东省</t>
+          <t>地级政协,日照市,市政协,山东省</t>
         </is>
       </c>
       <c r="AF418" t="b">
@@ -21791,12 +21731,12 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>威海市政协</t>
+          <t>临沂市政协</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>地级政协,威海市,市政协,山东省</t>
+          <t>地级政协,临沂市,市政协,山东省</t>
         </is>
       </c>
       <c r="AF419" t="b">
@@ -21824,12 +21764,12 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>日照市政协</t>
+          <t>德州市政协</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>地级政协,日照市,市政协,山东省</t>
+          <t>地级政协,德州市,市政协,山东省</t>
         </is>
       </c>
       <c r="AF420" t="b">
@@ -21857,12 +21797,12 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>临沂市政协</t>
+          <t>聊城市政协</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>地级政协,临沂市,市政协,山东省</t>
+          <t>地级政协,聊城市,市政协,山东省</t>
         </is>
       </c>
       <c r="AF421" t="b">
@@ -21890,12 +21830,12 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>德州市政协</t>
+          <t>滨州市政协</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>地级政协,德州市,市政协,山东省</t>
+          <t>地级政协,滨州市,市政协,山东省</t>
         </is>
       </c>
       <c r="AF422" t="b">
@@ -21923,12 +21863,12 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>聊城市政协</t>
+          <t>菏泽市政协</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>地级政协,聊城市,市政协,山东省</t>
+          <t>地级政协,菏泽市,市政协,山东省</t>
         </is>
       </c>
       <c r="AF423" t="b">
@@ -21956,12 +21896,12 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>滨州市政协</t>
+          <t>郑州市政协</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>地级政协,滨州市,市政协,山东省</t>
+          <t>地级政协,郑州市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF424" t="b">
@@ -21989,12 +21929,12 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>菏泽市政协</t>
+          <t>开封市政协</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>地级政协,菏泽市,市政协,山东省</t>
+          <t>地级政协,开封市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF425" t="b">
@@ -22022,12 +21962,12 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>郑州市政协</t>
+          <t>洛阳市政协</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>地级政协,郑州市,市政协,河南省</t>
+          <t>地级政协,洛阳市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF426" t="b">
@@ -22055,12 +21995,12 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>开封市政协</t>
+          <t>平顶山市政协</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>地级政协,开封市,市政协,河南省</t>
+          <t>地级政协,平顶山市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF427" t="b">
@@ -22088,12 +22028,12 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>洛阳市政协</t>
+          <t>安阳市政协</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>地级政协,洛阳市,市政协,河南省</t>
+          <t>地级政协,安阳市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF428" t="b">
@@ -22121,12 +22061,12 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>平顶山市政协</t>
+          <t>鹤壁市政协</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>地级政协,平顶山市,市政协,河南省</t>
+          <t>地级政协,鹤壁市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF429" t="b">
@@ -22154,12 +22094,12 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>安阳市政协</t>
+          <t>新乡市政协</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>地级政协,安阳市,市政协,河南省</t>
+          <t>地级政协,新乡市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF430" t="b">
@@ -22187,12 +22127,12 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>鹤壁市政协</t>
+          <t>焦作市政协</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>地级政协,鹤壁市,市政协,河南省</t>
+          <t>地级政协,焦作市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF431" t="b">
@@ -22220,12 +22160,12 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>新乡市政协</t>
+          <t>濮阳市政协</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>地级政协,新乡市,市政协,河南省</t>
+          <t>地级政协,濮阳市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF432" t="b">
@@ -22253,12 +22193,12 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>焦作市政协</t>
+          <t>许昌市政协</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>地级政协,焦作市,市政协,河南省</t>
+          <t>地级政协,许昌市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF433" t="b">
@@ -22286,12 +22226,12 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>濮阳市政协</t>
+          <t>漯河市政协</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>地级政协,濮阳市,市政协,河南省</t>
+          <t>地级政协,漯河市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF434" t="b">
@@ -22319,12 +22259,12 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>许昌市政协</t>
+          <t>三门峡市政协</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>地级政协,许昌市,市政协,河南省</t>
+          <t>地级政协,三门峡市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF435" t="b">
@@ -22352,12 +22292,12 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>漯河市政协</t>
+          <t>南阳市政协</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>地级政协,漯河市,市政协,河南省</t>
+          <t>地级政协,南阳市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF436" t="b">
@@ -22385,12 +22325,12 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>三门峡市政协</t>
+          <t>商丘市政协</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>地级政协,三门峡市,市政协,河南省</t>
+          <t>地级政协,商丘市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF437" t="b">
@@ -22418,12 +22358,12 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>南阳市政协</t>
+          <t>信阳市政协</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>地级政协,南阳市,市政协,河南省</t>
+          <t>地级政协,信阳市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF438" t="b">
@@ -22451,12 +22391,12 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>商丘市政协</t>
+          <t>周口市政协</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>地级政协,商丘市,市政协,河南省</t>
+          <t>地级政协,周口市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF439" t="b">
@@ -22484,12 +22424,12 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>信阳市政协</t>
+          <t>驻马店市政协</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>地级政协,信阳市,市政协,河南省</t>
+          <t>地级政协,驻马店市,市政协,河南省</t>
         </is>
       </c>
       <c r="AF440" t="b">
@@ -22517,12 +22457,12 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>周口市政协</t>
+          <t>黄石市政协</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>地级政协,周口市,市政协,河南省</t>
+          <t>地级政协,黄石市,市政协,湖北省</t>
         </is>
       </c>
       <c r="AF441" t="b">
@@ -22550,12 +22490,12 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>驻马店市政协</t>
+          <t>十堰市政协</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>地级政协,驻马店市,市政协,河南省</t>
+          <t>地级政协,十堰市,市政协,湖北省</t>
         </is>
       </c>
       <c r="AF442" t="b">
@@ -22583,12 +22523,12 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>黄石市政协</t>
+          <t>宜昌市政协</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>地级政协,黄石市,市政协,湖北省</t>
+          <t>地级政协,宜昌市,市政协,湖北省</t>
         </is>
       </c>
       <c r="AF443" t="b">
@@ -22616,12 +22556,12 @@
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>十堰市政协</t>
+          <t>襄阳市政协</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>地级政协,十堰市,市政协,湖北省</t>
+          <t>地级政协,襄阳市,市政协,湖北省</t>
         </is>
       </c>
       <c r="AF444" t="b">
@@ -22649,12 +22589,12 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>宜昌市政协</t>
+          <t>鄂州市政协</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>地级政协,宜昌市,市政协,湖北省</t>
+          <t>地级政协,鄂州市,市政协,湖北省</t>
         </is>
       </c>
       <c r="AF445" t="b">
@@ -22682,12 +22622,12 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>襄阳市政协</t>
+          <t>荆门市政协</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>地级政协,襄阳市,市政协,湖北省</t>
+          <t>地级政协,荆门市,市政协,湖北省</t>
         </is>
       </c>
       <c r="AF446" t="b">
@@ -22715,12 +22655,12 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>鄂州市政协</t>
+          <t>孝感市政协</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>地级政协,鄂州市,市政协,湖北省</t>
+          <t>地级政协,孝感市,市政协,湖北省</t>
         </is>
       </c>
       <c r="AF447" t="b">
@@ -22748,12 +22688,12 @@
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>荆门市政协</t>
+          <t>荆州市政协</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>地级政协,荆门市,市政协,湖北省</t>
+          <t>地级政协,荆州市,市政协,湖北省</t>
         </is>
       </c>
       <c r="AF448" t="b">
@@ -22781,12 +22721,12 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>孝感市政协</t>
+          <t>黄冈市政协</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>地级政协,孝感市,市政协,湖北省</t>
+          <t>地级政协,黄冈市,市政协,湖北省</t>
         </is>
       </c>
       <c r="AF449" t="b">
@@ -22814,12 +22754,12 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>荆州市政协</t>
+          <t>咸宁市政协</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>地级政协,荆州市,市政协,湖北省</t>
+          <t>地级政协,咸宁市,市政协,湖北省</t>
         </is>
       </c>
       <c r="AF450" t="b">
@@ -22847,12 +22787,12 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>黄冈市政协</t>
+          <t>随州市政协</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>地级政协,黄冈市,市政协,湖北省</t>
+          <t>地级政协,随州市,市政协,湖北省</t>
         </is>
       </c>
       <c r="AF451" t="b">
@@ -22880,12 +22820,12 @@
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>咸宁市政协</t>
+          <t>长沙市政协</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t>地级政协,咸宁市,市政协,湖北省</t>
+          <t>地级政协,长沙市,市政协,湖南省</t>
         </is>
       </c>
       <c r="AF452" t="b">
@@ -22913,12 +22853,12 @@
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>随州市政协</t>
+          <t>株洲市政协</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>地级政协,随州市,市政协,湖北省</t>
+          <t>地级政协,株洲市,市政协,湖南省</t>
         </is>
       </c>
       <c r="AF453" t="b">
@@ -22946,12 +22886,12 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>长沙市政协</t>
+          <t>湘潭市政协</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>地级政协,长沙市,市政协,湖南省</t>
+          <t>地级政协,湘潭市,市政协,湖南省</t>
         </is>
       </c>
       <c r="AF454" t="b">
@@ -22979,12 +22919,12 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>株洲市政协</t>
+          <t>衡阳市政协</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>地级政协,株洲市,市政协,湖南省</t>
+          <t>地级政协,衡阳市,市政协,湖南省</t>
         </is>
       </c>
       <c r="AF455" t="b">
@@ -23012,12 +22952,12 @@
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>湘潭市政协</t>
+          <t>邵阳市政协</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>地级政协,湘潭市,市政协,湖南省</t>
+          <t>地级政协,邵阳市,市政协,湖南省</t>
         </is>
       </c>
       <c r="AF456" t="b">
@@ -23045,12 +22985,12 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>衡阳市政协</t>
+          <t>岳阳市政协</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>地级政协,衡阳市,市政协,湖南省</t>
+          <t>地级政协,岳阳市,市政协,湖南省</t>
         </is>
       </c>
       <c r="AF457" t="b">
@@ -23078,12 +23018,12 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>邵阳市政协</t>
+          <t>常德市政协</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>地级政协,邵阳市,市政协,湖南省</t>
+          <t>地级政协,常德市,市政协,湖南省</t>
         </is>
       </c>
       <c r="AF458" t="b">
@@ -23111,12 +23051,12 @@
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>岳阳市政协</t>
+          <t>张家界市政协</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>地级政协,岳阳市,市政协,湖南省</t>
+          <t>地级政协,张家界市,市政协,湖南省</t>
         </is>
       </c>
       <c r="AF459" t="b">
@@ -23144,12 +23084,12 @@
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>常德市政协</t>
+          <t>益阳市政协</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>地级政协,常德市,市政协,湖南省</t>
+          <t>地级政协,益阳市,市政协,湖南省</t>
         </is>
       </c>
       <c r="AF460" t="b">
@@ -23177,12 +23117,12 @@
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>张家界市政协</t>
+          <t>郴州市政协</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t>地级政协,张家界市,市政协,湖南省</t>
+          <t>地级政协,郴州市,市政协,湖南省</t>
         </is>
       </c>
       <c r="AF461" t="b">
@@ -23210,12 +23150,12 @@
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>益阳市政协</t>
+          <t>永州市政协</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>地级政协,益阳市,市政协,湖南省</t>
+          <t>地级政协,永州市,市政协,湖南省</t>
         </is>
       </c>
       <c r="AF462" t="b">
@@ -23243,12 +23183,12 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>郴州市政协</t>
+          <t>怀化市政协</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
         <is>
-          <t>地级政协,郴州市,市政协,湖南省</t>
+          <t>地级政协,怀化市,市政协,湖南省</t>
         </is>
       </c>
       <c r="AF463" t="b">
@@ -23276,12 +23216,12 @@
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>永州市政协</t>
+          <t>娄底市政协</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>地级政协,永州市,市政协,湖南省</t>
+          <t>地级政协,娄底市,市政协,湖南省</t>
         </is>
       </c>
       <c r="AF464" t="b">
@@ -23309,12 +23249,12 @@
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>怀化市政协</t>
+          <t>南宁市政协</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t>地级政协,怀化市,市政协,湖南省</t>
+          <t>地级政协,南宁市,市政协,广西壮族自治区</t>
         </is>
       </c>
       <c r="AF465" t="b">
@@ -23342,12 +23282,12 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>娄底市政协</t>
+          <t>柳州市政协</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>地级政协,娄底市,市政协,湖南省</t>
+          <t>地级政协,柳州市,市政协,广西壮族自治区</t>
         </is>
       </c>
       <c r="AF466" t="b">
@@ -23375,12 +23315,12 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>南宁市政协</t>
+          <t>桂林市政协</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>地级政协,南宁市,市政协,广西壮族自治区</t>
+          <t>地级政协,桂林市,市政协,广西壮族自治区</t>
         </is>
       </c>
       <c r="AF467" t="b">
@@ -23408,12 +23348,12 @@
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>柳州市政协</t>
+          <t>梧州市政协</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>地级政协,柳州市,市政协,广西壮族自治区</t>
+          <t>地级政协,梧州市,市政协,广西壮族自治区</t>
         </is>
       </c>
       <c r="AF468" t="b">
@@ -23441,12 +23381,12 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>桂林市政协</t>
+          <t>北海市政协</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>地级政协,桂林市,市政协,广西壮族自治区</t>
+          <t>地级政协,北海市,市政协,广西壮族自治区</t>
         </is>
       </c>
       <c r="AF469" t="b">
@@ -23474,12 +23414,12 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>梧州市政协</t>
+          <t>防城港市政协</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>地级政协,梧州市,市政协,广西壮族自治区</t>
+          <t>地级政协,防城港市,市政协,广西壮族自治区</t>
         </is>
       </c>
       <c r="AF470" t="b">
@@ -23507,12 +23447,12 @@
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>北海市政协</t>
+          <t>钦州市政协</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>地级政协,北海市,市政协,广西壮族自治区</t>
+          <t>地级政协,钦州市,市政协,广西壮族自治区</t>
         </is>
       </c>
       <c r="AF471" t="b">
@@ -23540,12 +23480,12 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>防城港市政协</t>
+          <t>贵港市政协</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>地级政协,防城港市,市政协,广西壮族自治区</t>
+          <t>地级政协,贵港市,市政协,广西壮族自治区</t>
         </is>
       </c>
       <c r="AF472" t="b">
@@ -23573,12 +23513,12 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>钦州市政协</t>
+          <t>玉林市政协</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>地级政协,钦州市,市政协,广西壮族自治区</t>
+          <t>地级政协,玉林市,市政协,广西壮族自治区</t>
         </is>
       </c>
       <c r="AF473" t="b">
@@ -23606,12 +23546,12 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>贵港市政协</t>
+          <t>百色市政协</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>地级政协,贵港市,市政协,广西壮族自治区</t>
+          <t>地级政协,百色市,市政协,广西壮族自治区</t>
         </is>
       </c>
       <c r="AF474" t="b">
@@ -23639,12 +23579,12 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>玉林市政协</t>
+          <t>贺州市政协</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>地级政协,玉林市,市政协,广西壮族自治区</t>
+          <t>地级政协,贺州市,市政协,广西壮族自治区</t>
         </is>
       </c>
       <c r="AF475" t="b">
@@ -23672,12 +23612,12 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>百色市政协</t>
+          <t>河池市政协</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>地级政协,百色市,市政协,广西壮族自治区</t>
+          <t>地级政协,河池市,市政协,广西壮族自治区</t>
         </is>
       </c>
       <c r="AF476" t="b">
@@ -23705,12 +23645,12 @@
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>贺州市政协</t>
+          <t>来宾市政协</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
         <is>
-          <t>地级政协,贺州市,市政协,广西壮族自治区</t>
+          <t>地级政协,来宾市,市政协,广西壮族自治区</t>
         </is>
       </c>
       <c r="AF477" t="b">
@@ -23738,12 +23678,12 @@
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>河池市政协</t>
+          <t>崇左市政协</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>地级政协,河池市,市政协,广西壮族自治区</t>
+          <t>地级政协,崇左市,市政协,广西壮族自治区</t>
         </is>
       </c>
       <c r="AF478" t="b">
@@ -23771,12 +23711,12 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>来宾市政协</t>
+          <t>海口市政协</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t>地级政协,来宾市,市政协,广西壮族自治区</t>
+          <t>地级政协,海口市,市政协,海南省</t>
         </is>
       </c>
       <c r="AF479" t="b">
@@ -23804,12 +23744,12 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>崇左市政协</t>
+          <t>三亚市政协</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>地级政协,崇左市,市政协,广西壮族自治区</t>
+          <t>地级政协,三亚市,市政协,海南省</t>
         </is>
       </c>
       <c r="AF480" t="b">
@@ -23837,12 +23777,12 @@
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>海口市政协</t>
+          <t>三沙市政协</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t>地级政协,海口市,市政协,海南省</t>
+          <t>地级政协,三沙市,市政协,海南省</t>
         </is>
       </c>
       <c r="AF481" t="b">
@@ -23870,12 +23810,12 @@
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>三亚市政协</t>
+          <t>儋州市政协</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
         <is>
-          <t>地级政协,三亚市,市政协,海南省</t>
+          <t>地级政协,儋州市,市政协,海南省</t>
         </is>
       </c>
       <c r="AF482" t="b">
@@ -23903,12 +23843,12 @@
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>三沙市政协</t>
+          <t>自贡市政协</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>地级政协,三沙市,市政协,海南省</t>
+          <t>地级政协,自贡市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF483" t="b">
@@ -23936,12 +23876,12 @@
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>儋州市政协</t>
+          <t>攀枝花市政协</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t>地级政协,儋州市,市政协,海南省</t>
+          <t>地级政协,攀枝花市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF484" t="b">
@@ -23969,12 +23909,12 @@
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>自贡市政协</t>
+          <t>泸州市政协</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
         <is>
-          <t>地级政协,自贡市,市政协,四川省</t>
+          <t>地级政协,泸州市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF485" t="b">
@@ -24002,12 +23942,12 @@
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>攀枝花市政协</t>
+          <t>德阳市政协</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t>地级政协,攀枝花市,市政协,四川省</t>
+          <t>地级政协,德阳市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF486" t="b">
@@ -24035,12 +23975,12 @@
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>泸州市政协</t>
+          <t>绵阳市政协</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
         <is>
-          <t>地级政协,泸州市,市政协,四川省</t>
+          <t>地级政协,绵阳市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF487" t="b">
@@ -24068,12 +24008,12 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>德阳市政协</t>
+          <t>广元市政协</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>地级政协,德阳市,市政协,四川省</t>
+          <t>地级政协,广元市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF488" t="b">
@@ -24101,12 +24041,12 @@
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>绵阳市政协</t>
+          <t>遂宁市政协</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>地级政协,绵阳市,市政协,四川省</t>
+          <t>地级政协,遂宁市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF489" t="b">
@@ -24134,12 +24074,12 @@
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>广元市政协</t>
+          <t>内江市政协</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t>地级政协,广元市,市政协,四川省</t>
+          <t>地级政协,内江市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF490" t="b">
@@ -24167,12 +24107,12 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>遂宁市政协</t>
+          <t>乐山市政协</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t>地级政协,遂宁市,市政协,四川省</t>
+          <t>地级政协,乐山市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF491" t="b">
@@ -24200,12 +24140,12 @@
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>内江市政协</t>
+          <t>南充市政协</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
         <is>
-          <t>地级政协,内江市,市政协,四川省</t>
+          <t>地级政协,南充市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF492" t="b">
@@ -24233,12 +24173,12 @@
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>乐山市政协</t>
+          <t>眉山市政协</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>地级政协,乐山市,市政协,四川省</t>
+          <t>地级政协,眉山市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF493" t="b">
@@ -24266,12 +24206,12 @@
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>南充市政协</t>
+          <t>宜宾市政协</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>地级政协,南充市,市政协,四川省</t>
+          <t>地级政协,宜宾市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF494" t="b">
@@ -24299,12 +24239,12 @@
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>眉山市政协</t>
+          <t>广安市政协</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
         <is>
-          <t>地级政协,眉山市,市政协,四川省</t>
+          <t>地级政协,广安市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF495" t="b">
@@ -24332,12 +24272,12 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>宜宾市政协</t>
+          <t>达州市政协</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
         <is>
-          <t>地级政协,宜宾市,市政协,四川省</t>
+          <t>地级政协,达州市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF496" t="b">
@@ -24365,12 +24305,12 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>广安市政协</t>
+          <t>雅安市政协</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>地级政协,广安市,市政协,四川省</t>
+          <t>地级政协,雅安市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF497" t="b">
@@ -24398,12 +24338,12 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>达州市政协</t>
+          <t>巴中市政协</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>地级政协,达州市,市政协,四川省</t>
+          <t>地级政协,巴中市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF498" t="b">
@@ -24431,12 +24371,12 @@
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>雅安市政协</t>
+          <t>资阳市政协</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>地级政协,雅安市,市政协,四川省</t>
+          <t>地级政协,资阳市,市政协,四川省</t>
         </is>
       </c>
       <c r="AF499" t="b">
@@ -24464,12 +24404,12 @@
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>巴中市政协</t>
+          <t>贵阳市政协</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>地级政协,巴中市,市政协,四川省</t>
+          <t>地级政协,贵阳市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF500" t="b">
@@ -24497,12 +24437,12 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>资阳市政协</t>
+          <t>六盘水市政协</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>地级政协,资阳市,市政协,四川省</t>
+          <t>地级政协,六盘水市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF501" t="b">
@@ -24530,12 +24470,12 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>贵阳市政协</t>
+          <t>遵义市政协</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>地级政协,贵阳市,市政协,贵州省</t>
+          <t>地级政协,遵义市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF502" t="b">
@@ -24563,12 +24503,12 @@
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>六盘水市政协</t>
+          <t>安顺市政协</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>地级政协,六盘水市,市政协,贵州省</t>
+          <t>地级政协,安顺市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF503" t="b">
@@ -24596,12 +24536,12 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>遵义市政协</t>
+          <t>毕节市政协</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>地级政协,遵义市,市政协,贵州省</t>
+          <t>地级政协,毕节市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF504" t="b">
@@ -24629,12 +24569,12 @@
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>安顺市政协</t>
+          <t>铜仁市政协</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>地级政协,安顺市,市政协,贵州省</t>
+          <t>地级政协,铜仁市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF505" t="b">
@@ -24662,12 +24602,12 @@
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>毕节市政协</t>
+          <t>昆明市政协</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>地级政协,毕节市,市政协,贵州省</t>
+          <t>地级政协,昆明市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF506" t="b">
@@ -24695,12 +24635,12 @@
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>铜仁市政协</t>
+          <t>曲靖市政协</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>地级政协,铜仁市,市政协,贵州省</t>
+          <t>地级政协,曲靖市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF507" t="b">
@@ -24728,12 +24668,12 @@
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>昆明市政协</t>
+          <t>玉溪市政协</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>地级政协,昆明市,市政协,贵州省</t>
+          <t>地级政协,玉溪市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF508" t="b">
@@ -24761,12 +24701,12 @@
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>曲靖市政协</t>
+          <t>保山市政协</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>地级政协,曲靖市,市政协,贵州省</t>
+          <t>地级政协,保山市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF509" t="b">
@@ -24794,12 +24734,12 @@
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>玉溪市政协</t>
+          <t>昭通市政协</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>地级政协,玉溪市,市政协,贵州省</t>
+          <t>地级政协,昭通市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF510" t="b">
@@ -24827,12 +24767,12 @@
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>保山市政协</t>
+          <t>丽江市政协</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>地级政协,保山市,市政协,贵州省</t>
+          <t>地级政协,丽江市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF511" t="b">
@@ -24860,12 +24800,12 @@
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>昭通市政协</t>
+          <t>普洱市政协</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t>地级政协,昭通市,市政协,贵州省</t>
+          <t>地级政协,普洱市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF512" t="b">
@@ -24893,12 +24833,12 @@
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>丽江市政协</t>
+          <t>临沧市政协</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>地级政协,丽江市,市政协,贵州省</t>
+          <t>地级政协,临沧市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF513" t="b">
@@ -24926,12 +24866,12 @@
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>普洱市政协</t>
+          <t>拉萨市政协</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>地级政协,普洱市,市政协,贵州省</t>
+          <t>地级政协,拉萨市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF514" t="b">
@@ -24959,12 +24899,12 @@
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>临沧市政协</t>
+          <t>日喀则市政协</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
         <is>
-          <t>地级政协,临沧市,市政协,贵州省</t>
+          <t>地级政协,日喀则市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF515" t="b">
@@ -24992,12 +24932,12 @@
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>拉萨市政协</t>
+          <t>昌都市政协</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
         <is>
-          <t>地级政协,拉萨市,市政协,贵州省</t>
+          <t>地级政协,昌都市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF516" t="b">
@@ -25025,12 +24965,12 @@
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>日喀则市政协</t>
+          <t>林芝市政协</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
         <is>
-          <t>地级政协,日喀则市,市政协,贵州省</t>
+          <t>地级政协,林芝市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF517" t="b">
@@ -25058,12 +24998,12 @@
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>昌都市政协</t>
+          <t>山南市政协</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
         <is>
-          <t>地级政协,昌都市,市政协,贵州省</t>
+          <t>地级政协,山南市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF518" t="b">
@@ -25091,12 +25031,12 @@
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>林芝市政协</t>
+          <t>那曲市政协</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
         <is>
-          <t>地级政协,林芝市,市政协,贵州省</t>
+          <t>地级政协,那曲市,市政协,贵州省</t>
         </is>
       </c>
       <c r="AF519" t="b">
@@ -25124,12 +25064,12 @@
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>山南市政协</t>
+          <t>铜川市政协</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>地级政协,山南市,市政协,贵州省</t>
+          <t>地级政协,铜川市,市政协,陕西省</t>
         </is>
       </c>
       <c r="AF520" t="b">
@@ -25157,12 +25097,12 @@
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>那曲市政协</t>
+          <t>宝鸡市政协</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
         <is>
-          <t>地级政协,那曲市,市政协,贵州省</t>
+          <t>地级政协,宝鸡市,市政协,陕西省</t>
         </is>
       </c>
       <c r="AF521" t="b">
@@ -25190,12 +25130,12 @@
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>铜川市政协</t>
+          <t>咸阳市政协</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t>地级政协,铜川市,市政协,陕西省</t>
+          <t>地级政协,咸阳市,市政协,陕西省</t>
         </is>
       </c>
       <c r="AF522" t="b">
@@ -25223,12 +25163,12 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>宝鸡市政协</t>
+          <t>渭南市政协</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
         <is>
-          <t>地级政协,宝鸡市,市政协,陕西省</t>
+          <t>地级政协,渭南市,市政协,陕西省</t>
         </is>
       </c>
       <c r="AF523" t="b">
@@ -25256,12 +25196,12 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>咸阳市政协</t>
+          <t>延安市政协</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>地级政协,咸阳市,市政协,陕西省</t>
+          <t>地级政协,延安市,市政协,陕西省</t>
         </is>
       </c>
       <c r="AF524" t="b">
@@ -25289,12 +25229,12 @@
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>渭南市政协</t>
+          <t>汉中市政协</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
         <is>
-          <t>地级政协,渭南市,市政协,陕西省</t>
+          <t>地级政协,汉中市,市政协,陕西省</t>
         </is>
       </c>
       <c r="AF525" t="b">
@@ -25322,12 +25262,12 @@
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>延安市政协</t>
+          <t>榆林市政协</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
         <is>
-          <t>地级政协,延安市,市政协,陕西省</t>
+          <t>地级政协,榆林市,市政协,陕西省</t>
         </is>
       </c>
       <c r="AF526" t="b">
@@ -25355,12 +25295,12 @@
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>汉中市政协</t>
+          <t>安康市政协</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t>地级政协,汉中市,市政协,陕西省</t>
+          <t>地级政协,安康市,市政协,陕西省</t>
         </is>
       </c>
       <c r="AF527" t="b">
@@ -25388,12 +25328,12 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>榆林市政协</t>
+          <t>商洛市政协</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>地级政协,榆林市,市政协,陕西省</t>
+          <t>地级政协,商洛市,市政协,陕西省</t>
         </is>
       </c>
       <c r="AF528" t="b">
@@ -25421,12 +25361,12 @@
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>安康市政协</t>
+          <t>兰州市政协</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
         <is>
-          <t>地级政协,安康市,市政协,陕西省</t>
+          <t>地级政协,兰州市,市政协,甘肃省</t>
         </is>
       </c>
       <c r="AF529" t="b">
@@ -25454,12 +25394,12 @@
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>商洛市政协</t>
+          <t>嘉峪关市政协</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
         <is>
-          <t>地级政协,商洛市,市政协,陕西省</t>
+          <t>地级政协,嘉峪关市,市政协,甘肃省</t>
         </is>
       </c>
       <c r="AF530" t="b">
@@ -25487,12 +25427,12 @@
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>兰州市政协</t>
+          <t>金昌市政协</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
         <is>
-          <t>地级政协,兰州市,市政协,甘肃省</t>
+          <t>地级政协,金昌市,市政协,甘肃省</t>
         </is>
       </c>
       <c r="AF531" t="b">
@@ -25520,12 +25460,12 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>嘉峪关市政协</t>
+          <t>白银市政协</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
         <is>
-          <t>地级政协,嘉峪关市,市政协,甘肃省</t>
+          <t>地级政协,白银市,市政协,甘肃省</t>
         </is>
       </c>
       <c r="AF532" t="b">
@@ -25553,12 +25493,12 @@
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>金昌市政协</t>
+          <t>天水市政协</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t>地级政协,金昌市,市政协,甘肃省</t>
+          <t>地级政协,天水市,市政协,甘肃省</t>
         </is>
       </c>
       <c r="AF533" t="b">
@@ -25586,12 +25526,12 @@
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>白银市政协</t>
+          <t>武威市政协</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
         <is>
-          <t>地级政协,白银市,市政协,甘肃省</t>
+          <t>地级政协,武威市,市政协,甘肃省</t>
         </is>
       </c>
       <c r="AF534" t="b">
@@ -25619,12 +25559,12 @@
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>天水市政协</t>
+          <t>张掖市政协</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
         <is>
-          <t>地级政协,天水市,市政协,甘肃省</t>
+          <t>地级政协,张掖市,市政协,甘肃省</t>
         </is>
       </c>
       <c r="AF535" t="b">
@@ -25652,12 +25592,12 @@
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>武威市政协</t>
+          <t>平凉市政协</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
         <is>
-          <t>地级政协,武威市,市政协,甘肃省</t>
+          <t>地级政协,平凉市,市政协,甘肃省</t>
         </is>
       </c>
       <c r="AF536" t="b">
@@ -25685,12 +25625,12 @@
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>张掖市政协</t>
+          <t>酒泉市政协</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
         <is>
-          <t>地级政协,张掖市,市政协,甘肃省</t>
+          <t>地级政协,酒泉市,市政协,甘肃省</t>
         </is>
       </c>
       <c r="AF537" t="b">
@@ -25718,12 +25658,12 @@
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>平凉市政协</t>
+          <t>庆阳市政协</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
         <is>
-          <t>地级政协,平凉市,市政协,甘肃省</t>
+          <t>地级政协,庆阳市,市政协,甘肃省</t>
         </is>
       </c>
       <c r="AF538" t="b">
@@ -25751,12 +25691,12 @@
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>酒泉市政协</t>
+          <t>定西市政协</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
         <is>
-          <t>地级政协,酒泉市,市政协,甘肃省</t>
+          <t>地级政协,定西市,市政协,甘肃省</t>
         </is>
       </c>
       <c r="AF539" t="b">
@@ -25784,12 +25724,12 @@
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>庆阳市政协</t>
+          <t>陇南市政协</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
         <is>
-          <t>地级政协,庆阳市,市政协,甘肃省</t>
+          <t>地级政协,陇南市,市政协,甘肃省</t>
         </is>
       </c>
       <c r="AF540" t="b">
@@ -25817,12 +25757,12 @@
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>定西市政协</t>
+          <t>西宁市政协</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
         <is>
-          <t>地级政协,定西市,市政协,甘肃省</t>
+          <t>地级政协,西宁市,市政协,青海省</t>
         </is>
       </c>
       <c r="AF541" t="b">
@@ -25850,12 +25790,12 @@
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>陇南市政协</t>
+          <t>海东市政协</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
         <is>
-          <t>地级政协,陇南市,市政协,甘肃省</t>
+          <t>地级政协,海东市,市政协,青海省</t>
         </is>
       </c>
       <c r="AF542" t="b">
@@ -25883,12 +25823,12 @@
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>西宁市政协</t>
+          <t>银川市政协</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
         <is>
-          <t>地级政协,西宁市,市政协,青海省</t>
+          <t>地级政协,银川市,市政协,宁夏回族自治区</t>
         </is>
       </c>
       <c r="AF543" t="b">
@@ -25916,12 +25856,12 @@
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>海东市政协</t>
+          <t>石嘴山市政协</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
         <is>
-          <t>地级政协,海东市,市政协,青海省</t>
+          <t>地级政协,石嘴山市,市政协,宁夏回族自治区</t>
         </is>
       </c>
       <c r="AF544" t="b">
@@ -25949,12 +25889,12 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>银川市政协</t>
+          <t>吴忠市政协</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
         <is>
-          <t>地级政协,银川市,市政协,宁夏回族自治区</t>
+          <t>地级政协,吴忠市,市政协,宁夏回族自治区</t>
         </is>
       </c>
       <c r="AF545" t="b">
@@ -25982,12 +25922,12 @@
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>石嘴山市政协</t>
+          <t>固原市政协</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t>地级政协,石嘴山市,市政协,宁夏回族自治区</t>
+          <t>地级政协,固原市,市政协,宁夏回族自治区</t>
         </is>
       </c>
       <c r="AF546" t="b">
@@ -26015,12 +25955,12 @@
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>吴忠市政协</t>
+          <t>中卫市政协</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t>地级政协,吴忠市,市政协,宁夏回族自治区</t>
+          <t>地级政协,中卫市,市政协,宁夏回族自治区</t>
         </is>
       </c>
       <c r="AF547" t="b">
@@ -26048,12 +25988,12 @@
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>固原市政协</t>
+          <t>乌鲁木齐市政协</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
         <is>
-          <t>地级政协,固原市,市政协,宁夏回族自治区</t>
+          <t>地级政协,乌鲁木齐市,市政协,新疆维吾尔自治区</t>
         </is>
       </c>
       <c r="AF548" t="b">
@@ -26081,12 +26021,12 @@
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>中卫市政协</t>
+          <t>克拉玛依市政协</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
         <is>
-          <t>地级政协,中卫市,市政协,宁夏回族自治区</t>
+          <t>地级政协,克拉玛依市,市政协,新疆维吾尔自治区</t>
         </is>
       </c>
       <c r="AF549" t="b">
@@ -26114,12 +26054,12 @@
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>乌鲁木齐市政协</t>
+          <t>吐鲁番市政协</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
         <is>
-          <t>地级政协,乌鲁木齐市,市政协,新疆维吾尔自治区</t>
+          <t>地级政协,吐鲁番市,市政协,新疆维吾尔自治区</t>
         </is>
       </c>
       <c r="AF550" t="b">
@@ -26147,12 +26087,12 @@
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>克拉玛依市政协</t>
+          <t>哈密市政协</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
         <is>
-          <t>地级政协,克拉玛依市,市政协,新疆维吾尔自治区</t>
+          <t>地级政协,哈密市,市政协,新疆维吾尔自治区</t>
         </is>
       </c>
       <c r="AF551" t="b">
@@ -26172,7 +26112,7 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>相关机构</t>
         </is>
       </c>
       <c r="E552" t="n">
@@ -26180,16 +26120,46 @@
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>吐鲁番市政协</t>
+          <t>12321网络不良与垃圾信息举报受理中心</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>中国互联网协会受工业和信息化部委托设立的投诉受理机构。负责协助工业和信息化部承担关于互联网、移动电话网、固定电话网等各种形式信息通信网络及电信业务中不良与垃圾信息的投诉受理、线索转办及信息统计等工作。</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>https://www.12321.cn/Public/home/image/favicon.ico,#FFFFFF</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
         <is>
-          <t>地级政协,吐鲁番市,市政协,新疆维吾尔自治区</t>
+          <t>举报中心</t>
+        </is>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>访问官网</t>
+        </is>
+      </c>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>https://www.12321.cn</t>
+        </is>
+      </c>
+      <c r="N552" t="inlineStr">
+        <is>
+          <t>机构介绍</t>
+        </is>
+      </c>
+      <c r="O552" t="inlineStr">
+        <is>
+          <t>https://www.12321.cn/single?tpl=institution</t>
         </is>
       </c>
       <c r="AF552" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="553">
@@ -26205,24 +26175,54 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>相关机构</t>
         </is>
       </c>
       <c r="E553" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>哈密市政协</t>
+          <t>中央网信办（国家互联网信息办公室）违法和不良信息举报中心</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>统筹协调全国互联网违法和不良信息举报工作；指导、监督各地各网站规范开展互联网违法和不良信息举报工作；受理、协助处置网民对互联网违法和不良信息的举报；宣传动员广大网民积极参与互联网违法和不良信息举报监督；主办中国互联网联合辟谣平台，统筹做好网络辟谣工作；开展国际交流合作，加强与境外国际组织、相关机构、互联网企业的联系，协调处理相关有害信息。</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>https://zhengxie.com.cn/assets/images/12377-3-04.webp</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
         <is>
-          <t>地级政协,哈密市,市政协,新疆维吾尔自治区</t>
+          <t>举报中心</t>
+        </is>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>访问官网</t>
+        </is>
+      </c>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>https://www.12377.cn</t>
+        </is>
+      </c>
+      <c r="N553" t="inlineStr">
+        <is>
+          <t>机构简介</t>
+        </is>
+      </c>
+      <c r="O553" t="inlineStr">
+        <is>
+          <t>https://www.12377.cn/jgjj.html?tab=5</t>
         </is>
       </c>
       <c r="AF553" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/cards.unified.xlsx
+++ b/xlsx/cards.unified.xlsx
@@ -14333,7 +14333,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>https://www.hebzx.gov.cn</t>
+          <t>http://www.hebzx.gov.cn</t>
         </is>
       </c>
       <c r="AF229" t="inlineStr">
@@ -14578,7 +14578,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>https://www.jlzx.gov.cn</t>
+          <t>https://www.jlzx.gov.cn/szx.html</t>
         </is>
       </c>
       <c r="AF233" t="inlineStr">
@@ -14758,7 +14758,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>https://www.jszx.gov.cn</t>
+          <t>https://www.jszx.gov.cn/index.html</t>
         </is>
       </c>
       <c r="AF236" t="inlineStr">
@@ -15303,12 +15303,12 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>访问官网 - www.gdzxb.gov.cn</t>
+          <t>访问官网 - www.gdszx.gov.cn</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>https://www.gdzxb.gov.cn</t>
+          <t>https://www.gdszx.gov.cn/</t>
         </is>
       </c>
       <c r="AF245" t="inlineStr">
@@ -16126,12 +16126,12 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>访问官网 - www.whzx.org.cn</t>
+          <t>访问官网 - www.whzx.gov.cn</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.whzx.org.cn/  </t>
+          <t>https://www.whzx.gov.cn/</t>
         </is>
       </c>
       <c r="AF259" t="b">
@@ -16179,7 +16179,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>https://www.hrbzx.gov.cn/</t>
+          <t>http://www.hrbzx.gov.cn/</t>
         </is>
       </c>
       <c r="AF260" t="b">
@@ -16281,6 +16281,16 @@
           <t>南京市,副省级城市政协,省会城市,江苏省</t>
         </is>
       </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>访问官网 - www.njzx.gov.cn</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>http://www.njzx.gov.cn/</t>
+        </is>
+      </c>
       <c r="AF263" t="b">
         <v>1</v>
       </c>
@@ -16380,6 +16390,16 @@
           <t>济南市,副省级城市政协,省会城市,山东省</t>
         </is>
       </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>访问官网 - www.jnzx.gov.cn</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>https://www.jnzx.gov.cn/</t>
+        </is>
+      </c>
       <c r="AF266" t="b">
         <v>1</v>
       </c>
@@ -16413,6 +16433,16 @@
           <t>杭州市,副省级城市政协,省会城市,浙江省</t>
         </is>
       </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>访问官网 - www.hzzx.gov.cn</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>https://www.hzzx.gov.cn/</t>
+        </is>
+      </c>
       <c r="AF267" t="b">
         <v>1</v>
       </c>
@@ -16479,6 +16509,16 @@
           <t>青岛市,副省级城市政协,计划单列市,山东省</t>
         </is>
       </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>访问官网 - qdzx.qingdao.gov.cn</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>http://qdzx.qingdao.gov.cn/</t>
+        </is>
+      </c>
       <c r="AF269" t="b">
         <v>1</v>
       </c>
@@ -16591,6 +16631,16 @@
       <c r="I272" t="inlineStr">
         <is>
           <t>宁波市,副省级城市政协,计划单列市,浙江省</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>访问官网 - www.nbzx.gov.cn</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>http://www.nbzx.gov.cn/</t>
         </is>
       </c>
       <c r="AF272" t="b">

--- a/xlsx/cards.unified.xlsx
+++ b/xlsx/cards.unified.xlsx
@@ -16086,8 +16086,10 @@
           <t>https://www.gzzx.gov.cn</t>
         </is>
       </c>
-      <c r="AF258" t="b">
-        <v>1</v>
+      <c r="AF258" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="259">
@@ -16134,8 +16136,10 @@
           <t>https://www.whzx.gov.cn/</t>
         </is>
       </c>
-      <c r="AF259" t="b">
-        <v>1</v>
+      <c r="AF259" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="260">
@@ -16182,8 +16186,10 @@
           <t>http://www.hrbzx.gov.cn/</t>
         </is>
       </c>
-      <c r="AF260" t="b">
-        <v>1</v>
+      <c r="AF260" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="261">
@@ -16210,6 +16216,11 @@
           <t>沈阳市政协</t>
         </is>
       </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>中国人民政治协商会议沈阳市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+        </is>
+      </c>
       <c r="I261" t="inlineStr">
         <is>
           <t>沈阳市,副省级城市政协,省会城市,辽宁省</t>
@@ -16243,6 +16254,11 @@
           <t>成都市政协</t>
         </is>
       </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>中国人民政治协商会议成都市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+        </is>
+      </c>
       <c r="I262" t="inlineStr">
         <is>
           <t>成都市,副省级城市政协,省会城市,四川省</t>
@@ -16276,6 +16292,11 @@
           <t>南京市政协</t>
         </is>
       </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>中国人民政治协商会议南京市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+        </is>
+      </c>
       <c r="I263" t="inlineStr">
         <is>
           <t>南京市,副省级城市政协,省会城市,江苏省</t>
@@ -16291,8 +16312,10 @@
           <t>http://www.njzx.gov.cn/</t>
         </is>
       </c>
-      <c r="AF263" t="b">
-        <v>1</v>
+      <c r="AF263" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="264">
@@ -16319,6 +16342,11 @@
           <t>西安市政协</t>
         </is>
       </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>中国人民政治协商会议西安市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+        </is>
+      </c>
       <c r="I264" t="inlineStr">
         <is>
           <t>西安市,副省级城市政协,省会城市,陕西省</t>
@@ -16352,6 +16380,11 @@
           <t>长春市政协</t>
         </is>
       </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>中国人民政治协商会议长春市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+        </is>
+      </c>
       <c r="I265" t="inlineStr">
         <is>
           <t>长春市,副省级城市政协,省会城市,吉林省</t>
@@ -16385,6 +16418,11 @@
           <t>济南市政协</t>
         </is>
       </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>中国人民政治协商会议济南市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+        </is>
+      </c>
       <c r="I266" t="inlineStr">
         <is>
           <t>济南市,副省级城市政协,省会城市,山东省</t>
@@ -16400,8 +16438,10 @@
           <t>https://www.jnzx.gov.cn/</t>
         </is>
       </c>
-      <c r="AF266" t="b">
-        <v>1</v>
+      <c r="AF266" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="267">
@@ -16428,6 +16468,11 @@
           <t>杭州市政协</t>
         </is>
       </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>中国人民政治协商会议杭州市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+        </is>
+      </c>
       <c r="I267" t="inlineStr">
         <is>
           <t>杭州市,副省级城市政协,省会城市,浙江省</t>
@@ -16443,8 +16488,10 @@
           <t>https://www.hzzx.gov.cn/</t>
         </is>
       </c>
-      <c r="AF267" t="b">
-        <v>1</v>
+      <c r="AF267" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="268">
@@ -16471,6 +16518,11 @@
           <t>大连市政协</t>
         </is>
       </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>中国人民政治协商会议大连市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+        </is>
+      </c>
       <c r="I268" t="inlineStr">
         <is>
           <t>大连市,副省级城市政协,计划单列市,辽宁省</t>
@@ -16504,6 +16556,11 @@
           <t>青岛市政协</t>
         </is>
       </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>中国人民政治协商会议青岛市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+        </is>
+      </c>
       <c r="I269" t="inlineStr">
         <is>
           <t>青岛市,副省级城市政协,计划单列市,山东省</t>
@@ -16519,8 +16576,10 @@
           <t>http://qdzx.qingdao.gov.cn/</t>
         </is>
       </c>
-      <c r="AF269" t="b">
-        <v>1</v>
+      <c r="AF269" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="270">
@@ -16567,8 +16626,10 @@
           <t>https://www.szzx.gov.cn/</t>
         </is>
       </c>
-      <c r="AF270" t="b">
-        <v>1</v>
+      <c r="AF270" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="271">
@@ -16595,6 +16656,11 @@
           <t>厦门市政协</t>
         </is>
       </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>中国人民政治协商会议厦门市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+        </is>
+      </c>
       <c r="I271" t="inlineStr">
         <is>
           <t>厦门市,副省级城市政协,计划单列市,福建省</t>
@@ -16628,6 +16694,11 @@
           <t>宁波市政协</t>
         </is>
       </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>中国人民政治协商会议宁波市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+        </is>
+      </c>
       <c r="I272" t="inlineStr">
         <is>
           <t>宁波市,副省级城市政协,计划单列市,浙江省</t>
@@ -16643,8 +16714,10 @@
           <t>http://www.nbzx.gov.cn/</t>
         </is>
       </c>
-      <c r="AF272" t="b">
-        <v>1</v>
+      <c r="AF272" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="273">
@@ -16678,7 +16751,7 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>地级政协,珠海市,市政协,广东省</t>
+          <t>珠海市,地级市政协,广东省</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -16688,11 +16761,13 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>https://www.zhzx.gov.cn/</t>
-        </is>
-      </c>
-      <c r="AF273" t="b">
-        <v>0</v>
+          <t>http://www.zhzx.gov.cn/</t>
+        </is>
+      </c>
+      <c r="AF273" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="274">
@@ -16726,7 +16801,7 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>地级政协,汕头市,市政协,广东省</t>
+          <t>汕头市,地级市政协,广东省</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -16739,8 +16814,10 @@
           <t>https://stzx.shantou.gov.cn/</t>
         </is>
       </c>
-      <c r="AF274" t="b">
-        <v>0</v>
+      <c r="AF274" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="275">
@@ -16779,7 +16856,7 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>县级政协,汕头市金平区,市辖区政协,广东省</t>
+          <t>市辖区政协,汕头市,广东省</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -16827,7 +16904,7 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>地级政协,佛山市,市政协,广东省</t>
+          <t>佛山市,地级市政协,广东省</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -16875,7 +16952,7 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>地级政协,韶关市,市政协,广东省</t>
+          <t>韶关市,地级市政协,广东省</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -16888,8 +16965,10 @@
           <t>https://www.sgzxb.gov.cn/</t>
         </is>
       </c>
-      <c r="AF277" t="b">
-        <v>0</v>
+      <c r="AF277" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="278">
@@ -16923,7 +17002,7 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>地级政协,河源市,市政协,广东省</t>
+          <t>河源市,地级市政协,广东省</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -16933,11 +17012,13 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>https://www.gdhyzx.gov.cn/hyzx/index.html</t>
-        </is>
-      </c>
-      <c r="AF278" t="b">
-        <v>0</v>
+          <t>http://www.gdhyzx.gov.cn/hyzx/index.html</t>
+        </is>
+      </c>
+      <c r="AF278" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="279">
@@ -16971,7 +17052,7 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>地级政协,梅州市,市政协,广东省</t>
+          <t>梅州市,地级市政协,广东省</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -17019,21 +17100,23 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>地级政协,惠州市,市政协,广东省</t>
+          <t>惠州市,地级市政协,广东省</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>访问官网 - zx.huizhou.gov.cn</t>
+          <t>访问官网 - www.hzszx.gov.cn</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>https://zx.huizhou.gov.cn/</t>
-        </is>
-      </c>
-      <c r="AF280" t="b">
-        <v>0</v>
+          <t>http://www.hzszx.gov.cn/</t>
+        </is>
+      </c>
+      <c r="AF280" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="281">
@@ -17067,7 +17150,7 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>地级政协,汕尾市,市政协,广东省</t>
+          <t>汕尾市,地级市政协,广东省</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -17115,7 +17198,7 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>地级政协,东莞市,市政协,广东省</t>
+          <t>东莞市,地级市政协,广东省</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -17163,7 +17246,7 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>地级政协,中山市,市政协,广东省</t>
+          <t>中山市,地级市政协,广东省</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -17176,8 +17259,10 @@
           <t>https://zszx.zsnews.cn/</t>
         </is>
       </c>
-      <c r="AF283" t="b">
-        <v>0</v>
+      <c r="AF283" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="284">
@@ -17211,7 +17296,7 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>地级政协,江门市,市政协,广东省</t>
+          <t>江门市,地级市政协,广东省</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -17224,8 +17309,10 @@
           <t>https://zx.jiangmen.cn/</t>
         </is>
       </c>
-      <c r="AF284" t="b">
-        <v>0</v>
+      <c r="AF284" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="285">
@@ -17259,7 +17346,7 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>地级政协,阳江市,市政协,广东省</t>
+          <t>阳江市,地级市政协,广东省</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -17269,11 +17356,13 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>https://www.yjszx.gov.cn/default.html</t>
-        </is>
-      </c>
-      <c r="AF285" t="b">
-        <v>0</v>
+          <t>https://yjszx.gov.cn/yjzx/index</t>
+        </is>
+      </c>
+      <c r="AF285" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="286">
@@ -17312,7 +17401,7 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>地级政协,湛江市,市政协,广东省</t>
+          <t>湛江市,地级市政协,广东省</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -17325,8 +17414,10 @@
           <t>https://www.gdzjzx.gov.cn/</t>
         </is>
       </c>
-      <c r="AF286" t="b">
-        <v>0</v>
+      <c r="AF286" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="287">
@@ -17360,7 +17451,7 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>地级政协,茂名市,市政协,广东省</t>
+          <t>茂名市,地级市政协,广东省</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -17408,7 +17499,7 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>地级政协,肇庆市,市政协,广东省</t>
+          <t>肇庆市,地级市政协,广东省</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -17456,7 +17547,7 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>地级政协,潮州市,市政协,广东省</t>
+          <t>潮州市,地级市政协,广东省</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
@@ -17502,9 +17593,14 @@
           <t>中国人民政治协商会议揭阳市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>http://www.jieyangzhengxie.gov.cn/static/website/image/bmmb_c/zhengxie/favicon.ico</t>
+        </is>
+      </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>地级政协,揭阳市,市政协,广东省</t>
+          <t>揭阳市,地级市政协,广东省</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -17514,11 +17610,13 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.jieyangzhengxie.gov.cn/ </t>
-        </is>
-      </c>
-      <c r="AF290" t="b">
-        <v>0</v>
+          <t xml:space="preserve">http://www.jieyangzhengxie.gov.cn/ </t>
+        </is>
+      </c>
+      <c r="AF290" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="291">
@@ -17552,7 +17650,7 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>地级政协,云浮市,市政协,广东省</t>
+          <t>云浮市,地级市政协,广东省</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -17593,13 +17691,30 @@
           <t>清远市政协</t>
         </is>
       </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>中国人民政治协商会议清远市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+        </is>
+      </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>地级政协,清远市,市政协,广东省</t>
-        </is>
-      </c>
-      <c r="AF292" t="b">
-        <v>0</v>
+          <t>清远市,地级市政协,广东省</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>访问官网 - www.qyszx.org</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>https://www.qyszx.org/</t>
+        </is>
+      </c>
+      <c r="AF292" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
     <row r="293">

--- a/xlsx/cards.unified.xlsx
+++ b/xlsx/cards.unified.xlsx
@@ -13663,7 +13663,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>https://www.minge.gov.cn</t>
+          <t>http://www.minge.gov.cn</t>
         </is>
       </c>
       <c r="AF218" t="inlineStr">
@@ -13718,12 +13718,12 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>访问官网 - www.dem-league.org.cn</t>
+          <t>访问官网 - www.mmzy.org.cn</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>https://www.dem-league.org.cn</t>
+          <t>https://www.mmzy.org.cn/</t>
         </is>
       </c>
       <c r="AF219" t="inlineStr">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>http://www.cndca.org.cn</t>
+          <t>https://www.cndca.org.cn</t>
         </is>
       </c>
       <c r="AF220" t="inlineStr">
@@ -14121,6 +14121,11 @@
           <t>工商联是中国共产党领导的以民营企业和民营经济人士为主体，具有统战性、经济性、民间性有机统一基本特征的人民团体和商会组织，是党和政府联系民营经济人士的桥梁纽带，是政府管理和服务民营经济的助手，是中国人民政治协商会议的重要组成部分。工商联工作是党的统一战线工作和经济工作的重要组成部分。工商联事业是党和国家事业的重要组成部分。</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>https://www.acfic.org.cn/images/icotopn.png</t>
+        </is>
+      </c>
       <c r="I226" t="inlineStr">
         <is>
           <t>全国工商联</t>
@@ -16733,7 +16738,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E273" t="n">
@@ -16783,7 +16788,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E274" t="n">
@@ -16833,7 +16838,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>县级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E275" t="n">
@@ -16886,7 +16891,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E276" t="n">
@@ -16934,7 +16939,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E277" t="n">
@@ -16984,7 +16989,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E278" t="n">
@@ -17034,7 +17039,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E279" t="n">
@@ -17082,7 +17087,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E280" t="n">
@@ -17132,7 +17137,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E281" t="n">
@@ -17180,7 +17185,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E282" t="n">
@@ -17228,7 +17233,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E283" t="n">
@@ -17278,7 +17283,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E284" t="n">
@@ -17328,7 +17333,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E285" t="n">
@@ -17378,7 +17383,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E286" t="n">
@@ -17433,7 +17438,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E287" t="n">
@@ -17481,7 +17486,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E288" t="n">
@@ -17529,7 +17534,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E289" t="n">
@@ -17577,7 +17582,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E290" t="n">
@@ -17632,7 +17637,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E291" t="n">
@@ -17680,7 +17685,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E292" t="n">
@@ -17730,7 +17735,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E293" t="n">
@@ -17763,7 +17768,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E294" t="n">
@@ -17796,7 +17801,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E295" t="n">
@@ -17829,7 +17834,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E296" t="n">
@@ -17862,7 +17867,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E297" t="n">
@@ -17895,7 +17900,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E298" t="n">
@@ -17928,7 +17933,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E299" t="n">
@@ -17961,7 +17966,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E300" t="n">
@@ -17994,7 +17999,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E301" t="n">
@@ -18027,7 +18032,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E302" t="n">
@@ -18060,7 +18065,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E303" t="n">
@@ -18093,7 +18098,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E304" t="n">
@@ -18126,7 +18131,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E305" t="n">
@@ -18159,7 +18164,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E306" t="n">
@@ -18192,7 +18197,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E307" t="n">
@@ -18225,7 +18230,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E308" t="n">
@@ -18258,7 +18263,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E309" t="n">
@@ -18291,7 +18296,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E310" t="n">
@@ -18324,7 +18329,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E311" t="n">
@@ -18357,7 +18362,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E312" t="n">
@@ -18390,7 +18395,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E313" t="n">
@@ -18423,7 +18428,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E314" t="n">
@@ -18456,7 +18461,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E315" t="n">
@@ -18489,7 +18494,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E316" t="n">
@@ -18522,7 +18527,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E317" t="n">
@@ -18555,7 +18560,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E318" t="n">
@@ -18588,7 +18593,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E319" t="n">
@@ -18621,7 +18626,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E320" t="n">
@@ -18654,7 +18659,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E321" t="n">
@@ -18687,7 +18692,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E322" t="n">
@@ -18720,7 +18725,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E323" t="n">
@@ -18753,7 +18758,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E324" t="n">
@@ -18786,7 +18791,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E325" t="n">
@@ -18819,7 +18824,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E326" t="n">
@@ -18852,7 +18857,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E327" t="n">
@@ -18885,7 +18890,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E328" t="n">
@@ -18918,7 +18923,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E329" t="n">
@@ -18951,7 +18956,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E330" t="n">
@@ -18984,7 +18989,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E331" t="n">
@@ -19017,7 +19022,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E332" t="n">
@@ -19050,7 +19055,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E333" t="n">
@@ -19083,7 +19088,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E334" t="n">
@@ -19116,7 +19121,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E335" t="n">
@@ -19149,7 +19154,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E336" t="n">
@@ -19182,7 +19187,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E337" t="n">
@@ -19215,7 +19220,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E338" t="n">
@@ -19248,7 +19253,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E339" t="n">
@@ -19281,7 +19286,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E340" t="n">
@@ -19314,7 +19319,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E341" t="n">
@@ -19347,7 +19352,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E342" t="n">
@@ -19380,7 +19385,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E343" t="n">
@@ -19413,7 +19418,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E344" t="n">
@@ -19446,7 +19451,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E345" t="n">
@@ -19479,7 +19484,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E346" t="n">
@@ -19512,7 +19517,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E347" t="n">
@@ -19545,7 +19550,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E348" t="n">
@@ -19578,7 +19583,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E349" t="n">
@@ -19611,7 +19616,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E350" t="n">
@@ -19644,7 +19649,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E351" t="n">
@@ -19677,7 +19682,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E352" t="n">
@@ -19710,7 +19715,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E353" t="n">
@@ -19743,7 +19748,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E354" t="n">
@@ -19776,7 +19781,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E355" t="n">
@@ -19809,7 +19814,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E356" t="n">
@@ -19842,7 +19847,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E357" t="n">
@@ -19875,7 +19880,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E358" t="n">
@@ -19908,7 +19913,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E359" t="n">
@@ -19941,7 +19946,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E360" t="n">
@@ -19974,7 +19979,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E361" t="n">
@@ -20007,7 +20012,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E362" t="n">
@@ -20040,7 +20045,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E363" t="n">
@@ -20073,7 +20078,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E364" t="n">
@@ -20106,7 +20111,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E365" t="n">
@@ -20139,7 +20144,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E366" t="n">
@@ -20172,7 +20177,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E367" t="n">
@@ -20205,7 +20210,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E368" t="n">
@@ -20238,7 +20243,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E369" t="n">
@@ -20271,7 +20276,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E370" t="n">
@@ -20304,7 +20309,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E371" t="n">
@@ -20337,7 +20342,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E372" t="n">
@@ -20370,7 +20375,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E373" t="n">
@@ -20403,7 +20408,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E374" t="n">
@@ -20436,7 +20441,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E375" t="n">
@@ -20469,7 +20474,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E376" t="n">
@@ -20502,7 +20507,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E377" t="n">
@@ -20535,7 +20540,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E378" t="n">
@@ -20568,7 +20573,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E379" t="n">
@@ -20601,7 +20606,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E380" t="n">
@@ -20634,7 +20639,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E381" t="n">
@@ -20667,7 +20672,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E382" t="n">
@@ -20700,7 +20705,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E383" t="n">
@@ -20733,7 +20738,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E384" t="n">
@@ -20766,7 +20771,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E385" t="n">
@@ -20799,7 +20804,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E386" t="n">
@@ -20832,7 +20837,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E387" t="n">
@@ -20865,7 +20870,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E388" t="n">
@@ -20898,7 +20903,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E389" t="n">
@@ -20931,7 +20936,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E390" t="n">
@@ -20964,7 +20969,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E391" t="n">
@@ -20997,7 +21002,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E392" t="n">
@@ -21030,7 +21035,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E393" t="n">
@@ -21063,7 +21068,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E394" t="n">
@@ -21096,7 +21101,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E395" t="n">
@@ -21129,7 +21134,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E396" t="n">
@@ -21162,7 +21167,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E397" t="n">
@@ -21195,7 +21200,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E398" t="n">
@@ -21228,7 +21233,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E399" t="n">
@@ -21261,7 +21266,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E400" t="n">
@@ -21294,7 +21299,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E401" t="n">
@@ -21327,7 +21332,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E402" t="n">
@@ -21360,7 +21365,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E403" t="n">
@@ -21393,7 +21398,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E404" t="n">
@@ -21426,7 +21431,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E405" t="n">
@@ -21459,7 +21464,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E406" t="n">
@@ -21492,7 +21497,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E407" t="n">
@@ -21525,7 +21530,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E408" t="n">
@@ -21558,7 +21563,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E409" t="n">
@@ -21591,7 +21596,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E410" t="n">
@@ -21624,7 +21629,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E411" t="n">
@@ -21657,7 +21662,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E412" t="n">
@@ -21690,7 +21695,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E413" t="n">
@@ -21723,7 +21728,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E414" t="n">
@@ -21756,7 +21761,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E415" t="n">
@@ -21789,7 +21794,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E416" t="n">
@@ -21822,7 +21827,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E417" t="n">
@@ -21855,7 +21860,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E418" t="n">
@@ -21888,7 +21893,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E419" t="n">
@@ -21921,7 +21926,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E420" t="n">
@@ -21954,7 +21959,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E421" t="n">
@@ -21987,7 +21992,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E422" t="n">
@@ -22020,7 +22025,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E423" t="n">
@@ -22053,7 +22058,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E424" t="n">
@@ -22086,7 +22091,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E425" t="n">
@@ -22119,7 +22124,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E426" t="n">
@@ -22152,7 +22157,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E427" t="n">
@@ -22185,7 +22190,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E428" t="n">
@@ -22218,7 +22223,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E429" t="n">
@@ -22251,7 +22256,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E430" t="n">
@@ -22284,7 +22289,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E431" t="n">
@@ -22317,7 +22322,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E432" t="n">
@@ -22350,7 +22355,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E433" t="n">
@@ -22383,7 +22388,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E434" t="n">
@@ -22416,7 +22421,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E435" t="n">
@@ -22449,7 +22454,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E436" t="n">
@@ -22482,7 +22487,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E437" t="n">
@@ -22515,7 +22520,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E438" t="n">
@@ -22548,7 +22553,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E439" t="n">
@@ -22581,7 +22586,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E440" t="n">
@@ -22614,7 +22619,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E441" t="n">
@@ -22647,7 +22652,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E442" t="n">
@@ -22680,7 +22685,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E443" t="n">
@@ -22713,7 +22718,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E444" t="n">
@@ -22746,7 +22751,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E445" t="n">
@@ -22779,7 +22784,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E446" t="n">
@@ -22812,7 +22817,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E447" t="n">
@@ -22845,7 +22850,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E448" t="n">
@@ -22878,7 +22883,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E449" t="n">
@@ -22911,7 +22916,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E450" t="n">
@@ -22944,7 +22949,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E451" t="n">
@@ -22977,7 +22982,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E452" t="n">
@@ -23010,7 +23015,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E453" t="n">
@@ -23043,7 +23048,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E454" t="n">
@@ -23076,7 +23081,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E455" t="n">
@@ -23109,7 +23114,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E456" t="n">
@@ -23142,7 +23147,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E457" t="n">
@@ -23175,7 +23180,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E458" t="n">
@@ -23208,7 +23213,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E459" t="n">
@@ -23241,7 +23246,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E460" t="n">
@@ -23274,7 +23279,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E461" t="n">
@@ -23307,7 +23312,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E462" t="n">
@@ -23340,7 +23345,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E463" t="n">
@@ -23373,7 +23378,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E464" t="n">
@@ -23406,7 +23411,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E465" t="n">
@@ -23439,7 +23444,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E466" t="n">
@@ -23472,7 +23477,7 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E467" t="n">
@@ -23505,7 +23510,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E468" t="n">
@@ -23538,7 +23543,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E469" t="n">
@@ -23571,7 +23576,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E470" t="n">
@@ -23604,7 +23609,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E471" t="n">
@@ -23637,7 +23642,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E472" t="n">
@@ -23670,7 +23675,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E473" t="n">
@@ -23703,7 +23708,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E474" t="n">
@@ -23736,7 +23741,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E475" t="n">
@@ -23769,7 +23774,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E476" t="n">
@@ -23802,7 +23807,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E477" t="n">
@@ -23835,7 +23840,7 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E478" t="n">
@@ -23868,7 +23873,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E479" t="n">
@@ -23901,7 +23906,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E480" t="n">
@@ -23934,7 +23939,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E481" t="n">
@@ -23967,7 +23972,7 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E482" t="n">
@@ -24000,7 +24005,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E483" t="n">
@@ -24033,7 +24038,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E484" t="n">
@@ -24066,7 +24071,7 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E485" t="n">
@@ -24099,7 +24104,7 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E486" t="n">
@@ -24132,7 +24137,7 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E487" t="n">
@@ -24165,7 +24170,7 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E488" t="n">
@@ -24198,7 +24203,7 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E489" t="n">
@@ -24231,7 +24236,7 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E490" t="n">
@@ -24264,7 +24269,7 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E491" t="n">
@@ -24297,7 +24302,7 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E492" t="n">
@@ -24330,7 +24335,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E493" t="n">
@@ -24363,7 +24368,7 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E494" t="n">
@@ -24396,7 +24401,7 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E495" t="n">
@@ -24429,7 +24434,7 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E496" t="n">
@@ -24462,7 +24467,7 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E497" t="n">
@@ -24495,7 +24500,7 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E498" t="n">
@@ -24528,7 +24533,7 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E499" t="n">
@@ -24561,7 +24566,7 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E500" t="n">
@@ -24594,7 +24599,7 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E501" t="n">
@@ -24627,7 +24632,7 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E502" t="n">
@@ -24660,7 +24665,7 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E503" t="n">
@@ -24693,7 +24698,7 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E504" t="n">
@@ -24726,7 +24731,7 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E505" t="n">
@@ -24759,7 +24764,7 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E506" t="n">
@@ -24792,7 +24797,7 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E507" t="n">
@@ -24825,7 +24830,7 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E508" t="n">
@@ -24858,7 +24863,7 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E509" t="n">
@@ -24891,7 +24896,7 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E510" t="n">
@@ -24924,7 +24929,7 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E511" t="n">
@@ -24957,7 +24962,7 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E512" t="n">
@@ -24990,7 +24995,7 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E513" t="n">
@@ -25023,7 +25028,7 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E514" t="n">
@@ -25056,7 +25061,7 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E515" t="n">
@@ -25089,7 +25094,7 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E516" t="n">
@@ -25122,7 +25127,7 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E517" t="n">
@@ -25155,7 +25160,7 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E518" t="n">
@@ -25188,7 +25193,7 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E519" t="n">
@@ -25221,7 +25226,7 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E520" t="n">
@@ -25254,7 +25259,7 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E521" t="n">
@@ -25287,7 +25292,7 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E522" t="n">
@@ -25320,7 +25325,7 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E523" t="n">
@@ -25353,7 +25358,7 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E524" t="n">
@@ -25386,7 +25391,7 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E525" t="n">
@@ -25419,7 +25424,7 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E526" t="n">
@@ -25452,7 +25457,7 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E527" t="n">
@@ -25485,7 +25490,7 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E528" t="n">
@@ -25518,7 +25523,7 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E529" t="n">
@@ -25551,7 +25556,7 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E530" t="n">
@@ -25584,7 +25589,7 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E531" t="n">
@@ -25617,7 +25622,7 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E532" t="n">
@@ -25650,7 +25655,7 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E533" t="n">
@@ -25683,7 +25688,7 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E534" t="n">
@@ -25716,7 +25721,7 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E535" t="n">
@@ -25749,7 +25754,7 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E536" t="n">
@@ -25782,7 +25787,7 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E537" t="n">
@@ -25815,7 +25820,7 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E538" t="n">
@@ -25848,7 +25853,7 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E539" t="n">
@@ -25881,7 +25886,7 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E540" t="n">
@@ -25914,7 +25919,7 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E541" t="n">
@@ -25947,7 +25952,7 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E542" t="n">
@@ -25980,7 +25985,7 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E543" t="n">
@@ -26013,7 +26018,7 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E544" t="n">
@@ -26046,7 +26051,7 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E545" t="n">
@@ -26079,7 +26084,7 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E546" t="n">
@@ -26112,7 +26117,7 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E547" t="n">
@@ -26145,7 +26150,7 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E548" t="n">
@@ -26178,7 +26183,7 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E549" t="n">
@@ -26211,7 +26216,7 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E550" t="n">
@@ -26244,7 +26249,7 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>地级政协</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="E551" t="n">

--- a/xlsx/cards.unified.xlsx
+++ b/xlsx/cards.unified.xlsx
@@ -14196,6 +14196,11 @@
           <t>中国人民政治协商会议北京市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>https://www.bjzx.gov.cn/favicon.ico</t>
+        </is>
+      </c>
       <c r="I227" t="inlineStr">
         <is>
           <t>直辖市政协,北京市</t>
@@ -14561,6 +14566,11 @@
           <t>中国人民政治协商会议吉林省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>https://www.jlzx.gov.cn/images/favicon.png</t>
+        </is>
+      </c>
       <c r="I233" t="inlineStr">
         <is>
           <t>省政协,吉林省</t>
@@ -14621,6 +14631,11 @@
           <t>中国人民政治协商会议黑龙江省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>https://www.hljzx.gov.cn/favicon.ico</t>
+        </is>
+      </c>
       <c r="I234" t="inlineStr">
         <is>
           <t>省政协,黑龙江省</t>
@@ -14801,6 +14816,11 @@
           <t>中国人民政治协商会议浙江省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>https://www.zjzx.gov.cn/favicon.ico</t>
+        </is>
+      </c>
       <c r="I237" t="inlineStr">
         <is>
           <t>省政协,浙江省</t>
@@ -15291,6 +15311,11 @@
           <t>中国人民政治协商会议广东省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>https://www.gdszx.gov.cn/favicon.ico</t>
+        </is>
+      </c>
       <c r="I245" t="inlineStr">
         <is>
           <t>省政协,广东省</t>
@@ -17003,6 +17028,11 @@
       <c r="G278" t="inlineStr">
         <is>
           <t>中国人民政治协商会议河源市委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>http://www.gdhyzx.gov.cn/favicon.ico</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">

--- a/xlsx/cards.unified.xlsx
+++ b/xlsx/cards.unified.xlsx
@@ -14816,11 +14816,6 @@
           <t>中国人民政治协商会议浙江省委员会官方网站。提供政协动态、会议提案、委员履职等信息。</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>https://www.zjzx.gov.cn/favicon.ico</t>
-        </is>
-      </c>
       <c r="I237" t="inlineStr">
         <is>
           <t>省政协,浙江省</t>
